--- a/templates/excel/format CC5.xlsx
+++ b/templates/excel/format CC5.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github-desktop\UI\DEV\CA-DEV\CA-BACKEND-DEV\templates\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CA-DEV\CA-BACKEND-DEV\templates\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA3055EF-ACAC-41D7-9C5D-048527111C8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B95BB1EB-8AD7-49AD-8322-32F2FA1A866D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Assumptions.1" sheetId="26" r:id="rId1"/>
@@ -2445,7 +2445,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="395">
+  <cellXfs count="418">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2805,15 +2805,8 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="32" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3088,6 +3081,87 @@
     <xf numFmtId="1" fontId="10" fillId="6" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="26" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -3118,85 +3192,25 @@
     <xf numFmtId="17" fontId="28" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="26" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3208,51 +3222,15 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3324,6 +3302,81 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="4" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1"/>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1"/>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4100,31 +4153,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T200"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.7265625" customWidth="1"/>
-    <col min="2" max="2" width="15.453125" customWidth="1"/>
-    <col min="3" max="3" width="67.81640625" style="90" customWidth="1"/>
-    <col min="4" max="4" width="29.7265625" style="101" customWidth="1"/>
-    <col min="5" max="5" width="12.81640625" style="101" customWidth="1"/>
-    <col min="6" max="6" width="57.26953125" style="101" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.453125" style="101" customWidth="1"/>
-    <col min="8" max="8" width="14.7265625" customWidth="1"/>
-    <col min="9" max="9" width="34.7265625" style="101" customWidth="1"/>
-    <col min="10" max="10" width="23.54296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.1796875" customWidth="1"/>
-    <col min="12" max="12" width="32.453125" customWidth="1"/>
-    <col min="13" max="13" width="10.7265625" customWidth="1"/>
-    <col min="14" max="14" width="13.54296875" customWidth="1"/>
-    <col min="15" max="15" width="12.7265625" customWidth="1"/>
-    <col min="16" max="16" width="11.1796875" customWidth="1"/>
+    <col min="1" max="1" width="13.77734375" customWidth="1"/>
+    <col min="2" max="2" width="15.44140625" customWidth="1"/>
+    <col min="3" max="3" width="67.77734375" style="90" customWidth="1"/>
+    <col min="4" max="4" width="29.77734375" style="101" customWidth="1"/>
+    <col min="5" max="5" width="12.77734375" style="101" customWidth="1"/>
+    <col min="6" max="6" width="57.21875" style="101" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.44140625" style="101" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" customWidth="1"/>
+    <col min="9" max="9" width="34.77734375" style="101" customWidth="1"/>
+    <col min="10" max="10" width="23.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.21875" customWidth="1"/>
+    <col min="12" max="12" width="32.44140625" customWidth="1"/>
+    <col min="13" max="13" width="10.77734375" customWidth="1"/>
+    <col min="14" max="14" width="13.5546875" customWidth="1"/>
+    <col min="15" max="15" width="12.77734375" customWidth="1"/>
+    <col min="16" max="16" width="11.21875" customWidth="1"/>
     <col min="17" max="17" width="13" customWidth="1"/>
-    <col min="18" max="19" width="15.54296875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:17" ht="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:17" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:17" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:17" ht="53.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="146" t="s">
         <v>146</v>
       </c>
@@ -4159,8 +4212,8 @@
       <c r="P2" s="166"/>
       <c r="Q2" s="166"/>
     </row>
-    <row r="3" spans="2:17" ht="14" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="317" t="s">
+    <row r="3" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B3" s="341" t="s">
         <v>160</v>
       </c>
       <c r="C3" s="145" t="s">
@@ -4175,8 +4228,8 @@
       <c r="F3" s="111"/>
       <c r="G3" s="111"/>
       <c r="H3" s="112"/>
-      <c r="I3" s="216"/>
-      <c r="J3" s="217"/>
+      <c r="I3" s="213"/>
+      <c r="J3" s="214"/>
       <c r="L3" s="90"/>
       <c r="M3" s="90"/>
       <c r="N3" s="168"/>
@@ -4184,24 +4237,24 @@
       <c r="P3" s="166"/>
       <c r="Q3" s="166"/>
     </row>
-    <row r="4" spans="2:17" ht="13.5" x14ac:dyDescent="0.35">
-      <c r="B4" s="318"/>
-      <c r="C4" s="243" t="s">
+    <row r="4" spans="2:17" ht="14.4" x14ac:dyDescent="0.35">
+      <c r="B4" s="342"/>
+      <c r="C4" s="240" t="s">
         <v>248</v>
       </c>
-      <c r="D4" s="244" t="s">
+      <c r="D4" s="241" t="s">
         <v>195</v>
       </c>
-      <c r="E4" s="245" t="s">
+      <c r="E4" s="242" t="s">
         <v>125</v>
       </c>
-      <c r="F4" s="246" t="s">
+      <c r="F4" s="243" t="s">
         <v>249</v>
       </c>
-      <c r="G4" s="247"/>
+      <c r="G4" s="244"/>
       <c r="H4" s="137"/>
-      <c r="I4" s="248"/>
-      <c r="J4" s="242"/>
+      <c r="I4" s="245"/>
+      <c r="J4" s="239"/>
       <c r="L4" s="90"/>
       <c r="M4" s="90"/>
       <c r="N4" s="168"/>
@@ -4209,8 +4262,8 @@
       <c r="P4" s="166"/>
       <c r="Q4" s="166"/>
     </row>
-    <row r="5" spans="2:17" ht="13.5" x14ac:dyDescent="0.35">
-      <c r="B5" s="319"/>
+    <row r="5" spans="2:17" ht="14.4" x14ac:dyDescent="0.35">
+      <c r="B5" s="343"/>
       <c r="C5" s="106" t="s">
         <v>105</v>
       </c>
@@ -4223,8 +4276,8 @@
       <c r="F5" s="108"/>
       <c r="G5" s="108"/>
       <c r="H5" s="110"/>
-      <c r="I5" s="218"/>
-      <c r="J5" s="219"/>
+      <c r="I5" s="215"/>
+      <c r="J5" s="216"/>
       <c r="L5" s="90"/>
       <c r="M5" s="90"/>
       <c r="N5" s="168"/>
@@ -4232,8 +4285,8 @@
       <c r="P5" s="166"/>
       <c r="Q5" s="166"/>
     </row>
-    <row r="6" spans="2:17" ht="13.5" x14ac:dyDescent="0.3">
-      <c r="B6" s="319"/>
+    <row r="6" spans="2:17" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="B6" s="343"/>
       <c r="C6" s="109" t="s">
         <v>106</v>
       </c>
@@ -4246,8 +4299,8 @@
       <c r="F6" s="108"/>
       <c r="G6" s="108"/>
       <c r="H6" s="110"/>
-      <c r="I6" s="220"/>
-      <c r="J6" s="219"/>
+      <c r="I6" s="217"/>
+      <c r="J6" s="216"/>
       <c r="L6" s="90"/>
       <c r="M6" s="90"/>
       <c r="N6" s="168"/>
@@ -4255,8 +4308,8 @@
       <c r="P6" s="166"/>
       <c r="Q6" s="166"/>
     </row>
-    <row r="7" spans="2:17" ht="13.5" x14ac:dyDescent="0.3">
-      <c r="B7" s="320"/>
+    <row r="7" spans="2:17" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="B7" s="344"/>
       <c r="C7" s="151" t="s">
         <v>154</v>
       </c>
@@ -4271,8 +4324,8 @@
       </c>
       <c r="G7" s="143"/>
       <c r="H7" s="144"/>
-      <c r="I7" s="221"/>
-      <c r="J7" s="222"/>
+      <c r="I7" s="218"/>
+      <c r="J7" s="219"/>
       <c r="L7" s="90"/>
       <c r="M7" s="90"/>
       <c r="N7" s="168"/>
@@ -4280,8 +4333,8 @@
       <c r="P7" s="166"/>
       <c r="Q7" s="166"/>
     </row>
-    <row r="8" spans="2:17" ht="14" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="321"/>
+    <row r="8" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="345"/>
       <c r="C8" s="151" t="s">
         <v>132</v>
       </c>
@@ -4291,11 +4344,11 @@
       <c r="E8" s="143" t="s">
         <v>125</v>
       </c>
-      <c r="F8" s="190"/>
+      <c r="F8" s="189"/>
       <c r="G8" s="152"/>
       <c r="H8" s="144"/>
-      <c r="I8" s="221"/>
-      <c r="J8" s="223"/>
+      <c r="I8" s="218"/>
+      <c r="J8" s="220"/>
       <c r="L8" s="90"/>
       <c r="M8" s="90"/>
       <c r="N8" s="168"/>
@@ -4303,7 +4356,7 @@
       <c r="P8" s="166"/>
       <c r="Q8" s="166"/>
     </row>
-    <row r="9" spans="2:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:17" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="157"/>
       <c r="C9" s="153"/>
       <c r="D9" s="154"/>
@@ -4320,11 +4373,11 @@
       <c r="P9" s="166"/>
       <c r="Q9" s="166"/>
     </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B10" s="317" t="s">
+    <row r="10" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B10" s="341" t="s">
         <v>159</v>
       </c>
-      <c r="C10" s="244" t="s">
+      <c r="C10" s="241" t="s">
         <v>172</v>
       </c>
       <c r="D10" s="149" t="s">
@@ -4339,7 +4392,7 @@
       <c r="G10" s="111"/>
       <c r="H10" s="112"/>
       <c r="I10" s="111"/>
-      <c r="J10" s="217"/>
+      <c r="J10" s="214"/>
       <c r="L10" s="90"/>
       <c r="M10" s="90"/>
       <c r="N10" s="168"/>
@@ -4347,8 +4400,8 @@
       <c r="P10" s="166"/>
       <c r="Q10" s="166"/>
     </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B11" s="318"/>
+    <row r="11" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B11" s="342"/>
       <c r="C11" s="150" t="s">
         <v>184</v>
       </c>
@@ -4364,7 +4417,7 @@
       <c r="G11" s="136"/>
       <c r="H11" s="137"/>
       <c r="I11" s="136"/>
-      <c r="J11" s="224"/>
+      <c r="J11" s="221"/>
       <c r="L11" s="90"/>
       <c r="M11" s="90"/>
       <c r="N11" s="168"/>
@@ -4372,9 +4425,9 @@
       <c r="P11" s="166"/>
       <c r="Q11" s="166"/>
     </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B12" s="319"/>
-      <c r="C12" s="301" t="s">
+    <row r="12" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B12" s="343"/>
+      <c r="C12" s="298" t="s">
         <v>182</v>
       </c>
       <c r="D12" s="108" t="s">
@@ -4387,7 +4440,7 @@
       <c r="G12" s="108"/>
       <c r="H12" s="110"/>
       <c r="I12" s="108"/>
-      <c r="J12" s="225" t="s">
+      <c r="J12" s="222" t="s">
         <v>130</v>
       </c>
       <c r="L12" s="90"/>
@@ -4397,9 +4450,9 @@
       <c r="P12" s="166"/>
       <c r="Q12" s="166"/>
     </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B13" s="319"/>
-      <c r="C13" s="301" t="s">
+    <row r="13" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B13" s="343"/>
+      <c r="C13" s="298" t="s">
         <v>183</v>
       </c>
       <c r="D13" s="108" t="s">
@@ -4410,9 +4463,9 @@
       </c>
       <c r="F13" s="108"/>
       <c r="G13" s="108"/>
-      <c r="H13" s="240"/>
+      <c r="H13" s="237"/>
       <c r="I13" s="108"/>
-      <c r="J13" s="225"/>
+      <c r="J13" s="222"/>
       <c r="L13" s="90"/>
       <c r="M13" s="90"/>
       <c r="N13" s="168"/>
@@ -4420,8 +4473,8 @@
       <c r="P13" s="166"/>
       <c r="Q13" s="166"/>
     </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B14" s="319"/>
+    <row r="14" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B14" s="343"/>
       <c r="C14" s="106" t="s">
         <v>100</v>
       </c>
@@ -4433,14 +4486,14 @@
       </c>
       <c r="F14" s="108"/>
       <c r="G14" s="108"/>
-      <c r="H14" s="240">
-        <v>0</v>
-      </c>
-      <c r="I14" s="236">
+      <c r="H14" s="237">
+        <v>0</v>
+      </c>
+      <c r="I14" s="233">
         <f>H14*1/100</f>
         <v>0</v>
       </c>
-      <c r="J14" s="225" t="s">
+      <c r="J14" s="222" t="s">
         <v>129</v>
       </c>
       <c r="L14" s="90"/>
@@ -4450,8 +4503,8 @@
       <c r="P14" s="166"/>
       <c r="Q14" s="166"/>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B15" s="319"/>
+    <row r="15" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B15" s="343"/>
       <c r="C15" s="106" t="s">
         <v>185</v>
       </c>
@@ -4463,14 +4516,14 @@
       </c>
       <c r="F15" s="108"/>
       <c r="G15" s="108"/>
-      <c r="H15" s="240">
-        <v>0</v>
-      </c>
-      <c r="I15" s="237">
+      <c r="H15" s="237">
+        <v>0</v>
+      </c>
+      <c r="I15" s="234">
         <f>(H15+H15*18/100)*1/100</f>
         <v>0</v>
       </c>
-      <c r="J15" s="225" t="s">
+      <c r="J15" s="222" t="s">
         <v>128</v>
       </c>
       <c r="L15" s="90"/>
@@ -4480,8 +4533,8 @@
       <c r="P15" s="166"/>
       <c r="Q15" s="166"/>
     </row>
-    <row r="16" spans="2:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="320"/>
+    <row r="16" spans="2:17" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="344"/>
       <c r="C16" s="158" t="s">
         <v>109</v>
       </c>
@@ -4495,14 +4548,14 @@
       <c r="G16" s="143" t="s">
         <v>225</v>
       </c>
-      <c r="H16" s="241">
-        <v>0</v>
-      </c>
-      <c r="I16" s="238">
+      <c r="H16" s="238">
+        <v>0</v>
+      </c>
+      <c r="I16" s="235">
         <f>H16*1/100</f>
         <v>0</v>
       </c>
-      <c r="J16" s="226" t="s">
+      <c r="J16" s="223" t="s">
         <v>131</v>
       </c>
       <c r="L16" s="90"/>
@@ -4512,16 +4565,16 @@
       <c r="P16" s="166"/>
       <c r="Q16" s="166"/>
     </row>
-    <row r="17" spans="1:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="199"/>
-      <c r="C17" s="200"/>
-      <c r="D17" s="201"/>
-      <c r="E17" s="201"/>
-      <c r="F17" s="201"/>
-      <c r="G17" s="201"/>
-      <c r="H17" s="202"/>
-      <c r="I17" s="201"/>
-      <c r="J17" s="203"/>
+    <row r="17" spans="1:17" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="196"/>
+      <c r="C17" s="197"/>
+      <c r="D17" s="198"/>
+      <c r="E17" s="198"/>
+      <c r="F17" s="198"/>
+      <c r="G17" s="198"/>
+      <c r="H17" s="199"/>
+      <c r="I17" s="198"/>
+      <c r="J17" s="200"/>
       <c r="L17" s="90"/>
       <c r="M17" s="90"/>
       <c r="N17" s="168"/>
@@ -4529,8 +4582,8 @@
       <c r="P17" s="166"/>
       <c r="Q17" s="166"/>
     </row>
-    <row r="18" spans="1:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="323" t="s">
+    <row r="18" spans="1:17" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="347" t="s">
         <v>194</v>
       </c>
       <c r="C18" s="145" t="s">
@@ -4548,7 +4601,7 @@
       <c r="G18" s="145"/>
       <c r="H18" s="112"/>
       <c r="I18" s="111"/>
-      <c r="J18" s="227" t="s">
+      <c r="J18" s="224" t="s">
         <v>196</v>
       </c>
       <c r="L18" s="90" t="s">
@@ -4560,8 +4613,8 @@
       <c r="P18" s="166"/>
       <c r="Q18" s="166"/>
     </row>
-    <row r="19" spans="1:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="324"/>
+    <row r="19" spans="1:17" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="348"/>
       <c r="C19" s="106" t="s">
         <v>156</v>
       </c>
@@ -4577,7 +4630,7 @@
       <c r="G19" s="106"/>
       <c r="H19" s="110"/>
       <c r="I19" s="108"/>
-      <c r="J19" s="228" t="s">
+      <c r="J19" s="225" t="s">
         <v>107</v>
       </c>
       <c r="L19" s="90"/>
@@ -4587,8 +4640,8 @@
       <c r="P19" s="166"/>
       <c r="Q19" s="166"/>
     </row>
-    <row r="20" spans="1:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="324"/>
+    <row r="20" spans="1:17" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="348"/>
       <c r="C20" s="106" t="s">
         <v>157</v>
       </c>
@@ -4604,7 +4657,7 @@
       <c r="G20" s="106"/>
       <c r="H20" s="110"/>
       <c r="I20" s="108"/>
-      <c r="J20" s="228" t="s">
+      <c r="J20" s="225" t="s">
         <v>98</v>
       </c>
       <c r="L20" s="90"/>
@@ -4614,8 +4667,8 @@
       <c r="P20" s="166"/>
       <c r="Q20" s="166"/>
     </row>
-    <row r="21" spans="1:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="324"/>
+    <row r="21" spans="1:17" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="348"/>
       <c r="C21" s="158" t="s">
         <v>158</v>
       </c>
@@ -4631,7 +4684,7 @@
       <c r="G21" s="158"/>
       <c r="H21" s="144"/>
       <c r="I21" s="143"/>
-      <c r="J21" s="229" t="s">
+      <c r="J21" s="226" t="s">
         <v>98</v>
       </c>
       <c r="L21" s="90"/>
@@ -4641,9 +4694,9 @@
       <c r="P21" s="166"/>
       <c r="Q21" s="166"/>
     </row>
-    <row r="22" spans="1:17" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:17" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="153"/>
-      <c r="C22" s="204">
+      <c r="C22" s="201">
         <f>I18</f>
         <v>0</v>
       </c>
@@ -4662,13 +4715,13 @@
       <c r="Q22" s="166"/>
     </row>
     <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="325" t="s">
+      <c r="B23" s="349" t="s">
         <v>210</v>
       </c>
-      <c r="C23" s="193" t="s">
+      <c r="C23" s="190" t="s">
         <v>186</v>
       </c>
-      <c r="D23" s="212" t="s">
+      <c r="D23" s="209" t="s">
         <v>124</v>
       </c>
       <c r="E23" s="136" t="s">
@@ -4676,20 +4729,20 @@
       </c>
       <c r="F23" s="150"/>
       <c r="G23" s="150"/>
-      <c r="H23" s="215"/>
-      <c r="I23" s="230"/>
-      <c r="J23" s="231"/>
+      <c r="H23" s="212"/>
+      <c r="I23" s="227"/>
+      <c r="J23" s="228"/>
       <c r="N23" s="164"/>
-      <c r="O23" s="322"/>
-      <c r="P23" s="322"/>
-      <c r="Q23" s="322"/>
+      <c r="O23" s="346"/>
+      <c r="P23" s="346"/>
+      <c r="Q23" s="346"/>
     </row>
     <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="325"/>
-      <c r="C24" s="194" t="s">
+      <c r="B24" s="349"/>
+      <c r="C24" s="191" t="s">
         <v>1</v>
       </c>
-      <c r="D24" s="213" t="s">
+      <c r="D24" s="210" t="s">
         <v>124</v>
       </c>
       <c r="E24" s="108" t="s">
@@ -4697,23 +4750,23 @@
       </c>
       <c r="F24" s="106"/>
       <c r="G24" s="106"/>
-      <c r="H24" s="215"/>
-      <c r="I24" s="232"/>
-      <c r="J24" s="231"/>
+      <c r="H24" s="212"/>
+      <c r="I24" s="229"/>
+      <c r="J24" s="228"/>
       <c r="N24" s="164"/>
       <c r="O24" s="164"/>
       <c r="P24" s="164"/>
       <c r="Q24" s="164"/>
     </row>
     <row r="25" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="316" t="s">
+      <c r="A25" s="340" t="s">
         <v>221</v>
       </c>
-      <c r="B25" s="325"/>
-      <c r="C25" s="194" t="s">
+      <c r="B25" s="349"/>
+      <c r="C25" s="191" t="s">
         <v>96</v>
       </c>
-      <c r="D25" s="213" t="s">
+      <c r="D25" s="210" t="s">
         <v>124</v>
       </c>
       <c r="E25" s="108" t="s">
@@ -4721,21 +4774,21 @@
       </c>
       <c r="F25" s="106"/>
       <c r="G25" s="106"/>
-      <c r="H25" s="215"/>
-      <c r="I25" s="232"/>
-      <c r="J25" s="231"/>
+      <c r="H25" s="212"/>
+      <c r="I25" s="229"/>
+      <c r="J25" s="228"/>
       <c r="N25" s="164"/>
       <c r="O25" s="164"/>
       <c r="P25" s="164"/>
       <c r="Q25" s="164"/>
     </row>
     <row r="26" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="316"/>
-      <c r="B26" s="325"/>
-      <c r="C26" s="194" t="s">
+      <c r="A26" s="340"/>
+      <c r="B26" s="349"/>
+      <c r="C26" s="191" t="s">
         <v>2</v>
       </c>
-      <c r="D26" s="213" t="s">
+      <c r="D26" s="210" t="s">
         <v>124</v>
       </c>
       <c r="E26" s="108" t="s">
@@ -4743,20 +4796,20 @@
       </c>
       <c r="F26" s="106"/>
       <c r="G26" s="106"/>
-      <c r="H26" s="215"/>
-      <c r="I26" s="232"/>
-      <c r="J26" s="231"/>
+      <c r="H26" s="212"/>
+      <c r="I26" s="229"/>
+      <c r="J26" s="228"/>
       <c r="N26" s="164"/>
       <c r="O26" s="164"/>
       <c r="P26" s="164"/>
       <c r="Q26" s="164"/>
     </row>
     <row r="27" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="325"/>
-      <c r="C27" s="194" t="s">
+      <c r="B27" s="349"/>
+      <c r="C27" s="191" t="s">
         <v>188</v>
       </c>
-      <c r="D27" s="213" t="s">
+      <c r="D27" s="210" t="s">
         <v>124</v>
       </c>
       <c r="E27" s="108" t="s">
@@ -4764,20 +4817,20 @@
       </c>
       <c r="F27" s="106"/>
       <c r="G27" s="106"/>
-      <c r="H27" s="215"/>
-      <c r="I27" s="233"/>
-      <c r="J27" s="231"/>
+      <c r="H27" s="212"/>
+      <c r="I27" s="230"/>
+      <c r="J27" s="228"/>
       <c r="N27" s="164"/>
       <c r="O27" s="164"/>
       <c r="P27" s="164"/>
       <c r="Q27" s="164"/>
     </row>
     <row r="28" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="325"/>
-      <c r="C28" s="194" t="s">
+      <c r="B28" s="349"/>
+      <c r="C28" s="191" t="s">
         <v>69</v>
       </c>
-      <c r="D28" s="213" t="s">
+      <c r="D28" s="210" t="s">
         <v>124</v>
       </c>
       <c r="E28" s="108" t="s">
@@ -4785,20 +4838,20 @@
       </c>
       <c r="F28" s="106"/>
       <c r="G28" s="106"/>
-      <c r="H28" s="215"/>
-      <c r="I28" s="232"/>
-      <c r="J28" s="231"/>
+      <c r="H28" s="212"/>
+      <c r="I28" s="229"/>
+      <c r="J28" s="228"/>
       <c r="N28" s="164"/>
       <c r="O28" s="164"/>
       <c r="P28" s="164"/>
       <c r="Q28" s="164"/>
     </row>
     <row r="29" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="325"/>
-      <c r="C29" s="194" t="s">
+      <c r="B29" s="349"/>
+      <c r="C29" s="191" t="s">
         <v>33</v>
       </c>
-      <c r="D29" s="213" t="s">
+      <c r="D29" s="210" t="s">
         <v>124</v>
       </c>
       <c r="E29" s="108" t="s">
@@ -4806,20 +4859,20 @@
       </c>
       <c r="F29" s="106"/>
       <c r="G29" s="106"/>
-      <c r="H29" s="215"/>
-      <c r="I29" s="232"/>
-      <c r="J29" s="231"/>
+      <c r="H29" s="212"/>
+      <c r="I29" s="229"/>
+      <c r="J29" s="228"/>
       <c r="N29" s="164"/>
       <c r="O29" s="164"/>
       <c r="P29" s="164"/>
       <c r="Q29" s="164"/>
     </row>
     <row r="30" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="325"/>
-      <c r="C30" s="194" t="s">
+      <c r="B30" s="349"/>
+      <c r="C30" s="191" t="s">
         <v>163</v>
       </c>
-      <c r="D30" s="213" t="s">
+      <c r="D30" s="210" t="s">
         <v>124</v>
       </c>
       <c r="E30" s="108" t="s">
@@ -4827,20 +4880,20 @@
       </c>
       <c r="F30" s="106"/>
       <c r="G30" s="106"/>
-      <c r="H30" s="215"/>
-      <c r="I30" s="232"/>
-      <c r="J30" s="231"/>
+      <c r="H30" s="212"/>
+      <c r="I30" s="229"/>
+      <c r="J30" s="228"/>
       <c r="N30" s="164"/>
       <c r="O30" s="164"/>
       <c r="P30" s="164"/>
       <c r="Q30" s="164"/>
     </row>
     <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="325"/>
-      <c r="C31" s="194" t="s">
+      <c r="B31" s="349"/>
+      <c r="C31" s="191" t="s">
         <v>70</v>
       </c>
-      <c r="D31" s="213" t="s">
+      <c r="D31" s="210" t="s">
         <v>124</v>
       </c>
       <c r="E31" s="108" t="s">
@@ -4848,20 +4901,20 @@
       </c>
       <c r="F31" s="106"/>
       <c r="G31" s="106"/>
-      <c r="H31" s="215"/>
-      <c r="I31" s="232"/>
-      <c r="J31" s="231"/>
+      <c r="H31" s="212"/>
+      <c r="I31" s="229"/>
+      <c r="J31" s="228"/>
       <c r="N31" s="164"/>
       <c r="O31" s="164"/>
       <c r="P31" s="164"/>
       <c r="Q31" s="164"/>
     </row>
     <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="325"/>
-      <c r="C32" s="194" t="s">
+      <c r="B32" s="349"/>
+      <c r="C32" s="191" t="s">
         <v>185</v>
       </c>
-      <c r="D32" s="213" t="s">
+      <c r="D32" s="210" t="s">
         <v>124</v>
       </c>
       <c r="E32" s="108" t="s">
@@ -4869,20 +4922,20 @@
       </c>
       <c r="F32" s="106"/>
       <c r="G32" s="106"/>
-      <c r="H32" s="215"/>
-      <c r="I32" s="232"/>
-      <c r="J32" s="231"/>
+      <c r="H32" s="212"/>
+      <c r="I32" s="229"/>
+      <c r="J32" s="228"/>
       <c r="N32" s="164"/>
       <c r="O32" s="164"/>
       <c r="P32" s="164"/>
       <c r="Q32" s="164"/>
     </row>
     <row r="33" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="325"/>
-      <c r="C33" s="195" t="s">
+      <c r="B33" s="349"/>
+      <c r="C33" s="192" t="s">
         <v>197</v>
       </c>
-      <c r="D33" s="213" t="s">
+      <c r="D33" s="210" t="s">
         <v>124</v>
       </c>
       <c r="E33" s="143" t="s">
@@ -4890,20 +4943,20 @@
       </c>
       <c r="F33" s="106"/>
       <c r="G33" s="106"/>
-      <c r="H33" s="215"/>
-      <c r="I33" s="233"/>
-      <c r="J33" s="231"/>
+      <c r="H33" s="212"/>
+      <c r="I33" s="230"/>
+      <c r="J33" s="228"/>
       <c r="N33" s="164"/>
       <c r="O33" s="164"/>
       <c r="P33" s="164"/>
       <c r="Q33" s="164"/>
     </row>
     <row r="34" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B34" s="325"/>
-      <c r="C34" s="196" t="s">
+      <c r="B34" s="349"/>
+      <c r="C34" s="193" t="s">
         <v>136</v>
       </c>
-      <c r="D34" s="213" t="s">
+      <c r="D34" s="210" t="s">
         <v>124</v>
       </c>
       <c r="E34" s="143" t="s">
@@ -4911,20 +4964,20 @@
       </c>
       <c r="F34" s="106"/>
       <c r="G34" s="106"/>
-      <c r="H34" s="215"/>
-      <c r="I34" s="233"/>
-      <c r="J34" s="231"/>
+      <c r="H34" s="212"/>
+      <c r="I34" s="230"/>
+      <c r="J34" s="228"/>
       <c r="N34" s="164"/>
       <c r="O34" s="164"/>
       <c r="P34" s="164"/>
       <c r="Q34" s="164"/>
     </row>
     <row r="35" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B35" s="325"/>
-      <c r="C35" s="194" t="s">
+      <c r="B35" s="349"/>
+      <c r="C35" s="191" t="s">
         <v>239</v>
       </c>
-      <c r="D35" s="213" t="s">
+      <c r="D35" s="210" t="s">
         <v>124</v>
       </c>
       <c r="E35" s="108" t="s">
@@ -4932,44 +4985,44 @@
       </c>
       <c r="F35" s="106"/>
       <c r="G35" s="106"/>
-      <c r="H35" s="215"/>
-      <c r="I35" s="232"/>
-      <c r="J35" s="231"/>
+      <c r="H35" s="212"/>
+      <c r="I35" s="229"/>
+      <c r="J35" s="228"/>
       <c r="N35" s="164"/>
       <c r="O35" s="164"/>
       <c r="P35" s="164"/>
       <c r="Q35" s="164"/>
     </row>
-    <row r="36" spans="2:17" s="310" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="325"/>
-      <c r="C36" s="313" t="s">
+    <row r="36" spans="2:17" s="307" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B36" s="349"/>
+      <c r="C36" s="310" t="s">
         <v>244</v>
       </c>
-      <c r="D36" s="303" t="s">
+      <c r="D36" s="300" t="s">
         <v>243</v>
       </c>
-      <c r="E36" s="311" t="s">
+      <c r="E36" s="308" t="s">
         <v>245</v>
       </c>
-      <c r="F36" s="306"/>
-      <c r="G36" s="306"/>
-      <c r="H36" s="314"/>
-      <c r="I36" s="315">
+      <c r="F36" s="303"/>
+      <c r="G36" s="303"/>
+      <c r="H36" s="311"/>
+      <c r="I36" s="312">
         <f>I23+I26-I24-I25+I27-I28-I29-I30-I31-I32-I33-I34-I35</f>
         <v>0</v>
       </c>
-      <c r="J36" s="309"/>
-      <c r="N36" s="311"/>
-      <c r="O36" s="311"/>
-      <c r="P36" s="311"/>
-      <c r="Q36" s="311"/>
+      <c r="J36" s="306"/>
+      <c r="N36" s="308"/>
+      <c r="O36" s="308"/>
+      <c r="P36" s="308"/>
+      <c r="Q36" s="308"/>
     </row>
     <row r="37" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="325"/>
-      <c r="C37" s="197" t="s">
+      <c r="B37" s="349"/>
+      <c r="C37" s="194" t="s">
         <v>198</v>
       </c>
-      <c r="D37" s="213" t="s">
+      <c r="D37" s="210" t="s">
         <v>124</v>
       </c>
       <c r="E37" s="143" t="s">
@@ -4977,20 +5030,20 @@
       </c>
       <c r="F37" s="106"/>
       <c r="G37" s="106"/>
-      <c r="H37" s="215"/>
-      <c r="I37" s="230"/>
-      <c r="J37" s="231"/>
+      <c r="H37" s="212"/>
+      <c r="I37" s="227"/>
+      <c r="J37" s="228"/>
       <c r="N37" s="164"/>
       <c r="O37" s="164"/>
       <c r="P37" s="164"/>
       <c r="Q37" s="164"/>
     </row>
     <row r="38" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B38" s="325"/>
-      <c r="C38" s="196" t="s">
+      <c r="B38" s="349"/>
+      <c r="C38" s="193" t="s">
         <v>199</v>
       </c>
-      <c r="D38" s="213" t="s">
+      <c r="D38" s="210" t="s">
         <v>124</v>
       </c>
       <c r="E38" s="143" t="s">
@@ -4998,20 +5051,20 @@
       </c>
       <c r="F38" s="106"/>
       <c r="G38" s="106"/>
-      <c r="H38" s="215"/>
-      <c r="I38" s="232"/>
-      <c r="J38" s="231"/>
+      <c r="H38" s="212"/>
+      <c r="I38" s="229"/>
+      <c r="J38" s="228"/>
       <c r="N38" s="164"/>
       <c r="O38" s="164"/>
       <c r="P38" s="164"/>
       <c r="Q38" s="164"/>
     </row>
     <row r="39" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="325"/>
-      <c r="C39" s="196" t="s">
+      <c r="B39" s="349"/>
+      <c r="C39" s="193" t="s">
         <v>200</v>
       </c>
-      <c r="D39" s="213" t="s">
+      <c r="D39" s="210" t="s">
         <v>124</v>
       </c>
       <c r="E39" s="108" t="s">
@@ -5019,20 +5072,20 @@
       </c>
       <c r="F39" s="106"/>
       <c r="G39" s="106"/>
-      <c r="H39" s="215"/>
-      <c r="I39" s="233"/>
-      <c r="J39" s="231"/>
+      <c r="H39" s="212"/>
+      <c r="I39" s="230"/>
+      <c r="J39" s="228"/>
       <c r="N39" s="164"/>
       <c r="O39" s="164"/>
       <c r="P39" s="164"/>
       <c r="Q39" s="164"/>
     </row>
     <row r="40" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B40" s="325"/>
-      <c r="C40" s="196" t="s">
+      <c r="B40" s="349"/>
+      <c r="C40" s="193" t="s">
         <v>201</v>
       </c>
-      <c r="D40" s="213" t="s">
+      <c r="D40" s="210" t="s">
         <v>124</v>
       </c>
       <c r="E40" s="108" t="s">
@@ -5040,94 +5093,94 @@
       </c>
       <c r="F40" s="106"/>
       <c r="G40" s="106"/>
-      <c r="H40" s="215"/>
-      <c r="I40" s="232"/>
-      <c r="J40" s="231"/>
+      <c r="H40" s="212"/>
+      <c r="I40" s="229"/>
+      <c r="J40" s="228"/>
       <c r="N40" s="164"/>
       <c r="O40" s="164"/>
       <c r="P40" s="164"/>
       <c r="Q40" s="164"/>
     </row>
-    <row r="41" spans="2:17" s="310" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="325"/>
-      <c r="C41" s="302" t="s">
+    <row r="41" spans="2:17" s="307" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="349"/>
+      <c r="C41" s="299" t="s">
         <v>203</v>
       </c>
-      <c r="D41" s="303" t="s">
+      <c r="D41" s="300" t="s">
         <v>243</v>
       </c>
-      <c r="E41" s="304" t="s">
+      <c r="E41" s="301" t="s">
         <v>245</v>
       </c>
-      <c r="F41" s="305" t="s">
+      <c r="F41" s="302" t="s">
         <v>301</v>
       </c>
-      <c r="G41" s="306"/>
-      <c r="H41" s="307"/>
-      <c r="I41" s="308">
+      <c r="G41" s="303"/>
+      <c r="H41" s="304"/>
+      <c r="I41" s="305">
         <f>F200</f>
         <v>0</v>
       </c>
-      <c r="J41" s="309"/>
-      <c r="N41" s="311"/>
-      <c r="O41" s="311"/>
-      <c r="P41" s="311"/>
-      <c r="Q41" s="311"/>
-    </row>
-    <row r="42" spans="2:17" s="310" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="325"/>
-      <c r="C42" s="302" t="s">
+      <c r="J41" s="306"/>
+      <c r="N41" s="308"/>
+      <c r="O41" s="308"/>
+      <c r="P41" s="308"/>
+      <c r="Q41" s="308"/>
+    </row>
+    <row r="42" spans="2:17" s="307" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="349"/>
+      <c r="C42" s="299" t="s">
         <v>33</v>
       </c>
-      <c r="D42" s="303" t="s">
+      <c r="D42" s="300" t="s">
         <v>243</v>
       </c>
-      <c r="E42" s="304" t="s">
+      <c r="E42" s="301" t="s">
         <v>245</v>
       </c>
-      <c r="F42" s="306"/>
-      <c r="G42" s="306"/>
-      <c r="H42" s="307"/>
-      <c r="I42" s="312">
+      <c r="F42" s="303"/>
+      <c r="G42" s="303"/>
+      <c r="H42" s="304"/>
+      <c r="I42" s="309">
         <f>I29</f>
         <v>0</v>
       </c>
-      <c r="J42" s="309"/>
-      <c r="N42" s="311"/>
-      <c r="O42" s="311"/>
-      <c r="P42" s="311"/>
-      <c r="Q42" s="311"/>
-    </row>
-    <row r="43" spans="2:17" s="310" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="325"/>
-      <c r="C43" s="302" t="s">
+      <c r="J42" s="306"/>
+      <c r="N42" s="308"/>
+      <c r="O42" s="308"/>
+      <c r="P42" s="308"/>
+      <c r="Q42" s="308"/>
+    </row>
+    <row r="43" spans="2:17" s="307" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="349"/>
+      <c r="C43" s="299" t="s">
         <v>202</v>
       </c>
-      <c r="D43" s="303" t="s">
+      <c r="D43" s="300" t="s">
         <v>243</v>
       </c>
-      <c r="E43" s="304" t="s">
+      <c r="E43" s="301" t="s">
         <v>245</v>
       </c>
-      <c r="F43" s="306"/>
-      <c r="G43" s="306"/>
-      <c r="H43" s="307"/>
-      <c r="I43" s="312">
+      <c r="F43" s="303"/>
+      <c r="G43" s="303"/>
+      <c r="H43" s="304"/>
+      <c r="I43" s="309">
         <f>I42+I41</f>
         <v>0</v>
       </c>
-      <c r="J43" s="309"/>
-      <c r="N43" s="311"/>
-      <c r="O43" s="311"/>
-      <c r="P43" s="311"/>
-      <c r="Q43" s="311"/>
+      <c r="J43" s="306"/>
+      <c r="N43" s="308"/>
+      <c r="O43" s="308"/>
+      <c r="P43" s="308"/>
+      <c r="Q43" s="308"/>
     </row>
     <row r="44" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="325"/>
-      <c r="C44" s="196" t="s">
+      <c r="B44" s="349"/>
+      <c r="C44" s="193" t="s">
         <v>204</v>
       </c>
-      <c r="D44" s="213" t="s">
+      <c r="D44" s="210" t="s">
         <v>124</v>
       </c>
       <c r="E44" s="108" t="s">
@@ -5135,20 +5188,20 @@
       </c>
       <c r="F44" s="106"/>
       <c r="G44" s="106"/>
-      <c r="H44" s="215"/>
-      <c r="I44" s="232"/>
-      <c r="J44" s="231"/>
+      <c r="H44" s="212"/>
+      <c r="I44" s="229"/>
+      <c r="J44" s="228"/>
       <c r="N44" s="164"/>
       <c r="O44" s="164"/>
       <c r="P44" s="164"/>
       <c r="Q44" s="164"/>
     </row>
     <row r="45" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B45" s="325"/>
-      <c r="C45" s="196" t="s">
+      <c r="B45" s="349"/>
+      <c r="C45" s="193" t="s">
         <v>4</v>
       </c>
-      <c r="D45" s="213" t="s">
+      <c r="D45" s="210" t="s">
         <v>124</v>
       </c>
       <c r="E45" s="143" t="s">
@@ -5156,20 +5209,20 @@
       </c>
       <c r="F45" s="106"/>
       <c r="G45" s="106"/>
-      <c r="H45" s="215"/>
-      <c r="I45" s="232"/>
-      <c r="J45" s="231"/>
+      <c r="H45" s="212"/>
+      <c r="I45" s="229"/>
+      <c r="J45" s="228"/>
       <c r="N45" s="164"/>
       <c r="O45" s="164"/>
       <c r="P45" s="164"/>
       <c r="Q45" s="164"/>
     </row>
     <row r="46" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B46" s="325"/>
-      <c r="C46" s="196" t="s">
+      <c r="B46" s="349"/>
+      <c r="C46" s="193" t="s">
         <v>65</v>
       </c>
-      <c r="D46" s="213" t="s">
+      <c r="D46" s="210" t="s">
         <v>124</v>
       </c>
       <c r="E46" s="143" t="s">
@@ -5177,20 +5230,20 @@
       </c>
       <c r="F46" s="106"/>
       <c r="G46" s="106"/>
-      <c r="H46" s="215"/>
-      <c r="I46" s="232"/>
-      <c r="J46" s="231"/>
+      <c r="H46" s="212"/>
+      <c r="I46" s="229"/>
+      <c r="J46" s="228"/>
       <c r="N46" s="164"/>
       <c r="O46" s="164"/>
       <c r="P46" s="164"/>
       <c r="Q46" s="164"/>
     </row>
     <row r="47" spans="2:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B47" s="325"/>
-      <c r="C47" s="198" t="s">
+      <c r="B47" s="349"/>
+      <c r="C47" s="195" t="s">
         <v>205</v>
       </c>
-      <c r="D47" s="214" t="s">
+      <c r="D47" s="211" t="s">
         <v>124</v>
       </c>
       <c r="E47" s="143" t="s">
@@ -5198,16 +5251,16 @@
       </c>
       <c r="F47" s="158"/>
       <c r="G47" s="158"/>
-      <c r="H47" s="215"/>
-      <c r="I47" s="235"/>
-      <c r="J47" s="231"/>
+      <c r="H47" s="212"/>
+      <c r="I47" s="232"/>
+      <c r="J47" s="228"/>
       <c r="N47" s="164"/>
       <c r="O47" s="164"/>
       <c r="P47" s="164"/>
       <c r="Q47" s="164"/>
     </row>
-    <row r="48" spans="2:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="211"/>
+    <row r="48" spans="2:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B48" s="208"/>
       <c r="C48" s="160"/>
       <c r="D48" s="161"/>
       <c r="E48" s="161"/>
@@ -5221,25 +5274,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="332" t="s">
+    <row r="49" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="335" t="s">
         <v>247</v>
       </c>
-      <c r="C49" s="205" t="s">
+      <c r="C49" s="202" t="s">
         <v>241</v>
       </c>
-      <c r="D49" s="334" t="s">
+      <c r="D49" s="337" t="s">
         <v>246</v>
       </c>
-      <c r="E49" s="206"/>
-      <c r="F49" s="207"/>
-      <c r="G49" s="207"/>
-      <c r="H49" s="208"/>
-      <c r="I49" s="209" t="e">
+      <c r="E49" s="203"/>
+      <c r="F49" s="204"/>
+      <c r="G49" s="204"/>
+      <c r="H49" s="205"/>
+      <c r="I49" s="206" t="e">
         <f>100/I16/100</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J49" s="210" t="s">
+      <c r="J49" s="207" t="s">
         <v>108</v>
       </c>
       <c r="L49" s="90"/>
@@ -5249,17 +5302,17 @@
       <c r="P49" s="90"/>
       <c r="Q49" s="90"/>
     </row>
-    <row r="50" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="333"/>
+    <row r="50" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="336"/>
       <c r="C50" s="170" t="s">
         <v>99</v>
       </c>
-      <c r="D50" s="335"/>
+      <c r="D50" s="338"/>
       <c r="E50" s="175"/>
       <c r="F50" s="176"/>
       <c r="G50" s="176"/>
       <c r="H50" s="177"/>
-      <c r="I50" s="239">
+      <c r="I50" s="236">
         <v>1.05</v>
       </c>
       <c r="J50" s="178" t="s">
@@ -5272,17 +5325,17 @@
       <c r="P50" s="90"/>
       <c r="Q50" s="90"/>
     </row>
-    <row r="51" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B51" s="333"/>
+    <row r="51" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="336"/>
       <c r="C51" s="170" t="s">
         <v>242</v>
       </c>
-      <c r="D51" s="335"/>
+      <c r="D51" s="338"/>
       <c r="E51" s="175"/>
       <c r="F51" s="176"/>
       <c r="G51" s="176"/>
       <c r="H51" s="177"/>
-      <c r="I51" s="239">
+      <c r="I51" s="236">
         <v>1.0049999999999999</v>
       </c>
       <c r="J51" s="178" t="s">
@@ -5295,17 +5348,17 @@
       <c r="P51" s="90"/>
       <c r="Q51" s="90"/>
     </row>
-    <row r="52" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="333"/>
+    <row r="52" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="336"/>
       <c r="C52" s="170" t="s">
         <v>161</v>
       </c>
-      <c r="D52" s="335"/>
+      <c r="D52" s="338"/>
       <c r="E52" s="175"/>
       <c r="F52" s="176"/>
       <c r="G52" s="176"/>
       <c r="H52" s="177"/>
-      <c r="I52" s="239">
+      <c r="I52" s="236">
         <v>1.05</v>
       </c>
       <c r="J52" s="178" t="s">
@@ -5318,44 +5371,44 @@
       <c r="P52" s="90"/>
       <c r="Q52" s="90"/>
     </row>
-    <row r="53" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B53" s="333"/>
+    <row r="53" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="336"/>
       <c r="C53" s="170" t="s">
         <v>103</v>
       </c>
-      <c r="D53" s="335"/>
+      <c r="D53" s="338"/>
       <c r="E53" s="175"/>
       <c r="F53" s="176"/>
       <c r="G53" s="176"/>
       <c r="H53" s="177"/>
-      <c r="I53" s="239">
+      <c r="I53" s="236">
         <v>1.3</v>
       </c>
       <c r="J53" s="178" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="54" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="333"/>
+    <row r="54" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="336"/>
       <c r="C54" s="170" t="s">
         <v>97</v>
       </c>
-      <c r="D54" s="335"/>
+      <c r="D54" s="338"/>
       <c r="E54" s="175"/>
       <c r="F54" s="176"/>
       <c r="G54" s="176"/>
       <c r="H54" s="177"/>
-      <c r="I54" s="239">
+      <c r="I54" s="236">
         <v>1.01</v>
       </c>
       <c r="J54" s="178" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="55" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="333"/>
+    <row r="55" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="336"/>
       <c r="C55" s="128"/>
-      <c r="D55" s="335"/>
+      <c r="D55" s="338"/>
       <c r="E55" s="129"/>
       <c r="F55" s="114"/>
       <c r="G55" s="114"/>
@@ -5363,12 +5416,12 @@
       <c r="I55" s="114"/>
       <c r="J55" s="118"/>
     </row>
-    <row r="56" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="333"/>
+    <row r="56" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B56" s="336"/>
       <c r="C56" s="170" t="s">
         <v>134</v>
       </c>
-      <c r="D56" s="335"/>
+      <c r="D56" s="338"/>
       <c r="E56" s="175"/>
       <c r="F56" s="176"/>
       <c r="G56" s="176"/>
@@ -5379,12 +5432,12 @@
       </c>
       <c r="J56" s="180"/>
     </row>
-    <row r="57" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="333"/>
+    <row r="57" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B57" s="336"/>
       <c r="C57" s="170" t="s">
         <v>174</v>
       </c>
-      <c r="D57" s="335"/>
+      <c r="D57" s="338"/>
       <c r="E57" s="175"/>
       <c r="F57" s="176"/>
       <c r="G57" s="176"/>
@@ -5395,12 +5448,12 @@
       </c>
       <c r="J57" s="180"/>
     </row>
-    <row r="58" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="333"/>
+    <row r="58" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B58" s="336"/>
       <c r="C58" s="170" t="s">
         <v>177</v>
       </c>
-      <c r="D58" s="335"/>
+      <c r="D58" s="338"/>
       <c r="E58" s="175"/>
       <c r="F58" s="176"/>
       <c r="G58" s="176"/>
@@ -5411,12 +5464,12 @@
       </c>
       <c r="J58" s="180"/>
     </row>
-    <row r="59" spans="2:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="333"/>
+    <row r="59" spans="2:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B59" s="336"/>
       <c r="C59" s="170" t="s">
         <v>133</v>
       </c>
-      <c r="D59" s="335"/>
+      <c r="D59" s="338"/>
       <c r="E59" s="175"/>
       <c r="F59" s="176"/>
       <c r="G59" s="176"/>
@@ -5427,10 +5480,10 @@
       </c>
       <c r="J59" s="180"/>
     </row>
-    <row r="60" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="333"/>
+    <row r="60" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B60" s="336"/>
       <c r="C60" s="128"/>
-      <c r="D60" s="335"/>
+      <c r="D60" s="338"/>
       <c r="E60" s="129"/>
       <c r="F60" s="114"/>
       <c r="G60" s="114"/>
@@ -5439,12 +5492,12 @@
       <c r="J60" s="118"/>
       <c r="R60" s="81"/>
     </row>
-    <row r="61" spans="2:18" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="333"/>
+    <row r="61" spans="2:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B61" s="336"/>
       <c r="C61" s="170" t="s">
         <v>138</v>
       </c>
-      <c r="D61" s="335"/>
+      <c r="D61" s="338"/>
       <c r="E61" s="181"/>
       <c r="F61" s="182"/>
       <c r="G61" s="182"/>
@@ -5456,11 +5509,11 @@
       <c r="J61" s="180"/>
     </row>
     <row r="62" spans="2:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B62" s="333"/>
+      <c r="B62" s="336"/>
       <c r="C62" s="170" t="s">
         <v>175</v>
       </c>
-      <c r="D62" s="335"/>
+      <c r="D62" s="338"/>
       <c r="E62" s="181"/>
       <c r="F62" s="182"/>
       <c r="G62" s="182"/>
@@ -5471,12 +5524,12 @@
       </c>
       <c r="J62" s="180"/>
     </row>
-    <row r="63" spans="2:18" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B63" s="333"/>
+    <row r="63" spans="2:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B63" s="336"/>
       <c r="C63" s="170" t="s">
         <v>142</v>
       </c>
-      <c r="D63" s="335"/>
+      <c r="D63" s="338"/>
       <c r="E63" s="181"/>
       <c r="F63" s="182"/>
       <c r="G63" s="182"/>
@@ -5487,10 +5540,10 @@
       </c>
       <c r="J63" s="180"/>
     </row>
-    <row r="64" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="333"/>
+    <row r="64" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B64" s="336"/>
       <c r="C64" s="128"/>
-      <c r="D64" s="335"/>
+      <c r="D64" s="338"/>
       <c r="E64" s="130"/>
       <c r="F64" s="116"/>
       <c r="G64" s="116"/>
@@ -5498,12 +5551,12 @@
       <c r="I64" s="116"/>
       <c r="J64" s="119"/>
     </row>
-    <row r="65" spans="2:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B65" s="333"/>
+    <row r="65" spans="2:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B65" s="336"/>
       <c r="C65" s="170" t="s">
         <v>176</v>
       </c>
-      <c r="D65" s="335"/>
+      <c r="D65" s="338"/>
       <c r="E65" s="181"/>
       <c r="F65" s="182"/>
       <c r="G65" s="182"/>
@@ -5516,12 +5569,12 @@
       <c r="P65" s="165"/>
       <c r="Q65" s="165"/>
     </row>
-    <row r="66" spans="2:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B66" s="333"/>
+    <row r="66" spans="2:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B66" s="336"/>
       <c r="C66" s="170" t="s">
         <v>143</v>
       </c>
-      <c r="D66" s="335"/>
+      <c r="D66" s="338"/>
       <c r="E66" s="181"/>
       <c r="F66" s="182"/>
       <c r="G66" s="182"/>
@@ -5534,11 +5587,11 @@
       <c r="Q66" s="166"/>
     </row>
     <row r="67" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B67" s="333"/>
+      <c r="B67" s="336"/>
       <c r="C67" s="171" t="s">
         <v>135</v>
       </c>
-      <c r="D67" s="335"/>
+      <c r="D67" s="338"/>
       <c r="E67" s="184"/>
       <c r="F67" s="185"/>
       <c r="G67" s="185"/>
@@ -5551,12 +5604,12 @@
       <c r="P67" s="127"/>
       <c r="Q67" s="90"/>
     </row>
-    <row r="68" spans="2:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B68" s="333"/>
+    <row r="68" spans="2:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B68" s="336"/>
       <c r="C68" s="113" t="s">
         <v>240</v>
       </c>
-      <c r="D68" s="335"/>
+      <c r="D68" s="338"/>
       <c r="E68" s="114"/>
       <c r="F68" s="114"/>
       <c r="G68" s="114"/>
@@ -5568,182 +5621,182 @@
       <c r="P68" s="90"/>
       <c r="Q68" s="90"/>
     </row>
-    <row r="69" spans="2:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B69" s="333"/>
+    <row r="69" spans="2:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B69" s="336"/>
       <c r="C69" s="172" t="s">
         <v>102</v>
       </c>
-      <c r="D69" s="335"/>
+      <c r="D69" s="338"/>
       <c r="E69" s="182"/>
       <c r="F69" s="182"/>
       <c r="G69" s="182"/>
       <c r="H69" s="177"/>
-      <c r="I69" s="239">
+      <c r="I69" s="236">
         <v>0.15</v>
       </c>
       <c r="J69" s="180"/>
       <c r="P69" s="90"/>
       <c r="Q69" s="90"/>
     </row>
-    <row r="70" spans="2:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="333"/>
+    <row r="70" spans="2:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B70" s="336"/>
       <c r="C70" s="172" t="s">
         <v>170</v>
       </c>
-      <c r="D70" s="335"/>
+      <c r="D70" s="338"/>
       <c r="E70" s="182"/>
       <c r="F70" s="182"/>
       <c r="G70" s="182"/>
       <c r="H70" s="177"/>
-      <c r="I70" s="239">
+      <c r="I70" s="236">
         <v>0.15</v>
       </c>
       <c r="J70" s="180"/>
       <c r="P70" s="90"/>
       <c r="Q70" s="90"/>
     </row>
-    <row r="71" spans="2:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B71" s="333"/>
+    <row r="71" spans="2:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B71" s="336"/>
       <c r="C71" s="172" t="s">
         <v>283</v>
       </c>
-      <c r="D71" s="335"/>
+      <c r="D71" s="338"/>
       <c r="E71" s="182"/>
       <c r="F71" s="182"/>
       <c r="G71" s="182"/>
       <c r="H71" s="177"/>
-      <c r="I71" s="239">
+      <c r="I71" s="236">
         <v>0.1</v>
       </c>
       <c r="J71" s="180"/>
     </row>
-    <row r="72" spans="2:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B72" s="333"/>
+    <row r="72" spans="2:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B72" s="336"/>
       <c r="C72" s="172" t="s">
         <v>284</v>
       </c>
-      <c r="D72" s="335"/>
+      <c r="D72" s="338"/>
       <c r="E72" s="182"/>
       <c r="F72" s="182"/>
       <c r="G72" s="182"/>
       <c r="H72" s="177"/>
-      <c r="I72" s="239">
+      <c r="I72" s="236">
         <v>0</v>
       </c>
       <c r="J72" s="180"/>
     </row>
-    <row r="73" spans="2:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B73" s="333"/>
+    <row r="73" spans="2:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B73" s="336"/>
       <c r="C73" s="172" t="s">
         <v>101</v>
       </c>
-      <c r="D73" s="335"/>
+      <c r="D73" s="338"/>
       <c r="E73" s="182"/>
       <c r="F73" s="182"/>
       <c r="G73" s="182"/>
       <c r="H73" s="177"/>
-      <c r="I73" s="239">
+      <c r="I73" s="236">
         <v>0.1</v>
       </c>
       <c r="J73" s="180"/>
     </row>
-    <row r="74" spans="2:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B74" s="333"/>
+    <row r="74" spans="2:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B74" s="336"/>
       <c r="C74" s="172" t="s">
         <v>285</v>
       </c>
-      <c r="D74" s="335"/>
+      <c r="D74" s="338"/>
       <c r="E74" s="182"/>
       <c r="F74" s="182"/>
       <c r="G74" s="182"/>
       <c r="H74" s="177"/>
-      <c r="I74" s="239">
+      <c r="I74" s="236">
         <v>0.15</v>
       </c>
       <c r="J74" s="180"/>
     </row>
-    <row r="75" spans="2:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B75" s="333"/>
+    <row r="75" spans="2:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B75" s="336"/>
       <c r="C75" s="172" t="s">
         <v>299</v>
       </c>
-      <c r="D75" s="335"/>
+      <c r="D75" s="338"/>
       <c r="E75" s="182"/>
       <c r="F75" s="182"/>
       <c r="G75" s="182"/>
       <c r="H75" s="177"/>
-      <c r="I75" s="239">
+      <c r="I75" s="236">
         <v>0.15</v>
       </c>
       <c r="J75" s="180"/>
     </row>
-    <row r="76" spans="2:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B76" s="333"/>
+    <row r="76" spans="2:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B76" s="336"/>
       <c r="C76" s="172" t="s">
         <v>111</v>
       </c>
-      <c r="D76" s="335"/>
+      <c r="D76" s="338"/>
       <c r="E76" s="182"/>
       <c r="F76" s="182"/>
       <c r="G76" s="182"/>
       <c r="H76" s="177"/>
-      <c r="I76" s="239">
+      <c r="I76" s="236">
         <v>0.15</v>
       </c>
       <c r="J76" s="180"/>
     </row>
-    <row r="77" spans="2:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B77" s="333"/>
+    <row r="77" spans="2:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B77" s="336"/>
       <c r="C77" s="172" t="s">
         <v>289</v>
       </c>
-      <c r="D77" s="335"/>
+      <c r="D77" s="338"/>
       <c r="E77" s="182"/>
       <c r="F77" s="182"/>
       <c r="G77" s="182"/>
       <c r="H77" s="177"/>
-      <c r="I77" s="239">
+      <c r="I77" s="236">
         <v>0</v>
       </c>
       <c r="J77" s="180"/>
     </row>
-    <row r="78" spans="2:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B78" s="333"/>
+    <row r="78" spans="2:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B78" s="336"/>
       <c r="C78" s="173" t="s">
         <v>290</v>
       </c>
-      <c r="D78" s="335"/>
+      <c r="D78" s="338"/>
       <c r="E78" s="182"/>
       <c r="F78" s="182"/>
       <c r="G78" s="182"/>
       <c r="H78" s="177"/>
-      <c r="I78" s="239">
+      <c r="I78" s="236">
         <v>0</v>
       </c>
       <c r="J78" s="180"/>
     </row>
-    <row r="79" spans="2:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B79" s="333"/>
+    <row r="79" spans="2:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B79" s="336"/>
       <c r="C79" s="173" t="s">
         <v>110</v>
       </c>
-      <c r="D79" s="335"/>
+      <c r="D79" s="338"/>
       <c r="E79" s="182"/>
       <c r="F79" s="182"/>
       <c r="G79" s="182"/>
       <c r="H79" s="177"/>
-      <c r="I79" s="239">
+      <c r="I79" s="236">
         <v>0.1</v>
       </c>
       <c r="J79" s="180"/>
       <c r="P79" s="101"/>
     </row>
-    <row r="80" spans="2:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B80" s="333"/>
+    <row r="80" spans="2:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B80" s="336"/>
       <c r="C80" s="113" t="s">
         <v>206</v>
       </c>
-      <c r="D80" s="335"/>
+      <c r="D80" s="338"/>
       <c r="E80" s="114"/>
       <c r="F80" s="114"/>
       <c r="G80" s="114"/>
@@ -5751,13 +5804,13 @@
       <c r="I80" s="114"/>
       <c r="J80" s="115"/>
     </row>
-    <row r="81" spans="2:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B81" s="333"/>
+    <row r="81" spans="2:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B81" s="336"/>
       <c r="C81" s="174">
         <f>I18</f>
         <v>0</v>
       </c>
-      <c r="D81" s="335"/>
+      <c r="D81" s="338"/>
       <c r="E81" s="182"/>
       <c r="F81" s="182"/>
       <c r="G81" s="182"/>
@@ -5768,53 +5821,53 @@
       <c r="J81" s="177"/>
       <c r="O81" s="90"/>
     </row>
-    <row r="82" spans="2:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B82" s="333"/>
+    <row r="82" spans="2:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B82" s="336"/>
       <c r="C82" s="174">
         <f>I19</f>
         <v>0</v>
       </c>
-      <c r="D82" s="335"/>
+      <c r="D82" s="338"/>
       <c r="E82" s="182"/>
       <c r="F82" s="182"/>
       <c r="G82" s="182"/>
       <c r="H82" s="177"/>
-      <c r="I82" s="239">
+      <c r="I82" s="236">
         <v>0.05</v>
       </c>
       <c r="J82" s="177"/>
       <c r="O82" s="90"/>
     </row>
-    <row r="83" spans="2:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B83" s="333"/>
+    <row r="83" spans="2:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B83" s="336"/>
       <c r="C83" s="174">
         <f>I20</f>
         <v>0</v>
       </c>
-      <c r="D83" s="335"/>
+      <c r="D83" s="338"/>
       <c r="E83" s="182"/>
       <c r="F83" s="182"/>
       <c r="G83" s="182"/>
       <c r="H83" s="177"/>
-      <c r="I83" s="239">
+      <c r="I83" s="236">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="J83" s="177"/>
       <c r="O83" s="90"/>
       <c r="P83" s="167"/>
     </row>
-    <row r="84" spans="2:20" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B84" s="333"/>
+    <row r="84" spans="2:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B84" s="336"/>
       <c r="C84" s="174">
         <f>I21</f>
         <v>0</v>
       </c>
-      <c r="D84" s="335"/>
+      <c r="D84" s="338"/>
       <c r="E84" s="182"/>
       <c r="F84" s="182"/>
       <c r="G84" s="182"/>
       <c r="H84" s="177"/>
-      <c r="I84" s="239">
+      <c r="I84" s="236">
         <v>0.1</v>
       </c>
       <c r="J84" s="177"/>
@@ -5823,12 +5876,12 @@
       <c r="S84" s="38"/>
       <c r="T84" s="38"/>
     </row>
-    <row r="85" spans="2:20" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B85" s="333"/>
+    <row r="85" spans="2:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B85" s="336"/>
       <c r="C85" s="113" t="s">
         <v>207</v>
       </c>
-      <c r="D85" s="335"/>
+      <c r="D85" s="338"/>
       <c r="E85" s="114"/>
       <c r="F85" s="114"/>
       <c r="G85" s="114"/>
@@ -5839,18 +5892,18 @@
       <c r="S85" s="37"/>
       <c r="T85" s="37"/>
     </row>
-    <row r="86" spans="2:20" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B86" s="333"/>
+    <row r="86" spans="2:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B86" s="336"/>
       <c r="C86" s="174">
         <f>C81</f>
         <v>0</v>
       </c>
-      <c r="D86" s="335"/>
+      <c r="D86" s="338"/>
       <c r="E86" s="182"/>
       <c r="F86" s="182"/>
       <c r="G86" s="182"/>
       <c r="H86" s="177"/>
-      <c r="I86" s="239" t="e">
+      <c r="I86" s="236" t="e">
         <f>wp!C21/wp!C10</f>
         <v>#DIV/0!</v>
       </c>
@@ -5860,62 +5913,62 @@
       <c r="T86" s="38"/>
     </row>
     <row r="87" spans="2:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B87" s="333"/>
+      <c r="B87" s="336"/>
       <c r="C87" s="174">
         <f>C82</f>
         <v>0</v>
       </c>
-      <c r="D87" s="335"/>
+      <c r="D87" s="338"/>
       <c r="E87" s="182"/>
       <c r="F87" s="182"/>
       <c r="G87" s="182"/>
       <c r="H87" s="177"/>
-      <c r="I87" s="239" t="e">
+      <c r="I87" s="236" t="e">
         <f>I86*100.5/100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J87" s="177"/>
     </row>
     <row r="88" spans="2:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B88" s="333"/>
+      <c r="B88" s="336"/>
       <c r="C88" s="174">
         <f>C83</f>
         <v>0</v>
       </c>
-      <c r="D88" s="335"/>
+      <c r="D88" s="338"/>
       <c r="E88" s="177"/>
       <c r="F88" s="177"/>
       <c r="G88" s="177"/>
       <c r="H88" s="177"/>
-      <c r="I88" s="239" t="e">
+      <c r="I88" s="236" t="e">
         <f>I87*100.5/100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J88" s="177"/>
     </row>
     <row r="89" spans="2:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B89" s="333"/>
+      <c r="B89" s="336"/>
       <c r="C89" s="174">
         <f>C84</f>
         <v>0</v>
       </c>
-      <c r="D89" s="335"/>
+      <c r="D89" s="338"/>
       <c r="E89" s="182"/>
       <c r="F89" s="182"/>
       <c r="G89" s="182"/>
       <c r="H89" s="177"/>
-      <c r="I89" s="239" t="e">
+      <c r="I89" s="236" t="e">
         <f>I88*100.5/100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J89" s="177"/>
     </row>
-    <row r="90" spans="2:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B90" s="333"/>
+    <row r="90" spans="2:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B90" s="336"/>
       <c r="C90" s="113" t="s">
         <v>208</v>
       </c>
-      <c r="D90" s="335"/>
+      <c r="D90" s="338"/>
       <c r="E90" s="114"/>
       <c r="F90" s="114"/>
       <c r="G90" s="114"/>
@@ -5924,12 +5977,12 @@
       <c r="J90" s="115"/>
     </row>
     <row r="91" spans="2:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B91" s="333"/>
+      <c r="B91" s="336"/>
       <c r="C91" s="174">
         <f>C86</f>
         <v>0</v>
       </c>
-      <c r="D91" s="335"/>
+      <c r="D91" s="338"/>
       <c r="E91" s="182"/>
       <c r="F91" s="182"/>
       <c r="G91" s="182"/>
@@ -5940,12 +5993,12 @@
       <c r="J91" s="177"/>
     </row>
     <row r="92" spans="2:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B92" s="333"/>
+      <c r="B92" s="336"/>
       <c r="C92" s="174">
         <f>C87</f>
         <v>0</v>
       </c>
-      <c r="D92" s="335"/>
+      <c r="D92" s="338"/>
       <c r="E92" s="182"/>
       <c r="F92" s="182"/>
       <c r="G92" s="182"/>
@@ -5956,12 +6009,12 @@
       <c r="J92" s="177"/>
     </row>
     <row r="93" spans="2:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B93" s="333"/>
+      <c r="B93" s="336"/>
       <c r="C93" s="174">
         <f>C88</f>
         <v>0</v>
       </c>
-      <c r="D93" s="335"/>
+      <c r="D93" s="338"/>
       <c r="E93" s="182"/>
       <c r="F93" s="182"/>
       <c r="G93" s="182"/>
@@ -5972,12 +6025,12 @@
       <c r="J93" s="177"/>
     </row>
     <row r="94" spans="2:20" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B94" s="333"/>
+      <c r="B94" s="336"/>
       <c r="C94" s="174">
         <f>C89</f>
         <v>0</v>
       </c>
-      <c r="D94" s="336"/>
+      <c r="D94" s="339"/>
       <c r="E94" s="182"/>
       <c r="F94" s="182"/>
       <c r="G94" s="182"/>
@@ -5987,8 +6040,8 @@
       </c>
       <c r="J94" s="177"/>
     </row>
-    <row r="97" spans="2:10" ht="23.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B97" s="260" t="s">
+    <row r="97" spans="2:10" ht="23.4" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B97" s="257" t="s">
         <v>277</v>
       </c>
       <c r="C97"/>
@@ -5996,1005 +6049,1029 @@
       <c r="E97"/>
       <c r="F97"/>
     </row>
-    <row r="98" spans="2:10" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="261" t="s">
+    <row r="98" spans="2:10" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B98" s="258" t="s">
         <v>278</v>
       </c>
-      <c r="C98" s="262" t="s">
+      <c r="C98" s="259" t="s">
         <v>279</v>
       </c>
-      <c r="D98" s="263" t="s">
+      <c r="D98" s="260" t="s">
         <v>280</v>
       </c>
-      <c r="E98" s="264" t="s">
+      <c r="E98" s="261" t="s">
         <v>281</v>
       </c>
-      <c r="F98" s="264" t="s">
+      <c r="F98" s="261" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B99" s="326" t="s">
+    <row r="99" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B99" s="321" t="s">
         <v>102</v>
       </c>
-      <c r="C99" s="265">
+      <c r="C99" s="262">
         <v>1</v>
       </c>
-      <c r="D99" s="266"/>
-      <c r="E99" s="267"/>
-      <c r="F99" s="329">
+      <c r="D99" s="263"/>
+      <c r="E99" s="264"/>
+      <c r="F99" s="334">
         <f>SUM(E99:E108)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B100" s="327"/>
-      <c r="C100" s="268">
+    <row r="100" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B100" s="316"/>
+      <c r="C100" s="265">
         <v>2</v>
       </c>
-      <c r="D100" s="240"/>
-      <c r="E100" s="269"/>
-      <c r="F100" s="330"/>
-    </row>
-    <row r="101" spans="2:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B101" s="327"/>
-      <c r="C101" s="268">
+      <c r="D100" s="237"/>
+      <c r="E100" s="266"/>
+      <c r="F100" s="326"/>
+    </row>
+    <row r="101" spans="2:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B101" s="316"/>
+      <c r="C101" s="265">
         <v>3</v>
       </c>
-      <c r="D101" s="240"/>
-      <c r="E101" s="269"/>
-      <c r="F101" s="330"/>
-    </row>
-    <row r="102" spans="2:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B102" s="327"/>
-      <c r="C102" s="268">
+      <c r="D101" s="237"/>
+      <c r="E101" s="266"/>
+      <c r="F101" s="326"/>
+    </row>
+    <row r="102" spans="2:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B102" s="316"/>
+      <c r="C102" s="265">
         <v>4</v>
       </c>
-      <c r="D102" s="240"/>
-      <c r="E102" s="269"/>
-      <c r="F102" s="330"/>
+      <c r="D102" s="237"/>
+      <c r="E102" s="266"/>
+      <c r="F102" s="326"/>
       <c r="G102" s="102"/>
       <c r="H102" s="88"/>
       <c r="I102" s="102"/>
       <c r="J102" s="88"/>
     </row>
-    <row r="103" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B103" s="327"/>
-      <c r="C103" s="268">
+    <row r="103" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B103" s="316"/>
+      <c r="C103" s="265">
         <v>5</v>
       </c>
-      <c r="D103" s="240"/>
-      <c r="E103" s="269"/>
-      <c r="F103" s="330"/>
-    </row>
-    <row r="104" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B104" s="327"/>
-      <c r="C104" s="268">
+      <c r="D103" s="237"/>
+      <c r="E103" s="266"/>
+      <c r="F103" s="326"/>
+    </row>
+    <row r="104" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B104" s="316"/>
+      <c r="C104" s="265">
         <v>6</v>
       </c>
-      <c r="D104" s="240"/>
-      <c r="E104" s="269"/>
-      <c r="F104" s="330"/>
-    </row>
-    <row r="105" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B105" s="327"/>
-      <c r="C105" s="268">
+      <c r="D104" s="237"/>
+      <c r="E104" s="266"/>
+      <c r="F104" s="326"/>
+    </row>
+    <row r="105" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B105" s="316"/>
+      <c r="C105" s="265">
         <v>7</v>
       </c>
-      <c r="D105" s="240"/>
-      <c r="E105" s="269"/>
-      <c r="F105" s="330"/>
-    </row>
-    <row r="106" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B106" s="327"/>
-      <c r="C106" s="268">
+      <c r="D105" s="237"/>
+      <c r="E105" s="266"/>
+      <c r="F105" s="326"/>
+    </row>
+    <row r="106" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B106" s="316"/>
+      <c r="C106" s="265">
         <v>8</v>
       </c>
-      <c r="D106" s="240"/>
-      <c r="E106" s="269"/>
-      <c r="F106" s="330"/>
-    </row>
-    <row r="107" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B107" s="327"/>
-      <c r="C107" s="268">
+      <c r="D106" s="237"/>
+      <c r="E106" s="266"/>
+      <c r="F106" s="326"/>
+    </row>
+    <row r="107" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B107" s="316"/>
+      <c r="C107" s="265">
         <v>9</v>
       </c>
-      <c r="D107" s="240"/>
-      <c r="E107" s="269"/>
-      <c r="F107" s="330"/>
-    </row>
-    <row r="108" spans="2:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B108" s="328"/>
-      <c r="C108" s="270">
+      <c r="D107" s="237"/>
+      <c r="E107" s="266"/>
+      <c r="F107" s="326"/>
+    </row>
+    <row r="108" spans="2:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B108" s="317"/>
+      <c r="C108" s="267">
         <v>10</v>
       </c>
-      <c r="D108" s="271"/>
-      <c r="E108" s="272"/>
-      <c r="F108" s="331"/>
-    </row>
-    <row r="109" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B109" s="326" t="s">
+      <c r="D108" s="268"/>
+      <c r="E108" s="269"/>
+      <c r="F108" s="327"/>
+    </row>
+    <row r="109" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B109" s="321" t="s">
         <v>170</v>
       </c>
-      <c r="C109" s="265">
+      <c r="C109" s="262">
         <v>1</v>
       </c>
-      <c r="D109" s="266"/>
-      <c r="E109" s="273"/>
-      <c r="F109" s="337">
+      <c r="D109" s="263"/>
+      <c r="E109" s="270"/>
+      <c r="F109" s="325">
         <f>SUM(E109:E118)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B110" s="327"/>
-      <c r="C110" s="268">
+    <row r="110" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B110" s="316"/>
+      <c r="C110" s="265">
         <v>2</v>
       </c>
-      <c r="D110" s="240"/>
-      <c r="E110" s="269"/>
-      <c r="F110" s="330"/>
-    </row>
-    <row r="111" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B111" s="327"/>
-      <c r="C111" s="268">
+      <c r="D110" s="237"/>
+      <c r="E110" s="266"/>
+      <c r="F110" s="326"/>
+    </row>
+    <row r="111" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B111" s="316"/>
+      <c r="C111" s="265">
         <v>3</v>
       </c>
-      <c r="D111" s="240"/>
-      <c r="E111" s="269"/>
-      <c r="F111" s="330"/>
-    </row>
-    <row r="112" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B112" s="327"/>
-      <c r="C112" s="268">
+      <c r="D111" s="237"/>
+      <c r="E111" s="266"/>
+      <c r="F111" s="326"/>
+    </row>
+    <row r="112" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B112" s="316"/>
+      <c r="C112" s="265">
         <v>4</v>
       </c>
-      <c r="D112" s="240"/>
-      <c r="E112" s="269"/>
-      <c r="F112" s="330"/>
-    </row>
-    <row r="113" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B113" s="327"/>
-      <c r="C113" s="268">
+      <c r="D112" s="237"/>
+      <c r="E112" s="266"/>
+      <c r="F112" s="326"/>
+    </row>
+    <row r="113" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B113" s="316"/>
+      <c r="C113" s="265">
         <v>5</v>
       </c>
-      <c r="D113" s="240"/>
-      <c r="E113" s="269"/>
-      <c r="F113" s="330"/>
-    </row>
-    <row r="114" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B114" s="327"/>
-      <c r="C114" s="268">
+      <c r="D113" s="237"/>
+      <c r="E113" s="266"/>
+      <c r="F113" s="326"/>
+    </row>
+    <row r="114" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B114" s="316"/>
+      <c r="C114" s="265">
         <v>6</v>
       </c>
-      <c r="D114" s="240"/>
-      <c r="E114" s="269"/>
-      <c r="F114" s="330"/>
-    </row>
-    <row r="115" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B115" s="327"/>
-      <c r="C115" s="268">
+      <c r="D114" s="237"/>
+      <c r="E114" s="266"/>
+      <c r="F114" s="326"/>
+    </row>
+    <row r="115" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B115" s="316"/>
+      <c r="C115" s="265">
         <v>7</v>
       </c>
-      <c r="D115" s="240"/>
-      <c r="E115" s="269"/>
-      <c r="F115" s="330"/>
-    </row>
-    <row r="116" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B116" s="327"/>
-      <c r="C116" s="268">
+      <c r="D115" s="237"/>
+      <c r="E115" s="266"/>
+      <c r="F115" s="326"/>
+    </row>
+    <row r="116" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B116" s="316"/>
+      <c r="C116" s="265">
         <v>8</v>
       </c>
-      <c r="D116" s="240"/>
-      <c r="E116" s="269"/>
-      <c r="F116" s="330"/>
-    </row>
-    <row r="117" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B117" s="327"/>
-      <c r="C117" s="268">
+      <c r="D116" s="237"/>
+      <c r="E116" s="266"/>
+      <c r="F116" s="326"/>
+    </row>
+    <row r="117" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B117" s="316"/>
+      <c r="C117" s="265">
         <v>9</v>
       </c>
-      <c r="D117" s="240"/>
-      <c r="E117" s="269"/>
-      <c r="F117" s="330"/>
-    </row>
-    <row r="118" spans="2:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B118" s="328"/>
-      <c r="C118" s="270">
+      <c r="D117" s="237"/>
+      <c r="E117" s="266"/>
+      <c r="F117" s="326"/>
+    </row>
+    <row r="118" spans="2:6" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B118" s="317"/>
+      <c r="C118" s="267">
         <v>10</v>
       </c>
-      <c r="D118" s="271"/>
-      <c r="E118" s="272"/>
-      <c r="F118" s="331"/>
-    </row>
-    <row r="119" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B119" s="326" t="s">
+      <c r="D118" s="268"/>
+      <c r="E118" s="269"/>
+      <c r="F118" s="327"/>
+    </row>
+    <row r="119" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B119" s="321" t="s">
         <v>283</v>
       </c>
-      <c r="C119" s="265">
+      <c r="C119" s="262">
         <v>1</v>
       </c>
-      <c r="D119" s="266"/>
-      <c r="E119" s="273"/>
-      <c r="F119" s="337">
+      <c r="D119" s="263"/>
+      <c r="E119" s="270"/>
+      <c r="F119" s="325">
         <f>SUM(E119:E128)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B120" s="327"/>
-      <c r="C120" s="268">
+    <row r="120" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B120" s="316"/>
+      <c r="C120" s="265">
         <v>2</v>
       </c>
-      <c r="D120" s="240"/>
-      <c r="E120" s="269"/>
-      <c r="F120" s="330"/>
-    </row>
-    <row r="121" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B121" s="327"/>
-      <c r="C121" s="268">
+      <c r="D120" s="237"/>
+      <c r="E120" s="266"/>
+      <c r="F120" s="326"/>
+    </row>
+    <row r="121" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B121" s="316"/>
+      <c r="C121" s="265">
         <v>3</v>
       </c>
-      <c r="D121" s="240"/>
-      <c r="E121" s="269"/>
-      <c r="F121" s="330"/>
-    </row>
-    <row r="122" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B122" s="327"/>
-      <c r="C122" s="268">
+      <c r="D121" s="237"/>
+      <c r="E121" s="266"/>
+      <c r="F121" s="326"/>
+    </row>
+    <row r="122" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B122" s="316"/>
+      <c r="C122" s="265">
         <v>4</v>
       </c>
-      <c r="D122" s="240"/>
-      <c r="E122" s="269"/>
-      <c r="F122" s="330"/>
-    </row>
-    <row r="123" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B123" s="327"/>
-      <c r="C123" s="268">
+      <c r="D122" s="237"/>
+      <c r="E122" s="266"/>
+      <c r="F122" s="326"/>
+    </row>
+    <row r="123" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B123" s="316"/>
+      <c r="C123" s="265">
         <v>5</v>
       </c>
-      <c r="D123" s="240"/>
-      <c r="E123" s="269"/>
-      <c r="F123" s="330"/>
-    </row>
-    <row r="124" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B124" s="327"/>
-      <c r="C124" s="268">
+      <c r="D123" s="237"/>
+      <c r="E123" s="266"/>
+      <c r="F123" s="326"/>
+    </row>
+    <row r="124" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B124" s="316"/>
+      <c r="C124" s="265">
         <v>6</v>
       </c>
-      <c r="D124" s="240"/>
-      <c r="E124" s="269"/>
-      <c r="F124" s="330"/>
-    </row>
-    <row r="125" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B125" s="327"/>
-      <c r="C125" s="268">
+      <c r="D124" s="237"/>
+      <c r="E124" s="266"/>
+      <c r="F124" s="326"/>
+    </row>
+    <row r="125" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B125" s="316"/>
+      <c r="C125" s="265">
         <v>7</v>
       </c>
-      <c r="D125" s="240"/>
-      <c r="E125" s="269"/>
-      <c r="F125" s="330"/>
-    </row>
-    <row r="126" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B126" s="327"/>
-      <c r="C126" s="268">
+      <c r="D125" s="237"/>
+      <c r="E125" s="266"/>
+      <c r="F125" s="326"/>
+    </row>
+    <row r="126" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B126" s="316"/>
+      <c r="C126" s="265">
         <v>8</v>
       </c>
-      <c r="D126" s="240"/>
-      <c r="E126" s="269"/>
-      <c r="F126" s="330"/>
-    </row>
-    <row r="127" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B127" s="327"/>
-      <c r="C127" s="268">
+      <c r="D126" s="237"/>
+      <c r="E126" s="266"/>
+      <c r="F126" s="326"/>
+    </row>
+    <row r="127" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B127" s="316"/>
+      <c r="C127" s="265">
         <v>9</v>
       </c>
-      <c r="D127" s="240"/>
-      <c r="E127" s="269"/>
-      <c r="F127" s="330"/>
-    </row>
-    <row r="128" spans="2:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B128" s="328"/>
-      <c r="C128" s="270">
+      <c r="D127" s="237"/>
+      <c r="E127" s="266"/>
+      <c r="F127" s="326"/>
+    </row>
+    <row r="128" spans="2:6" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B128" s="317"/>
+      <c r="C128" s="267">
         <v>10</v>
       </c>
-      <c r="D128" s="271"/>
-      <c r="E128" s="272"/>
-      <c r="F128" s="331"/>
-    </row>
-    <row r="129" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B129" s="326" t="s">
+      <c r="D128" s="268"/>
+      <c r="E128" s="269"/>
+      <c r="F128" s="327"/>
+    </row>
+    <row r="129" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B129" s="321" t="s">
         <v>284</v>
       </c>
-      <c r="C129" s="265">
+      <c r="C129" s="262">
         <v>1</v>
       </c>
-      <c r="D129" s="266"/>
-      <c r="E129" s="273"/>
-      <c r="F129" s="337">
+      <c r="D129" s="263"/>
+      <c r="E129" s="270"/>
+      <c r="F129" s="325">
         <f>SUM(E129:E131)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B130" s="327"/>
-      <c r="C130" s="268">
+    <row r="130" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B130" s="316"/>
+      <c r="C130" s="265">
         <v>2</v>
       </c>
-      <c r="D130" s="240"/>
-      <c r="E130" s="269"/>
-      <c r="F130" s="330"/>
-    </row>
-    <row r="131" spans="2:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B131" s="327"/>
-      <c r="C131" s="268">
+      <c r="D130" s="237"/>
+      <c r="E130" s="266"/>
+      <c r="F130" s="326"/>
+    </row>
+    <row r="131" spans="2:6" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B131" s="316"/>
+      <c r="C131" s="265">
         <v>3</v>
       </c>
-      <c r="D131" s="240"/>
-      <c r="E131" s="269"/>
-      <c r="F131" s="330"/>
-    </row>
-    <row r="132" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B132" s="338" t="s">
+      <c r="D131" s="237"/>
+      <c r="E131" s="266"/>
+      <c r="F131" s="326"/>
+    </row>
+    <row r="132" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B132" s="322" t="s">
         <v>285</v>
       </c>
-      <c r="C132" s="274">
+      <c r="C132" s="271">
         <v>1</v>
       </c>
-      <c r="D132" s="275"/>
-      <c r="E132" s="276"/>
-      <c r="F132" s="341">
+      <c r="D132" s="272"/>
+      <c r="E132" s="273"/>
+      <c r="F132" s="331">
         <f>SUM(E132:E140)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B133" s="339"/>
-      <c r="C133" s="277">
+    <row r="133" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B133" s="323"/>
+      <c r="C133" s="274">
         <v>2</v>
       </c>
-      <c r="D133" s="278"/>
-      <c r="E133" s="279"/>
-      <c r="F133" s="342"/>
-    </row>
-    <row r="134" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B134" s="339"/>
-      <c r="C134" s="277">
+      <c r="D133" s="275"/>
+      <c r="E133" s="276"/>
+      <c r="F133" s="332"/>
+    </row>
+    <row r="134" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B134" s="323"/>
+      <c r="C134" s="274">
         <v>3</v>
       </c>
-      <c r="D134" s="278"/>
-      <c r="E134" s="279"/>
-      <c r="F134" s="342"/>
-    </row>
-    <row r="135" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B135" s="339"/>
-      <c r="C135" s="277">
+      <c r="D134" s="275"/>
+      <c r="E134" s="276"/>
+      <c r="F134" s="332"/>
+    </row>
+    <row r="135" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B135" s="323"/>
+      <c r="C135" s="274">
         <v>4</v>
       </c>
-      <c r="D135" s="278"/>
-      <c r="E135" s="279"/>
-      <c r="F135" s="342"/>
-    </row>
-    <row r="136" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B136" s="339"/>
-      <c r="C136" s="277">
+      <c r="D135" s="275"/>
+      <c r="E135" s="276"/>
+      <c r="F135" s="332"/>
+    </row>
+    <row r="136" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B136" s="323"/>
+      <c r="C136" s="274">
         <v>5</v>
       </c>
-      <c r="D136" s="278"/>
-      <c r="E136" s="279"/>
-      <c r="F136" s="342"/>
-    </row>
-    <row r="137" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B137" s="339"/>
-      <c r="C137" s="277">
+      <c r="D136" s="275"/>
+      <c r="E136" s="276"/>
+      <c r="F136" s="332"/>
+    </row>
+    <row r="137" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B137" s="323"/>
+      <c r="C137" s="274">
         <v>6</v>
       </c>
-      <c r="D137" s="278"/>
-      <c r="E137" s="279"/>
-      <c r="F137" s="342"/>
-    </row>
-    <row r="138" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B138" s="339"/>
-      <c r="C138" s="277">
+      <c r="D137" s="275"/>
+      <c r="E137" s="276"/>
+      <c r="F137" s="332"/>
+    </row>
+    <row r="138" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B138" s="323"/>
+      <c r="C138" s="274">
         <v>7</v>
       </c>
-      <c r="D138" s="278"/>
-      <c r="E138" s="279"/>
-      <c r="F138" s="342"/>
-    </row>
-    <row r="139" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B139" s="339"/>
-      <c r="C139" s="234">
+      <c r="D138" s="275"/>
+      <c r="E138" s="276"/>
+      <c r="F138" s="332"/>
+    </row>
+    <row r="139" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B139" s="323"/>
+      <c r="C139" s="231">
         <v>8</v>
       </c>
-      <c r="D139" s="280"/>
-      <c r="E139" s="281"/>
-      <c r="F139" s="342"/>
-    </row>
-    <row r="140" spans="2:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B140" s="340"/>
-      <c r="C140" s="282">
+      <c r="D139" s="277"/>
+      <c r="E139" s="278"/>
+      <c r="F139" s="332"/>
+    </row>
+    <row r="140" spans="2:6" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B140" s="324"/>
+      <c r="C140" s="279">
         <v>9</v>
       </c>
-      <c r="D140" s="283"/>
-      <c r="E140" s="284"/>
-      <c r="F140" s="343"/>
-    </row>
-    <row r="141" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B141" s="326" t="s">
+      <c r="D140" s="280"/>
+      <c r="E140" s="281"/>
+      <c r="F140" s="333"/>
+    </row>
+    <row r="141" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B141" s="321" t="s">
         <v>286</v>
       </c>
-      <c r="C141" s="285">
+      <c r="C141" s="282">
         <v>1</v>
       </c>
-      <c r="D141" s="286"/>
-      <c r="E141" s="287"/>
-      <c r="F141" s="337">
+      <c r="D141" s="283"/>
+      <c r="E141" s="284"/>
+      <c r="F141" s="325">
         <f>SUM(E141:E150)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B142" s="327"/>
-      <c r="C142" s="268">
+    <row r="142" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B142" s="316"/>
+      <c r="C142" s="265">
         <v>2</v>
       </c>
-      <c r="D142" s="240"/>
-      <c r="E142" s="269"/>
-      <c r="F142" s="330"/>
-    </row>
-    <row r="143" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B143" s="327"/>
-      <c r="C143" s="268">
+      <c r="D142" s="237"/>
+      <c r="E142" s="266"/>
+      <c r="F142" s="326"/>
+    </row>
+    <row r="143" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B143" s="316"/>
+      <c r="C143" s="265">
         <v>3</v>
       </c>
-      <c r="D143" s="240"/>
-      <c r="E143" s="269"/>
-      <c r="F143" s="330"/>
-    </row>
-    <row r="144" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B144" s="327"/>
-      <c r="C144" s="268">
+      <c r="D143" s="237"/>
+      <c r="E143" s="266"/>
+      <c r="F143" s="326"/>
+    </row>
+    <row r="144" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B144" s="316"/>
+      <c r="C144" s="265">
         <v>4</v>
       </c>
-      <c r="D144" s="240"/>
-      <c r="E144" s="269"/>
-      <c r="F144" s="330"/>
-    </row>
-    <row r="145" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B145" s="327"/>
-      <c r="C145" s="268">
+      <c r="D144" s="237"/>
+      <c r="E144" s="266"/>
+      <c r="F144" s="326"/>
+    </row>
+    <row r="145" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B145" s="316"/>
+      <c r="C145" s="265">
         <v>5</v>
       </c>
-      <c r="D145" s="240"/>
-      <c r="E145" s="269"/>
-      <c r="F145" s="330"/>
-    </row>
-    <row r="146" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B146" s="327"/>
-      <c r="C146" s="268">
+      <c r="D145" s="237"/>
+      <c r="E145" s="266"/>
+      <c r="F145" s="326"/>
+    </row>
+    <row r="146" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B146" s="316"/>
+      <c r="C146" s="265">
         <v>6</v>
       </c>
-      <c r="D146" s="240"/>
-      <c r="E146" s="269"/>
-      <c r="F146" s="330"/>
-    </row>
-    <row r="147" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B147" s="327"/>
-      <c r="C147" s="268">
+      <c r="D146" s="237"/>
+      <c r="E146" s="266"/>
+      <c r="F146" s="326"/>
+    </row>
+    <row r="147" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B147" s="316"/>
+      <c r="C147" s="265">
         <v>7</v>
       </c>
-      <c r="D147" s="240"/>
-      <c r="E147" s="269"/>
-      <c r="F147" s="330"/>
-    </row>
-    <row r="148" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B148" s="327"/>
-      <c r="C148" s="268">
+      <c r="D147" s="237"/>
+      <c r="E147" s="266"/>
+      <c r="F147" s="326"/>
+    </row>
+    <row r="148" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B148" s="316"/>
+      <c r="C148" s="265">
         <v>8</v>
       </c>
-      <c r="D148" s="240"/>
-      <c r="E148" s="269"/>
-      <c r="F148" s="330"/>
-    </row>
-    <row r="149" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B149" s="327"/>
-      <c r="C149" s="268">
+      <c r="D148" s="237"/>
+      <c r="E148" s="266"/>
+      <c r="F148" s="326"/>
+    </row>
+    <row r="149" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B149" s="316"/>
+      <c r="C149" s="265">
         <v>9</v>
       </c>
-      <c r="D149" s="240"/>
-      <c r="E149" s="269"/>
-      <c r="F149" s="330"/>
-    </row>
-    <row r="150" spans="2:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B150" s="328"/>
-      <c r="C150" s="288">
+      <c r="D149" s="237"/>
+      <c r="E149" s="266"/>
+      <c r="F149" s="326"/>
+    </row>
+    <row r="150" spans="2:6" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B150" s="317"/>
+      <c r="C150" s="285">
         <v>10</v>
       </c>
-      <c r="D150" s="241"/>
-      <c r="E150" s="289"/>
-      <c r="F150" s="331"/>
-    </row>
-    <row r="151" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B151" s="326" t="s">
+      <c r="D150" s="238"/>
+      <c r="E150" s="286"/>
+      <c r="F150" s="327"/>
+    </row>
+    <row r="151" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B151" s="321" t="s">
         <v>287</v>
       </c>
-      <c r="C151" s="290">
+      <c r="C151" s="287">
         <v>1</v>
       </c>
-      <c r="D151" s="266"/>
-      <c r="E151" s="291"/>
-      <c r="F151" s="344">
+      <c r="D151" s="263"/>
+      <c r="E151" s="288"/>
+      <c r="F151" s="328">
         <f>SUM(E151:E160)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B152" s="327"/>
-      <c r="C152" s="292">
+    <row r="152" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B152" s="316"/>
+      <c r="C152" s="289">
         <v>2</v>
       </c>
-      <c r="D152" s="240"/>
-      <c r="E152" s="293"/>
-      <c r="F152" s="345"/>
-    </row>
-    <row r="153" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B153" s="327"/>
-      <c r="C153" s="292">
+      <c r="D152" s="237"/>
+      <c r="E152" s="290"/>
+      <c r="F152" s="329"/>
+    </row>
+    <row r="153" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B153" s="316"/>
+      <c r="C153" s="289">
         <v>3</v>
       </c>
-      <c r="D153" s="240"/>
-      <c r="E153" s="293"/>
-      <c r="F153" s="345"/>
-    </row>
-    <row r="154" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B154" s="327"/>
-      <c r="C154" s="292">
+      <c r="D153" s="237"/>
+      <c r="E153" s="290"/>
+      <c r="F153" s="329"/>
+    </row>
+    <row r="154" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B154" s="316"/>
+      <c r="C154" s="289">
         <v>4</v>
       </c>
-      <c r="D154" s="240"/>
-      <c r="E154" s="293"/>
-      <c r="F154" s="345"/>
-    </row>
-    <row r="155" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B155" s="327"/>
-      <c r="C155" s="292">
+      <c r="D154" s="237"/>
+      <c r="E154" s="290"/>
+      <c r="F154" s="329"/>
+    </row>
+    <row r="155" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B155" s="316"/>
+      <c r="C155" s="289">
         <v>5</v>
       </c>
-      <c r="D155" s="240"/>
-      <c r="E155" s="293"/>
-      <c r="F155" s="345"/>
-    </row>
-    <row r="156" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B156" s="327"/>
-      <c r="C156" s="292">
+      <c r="D155" s="237"/>
+      <c r="E155" s="290"/>
+      <c r="F155" s="329"/>
+    </row>
+    <row r="156" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B156" s="316"/>
+      <c r="C156" s="289">
         <v>6</v>
       </c>
-      <c r="D156" s="240"/>
-      <c r="E156" s="293"/>
-      <c r="F156" s="345"/>
-    </row>
-    <row r="157" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B157" s="327"/>
-      <c r="C157" s="292">
+      <c r="D156" s="237"/>
+      <c r="E156" s="290"/>
+      <c r="F156" s="329"/>
+    </row>
+    <row r="157" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B157" s="316"/>
+      <c r="C157" s="289">
         <v>7</v>
       </c>
-      <c r="D157" s="240"/>
-      <c r="E157" s="293"/>
-      <c r="F157" s="345"/>
-    </row>
-    <row r="158" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B158" s="327"/>
-      <c r="C158" s="292">
+      <c r="D157" s="237"/>
+      <c r="E157" s="290"/>
+      <c r="F157" s="329"/>
+    </row>
+    <row r="158" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B158" s="316"/>
+      <c r="C158" s="289">
         <v>8</v>
       </c>
-      <c r="D158" s="240"/>
-      <c r="E158" s="293"/>
-      <c r="F158" s="345"/>
-    </row>
-    <row r="159" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B159" s="327"/>
-      <c r="C159" s="292">
+      <c r="D158" s="237"/>
+      <c r="E158" s="290"/>
+      <c r="F158" s="329"/>
+    </row>
+    <row r="159" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B159" s="316"/>
+      <c r="C159" s="289">
         <v>9</v>
       </c>
-      <c r="D159" s="240"/>
-      <c r="E159" s="293"/>
-      <c r="F159" s="345"/>
-    </row>
-    <row r="160" spans="2:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B160" s="328"/>
-      <c r="C160" s="294">
+      <c r="D159" s="237"/>
+      <c r="E159" s="290"/>
+      <c r="F159" s="329"/>
+    </row>
+    <row r="160" spans="2:6" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B160" s="317"/>
+      <c r="C160" s="291">
         <v>10</v>
       </c>
-      <c r="D160" s="271"/>
-      <c r="E160" s="295"/>
-      <c r="F160" s="346"/>
-    </row>
-    <row r="161" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B161" s="327" t="s">
+      <c r="D160" s="268"/>
+      <c r="E160" s="292"/>
+      <c r="F160" s="330"/>
+    </row>
+    <row r="161" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B161" s="316" t="s">
         <v>288</v>
       </c>
-      <c r="C161" s="290">
+      <c r="C161" s="287">
         <v>1</v>
       </c>
-      <c r="D161" s="266"/>
-      <c r="E161" s="273"/>
-      <c r="F161" s="347">
+      <c r="D161" s="263"/>
+      <c r="E161" s="270"/>
+      <c r="F161" s="318">
         <f>SUM(E161:E170)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B162" s="327"/>
-      <c r="C162" s="292">
+    <row r="162" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B162" s="316"/>
+      <c r="C162" s="289">
         <v>2</v>
       </c>
-      <c r="D162" s="240"/>
-      <c r="E162" s="269"/>
-      <c r="F162" s="348"/>
-    </row>
-    <row r="163" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B163" s="327"/>
-      <c r="C163" s="292">
+      <c r="D162" s="237"/>
+      <c r="E162" s="266"/>
+      <c r="F162" s="319"/>
+    </row>
+    <row r="163" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B163" s="316"/>
+      <c r="C163" s="289">
         <v>3</v>
       </c>
-      <c r="D163" s="240"/>
-      <c r="E163" s="269"/>
-      <c r="F163" s="348"/>
-    </row>
-    <row r="164" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B164" s="327"/>
-      <c r="C164" s="292">
+      <c r="D163" s="237"/>
+      <c r="E163" s="266"/>
+      <c r="F163" s="319"/>
+    </row>
+    <row r="164" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B164" s="316"/>
+      <c r="C164" s="289">
         <v>4</v>
       </c>
-      <c r="D164" s="240"/>
-      <c r="E164" s="269"/>
-      <c r="F164" s="348"/>
-    </row>
-    <row r="165" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B165" s="327"/>
-      <c r="C165" s="292">
+      <c r="D164" s="237"/>
+      <c r="E164" s="266"/>
+      <c r="F164" s="319"/>
+    </row>
+    <row r="165" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B165" s="316"/>
+      <c r="C165" s="289">
         <v>5</v>
       </c>
-      <c r="D165" s="240"/>
-      <c r="E165" s="269"/>
-      <c r="F165" s="348"/>
-    </row>
-    <row r="166" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B166" s="327"/>
-      <c r="C166" s="292">
+      <c r="D165" s="237"/>
+      <c r="E165" s="266"/>
+      <c r="F165" s="319"/>
+    </row>
+    <row r="166" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B166" s="316"/>
+      <c r="C166" s="289">
         <v>6</v>
       </c>
-      <c r="D166" s="240"/>
-      <c r="E166" s="269"/>
-      <c r="F166" s="348"/>
-    </row>
-    <row r="167" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B167" s="327"/>
-      <c r="C167" s="292">
+      <c r="D166" s="237"/>
+      <c r="E166" s="266"/>
+      <c r="F166" s="319"/>
+    </row>
+    <row r="167" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B167" s="316"/>
+      <c r="C167" s="289">
         <v>7</v>
       </c>
-      <c r="D167" s="240"/>
-      <c r="E167" s="269"/>
-      <c r="F167" s="348"/>
-    </row>
-    <row r="168" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B168" s="327"/>
-      <c r="C168" s="292">
+      <c r="D167" s="237"/>
+      <c r="E167" s="266"/>
+      <c r="F167" s="319"/>
+    </row>
+    <row r="168" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B168" s="316"/>
+      <c r="C168" s="289">
         <v>8</v>
       </c>
-      <c r="D168" s="240"/>
-      <c r="E168" s="269"/>
-      <c r="F168" s="348"/>
-    </row>
-    <row r="169" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B169" s="327"/>
-      <c r="C169" s="292">
+      <c r="D168" s="237"/>
+      <c r="E168" s="266"/>
+      <c r="F168" s="319"/>
+    </row>
+    <row r="169" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B169" s="316"/>
+      <c r="C169" s="289">
         <v>9</v>
       </c>
-      <c r="D169" s="240"/>
-      <c r="E169" s="269"/>
-      <c r="F169" s="348"/>
-    </row>
-    <row r="170" spans="2:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B170" s="328"/>
-      <c r="C170" s="294">
+      <c r="D169" s="237"/>
+      <c r="E169" s="266"/>
+      <c r="F169" s="319"/>
+    </row>
+    <row r="170" spans="2:6" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B170" s="317"/>
+      <c r="C170" s="291">
         <v>10</v>
       </c>
-      <c r="D170" s="271"/>
-      <c r="E170" s="272"/>
-      <c r="F170" s="349"/>
-    </row>
-    <row r="171" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B171" s="326" t="s">
+      <c r="D170" s="268"/>
+      <c r="E170" s="269"/>
+      <c r="F170" s="320"/>
+    </row>
+    <row r="171" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B171" s="321" t="s">
         <v>289</v>
       </c>
-      <c r="C171" s="285">
+      <c r="C171" s="282">
         <v>1</v>
       </c>
-      <c r="D171" s="286"/>
-      <c r="E171" s="287"/>
-      <c r="F171" s="347">
+      <c r="D171" s="283"/>
+      <c r="E171" s="284"/>
+      <c r="F171" s="318">
         <f>SUM(E171:E179)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B172" s="327"/>
-      <c r="C172" s="268">
+    <row r="172" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B172" s="316"/>
+      <c r="C172" s="265">
         <v>2</v>
       </c>
-      <c r="D172" s="240"/>
-      <c r="E172" s="269"/>
-      <c r="F172" s="348"/>
-    </row>
-    <row r="173" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B173" s="327"/>
-      <c r="C173" s="268">
+      <c r="D172" s="237"/>
+      <c r="E172" s="266"/>
+      <c r="F172" s="319"/>
+    </row>
+    <row r="173" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B173" s="316"/>
+      <c r="C173" s="265">
         <v>3</v>
       </c>
-      <c r="D173" s="240"/>
-      <c r="E173" s="269"/>
-      <c r="F173" s="348"/>
-    </row>
-    <row r="174" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B174" s="327"/>
-      <c r="C174" s="268">
+      <c r="D173" s="237"/>
+      <c r="E173" s="266"/>
+      <c r="F173" s="319"/>
+    </row>
+    <row r="174" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B174" s="316"/>
+      <c r="C174" s="265">
         <v>4</v>
       </c>
-      <c r="D174" s="240"/>
-      <c r="E174" s="269"/>
-      <c r="F174" s="348"/>
-    </row>
-    <row r="175" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B175" s="327"/>
-      <c r="C175" s="268">
+      <c r="D174" s="237"/>
+      <c r="E174" s="266"/>
+      <c r="F174" s="319"/>
+    </row>
+    <row r="175" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B175" s="316"/>
+      <c r="C175" s="265">
         <v>5</v>
       </c>
-      <c r="D175" s="240"/>
-      <c r="E175" s="269"/>
-      <c r="F175" s="348"/>
-    </row>
-    <row r="176" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B176" s="327"/>
-      <c r="C176" s="268">
+      <c r="D175" s="237"/>
+      <c r="E175" s="266"/>
+      <c r="F175" s="319"/>
+    </row>
+    <row r="176" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B176" s="316"/>
+      <c r="C176" s="265">
         <v>6</v>
       </c>
-      <c r="D176" s="240"/>
-      <c r="E176" s="269"/>
-      <c r="F176" s="348"/>
-    </row>
-    <row r="177" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B177" s="327"/>
-      <c r="C177" s="268">
+      <c r="D176" s="237"/>
+      <c r="E176" s="266"/>
+      <c r="F176" s="319"/>
+    </row>
+    <row r="177" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B177" s="316"/>
+      <c r="C177" s="265">
         <v>7</v>
       </c>
-      <c r="D177" s="240"/>
-      <c r="E177" s="269"/>
-      <c r="F177" s="348"/>
-    </row>
-    <row r="178" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B178" s="327"/>
-      <c r="C178" s="268">
+      <c r="D177" s="237"/>
+      <c r="E177" s="266"/>
+      <c r="F177" s="319"/>
+    </row>
+    <row r="178" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B178" s="316"/>
+      <c r="C178" s="265">
         <v>8</v>
       </c>
-      <c r="D178" s="240"/>
-      <c r="E178" s="269"/>
-      <c r="F178" s="348"/>
-    </row>
-    <row r="179" spans="2:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B179" s="327"/>
-      <c r="C179" s="288">
+      <c r="D178" s="237"/>
+      <c r="E178" s="266"/>
+      <c r="F178" s="319"/>
+    </row>
+    <row r="179" spans="2:6" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B179" s="316"/>
+      <c r="C179" s="285">
         <v>9</v>
       </c>
-      <c r="D179" s="241"/>
-      <c r="E179" s="289"/>
-      <c r="F179" s="349"/>
-    </row>
-    <row r="180" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B180" s="338" t="s">
+      <c r="D179" s="238"/>
+      <c r="E179" s="286"/>
+      <c r="F179" s="320"/>
+    </row>
+    <row r="180" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B180" s="322" t="s">
         <v>110</v>
       </c>
-      <c r="C180" s="274">
+      <c r="C180" s="271">
         <v>1</v>
       </c>
-      <c r="D180" s="275"/>
-      <c r="E180" s="296"/>
-      <c r="F180" s="347">
+      <c r="D180" s="272"/>
+      <c r="E180" s="293"/>
+      <c r="F180" s="318">
         <f>SUM(E180:E189)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B181" s="339"/>
-      <c r="C181" s="234">
+    <row r="181" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B181" s="323"/>
+      <c r="C181" s="231">
         <v>2</v>
       </c>
-      <c r="D181" s="280"/>
-      <c r="E181" s="297"/>
-      <c r="F181" s="348"/>
-    </row>
-    <row r="182" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B182" s="339"/>
-      <c r="C182" s="234">
+      <c r="D181" s="277"/>
+      <c r="E181" s="294"/>
+      <c r="F181" s="319"/>
+    </row>
+    <row r="182" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B182" s="323"/>
+      <c r="C182" s="231">
         <v>3</v>
       </c>
-      <c r="D182" s="280"/>
-      <c r="E182" s="297"/>
-      <c r="F182" s="348"/>
-    </row>
-    <row r="183" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B183" s="339"/>
-      <c r="C183" s="234">
+      <c r="D182" s="277"/>
+      <c r="E182" s="294"/>
+      <c r="F182" s="319"/>
+    </row>
+    <row r="183" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B183" s="323"/>
+      <c r="C183" s="231">
         <v>4</v>
       </c>
-      <c r="D183" s="280"/>
-      <c r="E183" s="297"/>
-      <c r="F183" s="348"/>
-    </row>
-    <row r="184" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B184" s="339"/>
-      <c r="C184" s="234">
+      <c r="D183" s="277"/>
+      <c r="E183" s="294"/>
+      <c r="F183" s="319"/>
+    </row>
+    <row r="184" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B184" s="323"/>
+      <c r="C184" s="231">
         <v>5</v>
       </c>
-      <c r="D184" s="280"/>
-      <c r="E184" s="297"/>
-      <c r="F184" s="348"/>
-    </row>
-    <row r="185" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B185" s="339"/>
-      <c r="C185" s="234">
+      <c r="D184" s="277"/>
+      <c r="E184" s="294"/>
+      <c r="F184" s="319"/>
+    </row>
+    <row r="185" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B185" s="323"/>
+      <c r="C185" s="231">
         <v>6</v>
       </c>
-      <c r="D185" s="280"/>
-      <c r="E185" s="297"/>
-      <c r="F185" s="348"/>
-    </row>
-    <row r="186" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B186" s="339"/>
-      <c r="C186" s="234">
+      <c r="D185" s="277"/>
+      <c r="E185" s="294"/>
+      <c r="F185" s="319"/>
+    </row>
+    <row r="186" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B186" s="323"/>
+      <c r="C186" s="231">
         <v>7</v>
       </c>
-      <c r="D186" s="280"/>
-      <c r="E186" s="297"/>
-      <c r="F186" s="348"/>
-    </row>
-    <row r="187" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B187" s="339"/>
-      <c r="C187" s="234">
+      <c r="D186" s="277"/>
+      <c r="E186" s="294"/>
+      <c r="F186" s="319"/>
+    </row>
+    <row r="187" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B187" s="323"/>
+      <c r="C187" s="231">
         <v>8</v>
       </c>
-      <c r="D187" s="280"/>
-      <c r="E187" s="297"/>
-      <c r="F187" s="348"/>
-    </row>
-    <row r="188" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B188" s="339"/>
-      <c r="C188" s="234">
+      <c r="D187" s="277"/>
+      <c r="E187" s="294"/>
+      <c r="F187" s="319"/>
+    </row>
+    <row r="188" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B188" s="323"/>
+      <c r="C188" s="231">
         <v>9</v>
       </c>
-      <c r="D188" s="280"/>
-      <c r="E188" s="297"/>
-      <c r="F188" s="348"/>
-    </row>
-    <row r="189" spans="2:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B189" s="340"/>
-      <c r="C189" s="282">
+      <c r="D188" s="277"/>
+      <c r="E188" s="294"/>
+      <c r="F188" s="319"/>
+    </row>
+    <row r="189" spans="2:6" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B189" s="324"/>
+      <c r="C189" s="279">
         <v>10</v>
       </c>
-      <c r="D189" s="283"/>
-      <c r="E189" s="298"/>
-      <c r="F189" s="349"/>
-    </row>
-    <row r="190" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B190" s="338" t="s">
+      <c r="D189" s="280"/>
+      <c r="E189" s="295"/>
+      <c r="F189" s="320"/>
+    </row>
+    <row r="190" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B190" s="322" t="s">
         <v>290</v>
       </c>
-      <c r="C190" s="274">
+      <c r="C190" s="271">
         <v>1</v>
       </c>
-      <c r="D190" s="275"/>
-      <c r="E190" s="296"/>
-      <c r="F190" s="347">
+      <c r="D190" s="272"/>
+      <c r="E190" s="293"/>
+      <c r="F190" s="318">
         <f>SUM(E190:E199)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B191" s="339"/>
-      <c r="C191" s="234">
+    <row r="191" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B191" s="323"/>
+      <c r="C191" s="231">
         <v>2</v>
       </c>
-      <c r="D191" s="280"/>
-      <c r="E191" s="297"/>
-      <c r="F191" s="348"/>
-    </row>
-    <row r="192" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B192" s="339"/>
-      <c r="C192" s="234">
+      <c r="D191" s="277"/>
+      <c r="E191" s="294"/>
+      <c r="F191" s="319"/>
+    </row>
+    <row r="192" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B192" s="323"/>
+      <c r="C192" s="231">
         <v>3</v>
       </c>
-      <c r="D192" s="280"/>
-      <c r="E192" s="297"/>
-      <c r="F192" s="348"/>
-    </row>
-    <row r="193" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B193" s="339"/>
-      <c r="C193" s="234">
+      <c r="D192" s="277"/>
+      <c r="E192" s="294"/>
+      <c r="F192" s="319"/>
+    </row>
+    <row r="193" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B193" s="323"/>
+      <c r="C193" s="231">
         <v>4</v>
       </c>
-      <c r="D193" s="280"/>
-      <c r="E193" s="297"/>
-      <c r="F193" s="348"/>
-    </row>
-    <row r="194" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B194" s="339"/>
-      <c r="C194" s="234">
+      <c r="D193" s="277"/>
+      <c r="E193" s="294"/>
+      <c r="F193" s="319"/>
+    </row>
+    <row r="194" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B194" s="323"/>
+      <c r="C194" s="231">
         <v>5</v>
       </c>
-      <c r="D194" s="280"/>
-      <c r="E194" s="297"/>
-      <c r="F194" s="348"/>
-    </row>
-    <row r="195" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B195" s="339"/>
-      <c r="C195" s="234">
+      <c r="D194" s="277"/>
+      <c r="E194" s="294"/>
+      <c r="F194" s="319"/>
+    </row>
+    <row r="195" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B195" s="323"/>
+      <c r="C195" s="231">
         <v>6</v>
       </c>
-      <c r="D195" s="280"/>
-      <c r="E195" s="297"/>
-      <c r="F195" s="348"/>
-    </row>
-    <row r="196" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B196" s="339"/>
-      <c r="C196" s="234">
+      <c r="D195" s="277"/>
+      <c r="E195" s="294"/>
+      <c r="F195" s="319"/>
+    </row>
+    <row r="196" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B196" s="323"/>
+      <c r="C196" s="231">
         <v>7</v>
       </c>
-      <c r="D196" s="280"/>
-      <c r="E196" s="297"/>
-      <c r="F196" s="348"/>
-    </row>
-    <row r="197" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B197" s="339"/>
-      <c r="C197" s="234">
+      <c r="D196" s="277"/>
+      <c r="E196" s="294"/>
+      <c r="F196" s="319"/>
+    </row>
+    <row r="197" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B197" s="323"/>
+      <c r="C197" s="231">
         <v>8</v>
       </c>
-      <c r="D197" s="280"/>
-      <c r="E197" s="297"/>
-      <c r="F197" s="348"/>
-    </row>
-    <row r="198" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B198" s="339"/>
-      <c r="C198" s="234">
+      <c r="D197" s="277"/>
+      <c r="E197" s="294"/>
+      <c r="F197" s="319"/>
+    </row>
+    <row r="198" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B198" s="323"/>
+      <c r="C198" s="231">
         <v>9</v>
       </c>
-      <c r="D198" s="280"/>
-      <c r="E198" s="297"/>
-      <c r="F198" s="348"/>
-    </row>
-    <row r="199" spans="2:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B199" s="340"/>
-      <c r="C199" s="282">
+      <c r="D198" s="277"/>
+      <c r="E198" s="294"/>
+      <c r="F198" s="319"/>
+    </row>
+    <row r="199" spans="2:6" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B199" s="324"/>
+      <c r="C199" s="279">
         <v>10</v>
       </c>
-      <c r="D199" s="283"/>
-      <c r="E199" s="298"/>
-      <c r="F199" s="349"/>
-    </row>
-    <row r="200" spans="2:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B200" s="350" t="s">
+      <c r="D199" s="280"/>
+      <c r="E199" s="295"/>
+      <c r="F199" s="320"/>
+    </row>
+    <row r="200" spans="2:6" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B200" s="313" t="s">
         <v>291</v>
       </c>
-      <c r="C200" s="351"/>
-      <c r="D200" s="351"/>
-      <c r="E200" s="352"/>
-      <c r="F200" s="299">
+      <c r="C200" s="314"/>
+      <c r="D200" s="314"/>
+      <c r="E200" s="315"/>
+      <c r="F200" s="296">
         <f>SUM(F99:F199)</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B3:B8"/>
+    <mergeCell ref="B10:B16"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="B18:B21"/>
+    <mergeCell ref="B23:B47"/>
+    <mergeCell ref="B99:B108"/>
+    <mergeCell ref="F99:F108"/>
+    <mergeCell ref="B49:B94"/>
+    <mergeCell ref="D49:D94"/>
+    <mergeCell ref="B109:B118"/>
+    <mergeCell ref="F109:F118"/>
+    <mergeCell ref="B119:B128"/>
+    <mergeCell ref="F119:F128"/>
+    <mergeCell ref="B129:B131"/>
+    <mergeCell ref="F129:F131"/>
+    <mergeCell ref="B132:B140"/>
+    <mergeCell ref="F132:F140"/>
+    <mergeCell ref="B141:B150"/>
+    <mergeCell ref="F141:F150"/>
+    <mergeCell ref="B151:B160"/>
+    <mergeCell ref="F151:F160"/>
+    <mergeCell ref="B190:B199"/>
+    <mergeCell ref="F190:F199"/>
     <mergeCell ref="B200:E200"/>
     <mergeCell ref="B161:B170"/>
     <mergeCell ref="F161:F170"/>
@@ -7002,30 +7079,6 @@
     <mergeCell ref="F171:F179"/>
     <mergeCell ref="B180:B189"/>
     <mergeCell ref="F180:F189"/>
-    <mergeCell ref="B141:B150"/>
-    <mergeCell ref="F141:F150"/>
-    <mergeCell ref="B151:B160"/>
-    <mergeCell ref="F151:F160"/>
-    <mergeCell ref="B190:B199"/>
-    <mergeCell ref="F190:F199"/>
-    <mergeCell ref="B119:B128"/>
-    <mergeCell ref="F119:F128"/>
-    <mergeCell ref="B129:B131"/>
-    <mergeCell ref="F129:F131"/>
-    <mergeCell ref="B132:B140"/>
-    <mergeCell ref="F132:F140"/>
-    <mergeCell ref="B99:B108"/>
-    <mergeCell ref="F99:F108"/>
-    <mergeCell ref="B49:B94"/>
-    <mergeCell ref="D49:D94"/>
-    <mergeCell ref="B109:B118"/>
-    <mergeCell ref="F109:F118"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="B3:B8"/>
-    <mergeCell ref="B10:B16"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="B18:B21"/>
-    <mergeCell ref="B23:B47"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -7036,62 +7089,62 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:V114"/>
-  <sheetFormatPr defaultColWidth="21.81640625" defaultRowHeight="25.5" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="21.77734375" defaultRowHeight="25.8" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="55.26953125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.81640625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="27.81640625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="27.26953125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="30.1796875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="55.21875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.77734375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="27.77734375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="27.21875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="30.21875" style="2" customWidth="1"/>
     <col min="6" max="6" width="31" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="21.81640625" style="2"/>
+    <col min="7" max="16384" width="21.77734375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="362"/>
-      <c r="B1" s="362"/>
-      <c r="C1" s="362"/>
-      <c r="D1" s="362"/>
-      <c r="E1" s="362"/>
-      <c r="F1" s="362"/>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="362"/>
-      <c r="B2" s="362"/>
-      <c r="C2" s="362"/>
-      <c r="D2" s="362"/>
-      <c r="E2" s="362"/>
-      <c r="F2" s="362"/>
-    </row>
-    <row r="3" spans="1:15" ht="29.25" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="A3" s="363" t="s">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.5">
+      <c r="A1" s="350"/>
+      <c r="B1" s="350"/>
+      <c r="C1" s="350"/>
+      <c r="D1" s="350"/>
+      <c r="E1" s="350"/>
+      <c r="F1" s="350"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.5">
+      <c r="A2" s="350"/>
+      <c r="B2" s="350"/>
+      <c r="C2" s="350"/>
+      <c r="D2" s="350"/>
+      <c r="E2" s="350"/>
+      <c r="F2" s="350"/>
+    </row>
+    <row r="3" spans="1:15" ht="29.25" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A3" s="351" t="s">
         <v>217</v>
       </c>
-      <c r="B3" s="363"/>
-      <c r="C3" s="363"/>
-      <c r="D3" s="363"/>
-      <c r="E3" s="363"/>
-      <c r="F3" s="363"/>
-      <c r="M3" s="361"/>
-      <c r="N3" s="361"/>
-      <c r="O3" s="361"/>
-    </row>
-    <row r="4" spans="1:15" ht="57" customHeight="1" x14ac:dyDescent="1">
-      <c r="A4" s="356" t="s">
+      <c r="B3" s="351"/>
+      <c r="C3" s="351"/>
+      <c r="D3" s="351"/>
+      <c r="E3" s="351"/>
+      <c r="F3" s="351"/>
+      <c r="M3" s="360"/>
+      <c r="N3" s="360"/>
+      <c r="O3" s="360"/>
+    </row>
+    <row r="4" spans="1:15" ht="57" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="A4" s="361" t="s">
         <v>216</v>
       </c>
-      <c r="B4" s="356"/>
-      <c r="C4" s="356"/>
-      <c r="D4" s="356"/>
-      <c r="E4" s="356"/>
-      <c r="F4" s="356"/>
+      <c r="B4" s="361"/>
+      <c r="C4" s="361"/>
+      <c r="D4" s="361"/>
+      <c r="E4" s="361"/>
+      <c r="F4" s="361"/>
       <c r="H4" s="126"/>
     </row>
-    <row r="5" spans="1:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="364" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="358" t="s">
+    <row r="5" spans="1:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="352" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="354" t="s">
         <v>36</v>
       </c>
       <c r="C5" s="89" t="str">
@@ -7112,9 +7165,9 @@
       </c>
       <c r="H5"/>
     </row>
-    <row r="6" spans="1:15" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A6" s="365"/>
-      <c r="B6" s="359"/>
+    <row r="6" spans="1:15" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="353"/>
+      <c r="B6" s="355"/>
       <c r="C6" s="138">
         <f>Assumptions.1!I18</f>
         <v>0</v>
@@ -7133,10 +7186,10 @@
       </c>
       <c r="G6" s="3"/>
     </row>
-    <row r="7" spans="1:15" s="3" customFormat="1" ht="26" thickTop="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:15" s="3" customFormat="1" ht="26.4" thickTop="1" x14ac:dyDescent="0.5">
       <c r="E7" s="4"/>
     </row>
-    <row r="8" spans="1:15" s="3" customFormat="1" ht="31" x14ac:dyDescent="0.7">
+    <row r="8" spans="1:15" s="3" customFormat="1" ht="30.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="5" t="s">
         <v>145</v>
       </c>
@@ -7144,12 +7197,12 @@
       <c r="E8" s="141"/>
       <c r="F8" s="141"/>
     </row>
-    <row r="9" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A9" s="5"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
     </row>
-    <row r="10" spans="1:15" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:15" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A10" s="2" t="s">
         <v>178</v>
       </c>
@@ -7171,7 +7224,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="11" spans="1:15" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:15" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="6"/>
@@ -7179,7 +7232,7 @@
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
     </row>
-    <row r="12" spans="1:15" ht="38.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:15" ht="38.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="C12" s="7">
         <f>SUM(C10:C11)</f>
         <v>0</v>
@@ -7197,15 +7250,15 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.5">
       <c r="A14" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.5">
       <c r="A15" s="5"/>
     </row>
-    <row r="16" spans="1:15" ht="35.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:15" ht="35.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A16" s="2" t="s">
         <v>1</v>
       </c>
@@ -7227,7 +7280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:22" ht="37.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:22" ht="37.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A17" s="2" t="s">
         <v>96</v>
       </c>
@@ -7251,7 +7304,7 @@
       <c r="L17"/>
       <c r="T17" s="6"/>
     </row>
-    <row r="18" spans="1:22" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:22" ht="36" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A18" s="2" t="s">
         <v>2</v>
       </c>
@@ -7273,7 +7326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:22" ht="39.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:22" ht="39.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A19" s="3" t="s">
         <v>66</v>
       </c>
@@ -7294,12 +7347,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="20" spans="1:22" ht="46.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:22" ht="46.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A20" s="5"/>
       <c r="C20" s="3"/>
       <c r="D20" s="6"/>
     </row>
-    <row r="21" spans="1:22" s="3" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:22" s="3" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A21" s="5" t="s">
         <v>179</v>
       </c>
@@ -7325,14 +7378,14 @@
       <c r="K21" s="82"/>
       <c r="L21" s="82"/>
     </row>
-    <row r="22" spans="1:22" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:22" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A22" s="5"/>
       <c r="C22" s="135"/>
       <c r="D22" s="135"/>
       <c r="E22" s="135"/>
       <c r="F22" s="135"/>
     </row>
-    <row r="23" spans="1:22" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:22" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A23" s="2" t="s">
         <v>165</v>
       </c>
@@ -7354,7 +7407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:22" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:22" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A24" s="2"/>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
@@ -7362,7 +7415,7 @@
       <c r="F24" s="7"/>
       <c r="V24"/>
     </row>
-    <row r="25" spans="1:22" ht="43.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:22" ht="43.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A25" s="2" t="s">
         <v>166</v>
       </c>
@@ -7389,7 +7442,7 @@
       <c r="K25" s="86"/>
       <c r="L25" s="86"/>
     </row>
-    <row r="26" spans="1:22" ht="43.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:22" ht="43.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B26" s="10"/>
       <c r="H26" s="83"/>
       <c r="I26" s="83"/>
@@ -7397,7 +7450,7 @@
       <c r="K26" s="83"/>
       <c r="L26" s="83"/>
     </row>
-    <row r="27" spans="1:22" ht="43.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:22" ht="43.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A27" s="5" t="s">
         <v>180</v>
       </c>
@@ -7424,7 +7477,7 @@
       <c r="K27" s="83"/>
       <c r="L27" s="83"/>
     </row>
-    <row r="28" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A28" s="3"/>
       <c r="B28" s="10"/>
       <c r="H28" s="86"/>
@@ -7433,7 +7486,7 @@
       <c r="K28" s="86"/>
       <c r="L28" s="86"/>
     </row>
-    <row r="29" spans="1:22" ht="43.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:22" ht="43.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A29" s="2" t="s">
         <v>181</v>
       </c>
@@ -7460,7 +7513,7 @@
       <c r="K29" s="83"/>
       <c r="L29" s="83"/>
     </row>
-    <row r="30" spans="1:22" ht="43.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:22" ht="43.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B30" s="10"/>
       <c r="C30" s="6"/>
       <c r="D30" s="6"/>
@@ -7472,7 +7525,7 @@
       <c r="K30" s="83"/>
       <c r="L30" s="83"/>
     </row>
-    <row r="31" spans="1:22" s="15" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:22" s="15" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A31" s="5" t="s">
         <v>168</v>
       </c>
@@ -7498,7 +7551,7 @@
       <c r="K31" s="84"/>
       <c r="L31" s="84"/>
     </row>
-    <row r="32" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A32" s="3"/>
       <c r="D32" s="6"/>
       <c r="E32" s="6"/>
@@ -7509,7 +7562,7 @@
       <c r="K32" s="83"/>
       <c r="L32" s="83"/>
     </row>
-    <row r="33" spans="1:14" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:14" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A33" s="2" t="s">
         <v>167</v>
       </c>
@@ -7536,14 +7589,14 @@
       <c r="K33" s="83"/>
       <c r="L33" s="83"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.5">
       <c r="H34" s="83"/>
       <c r="I34" s="83"/>
       <c r="J34" s="83"/>
       <c r="K34" s="83"/>
       <c r="L34" s="83"/>
     </row>
-    <row r="35" spans="1:14" s="3" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:14" s="3" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A35" s="8" t="s">
         <v>169</v>
       </c>
@@ -7571,54 +7624,54 @@
       <c r="L35" s="85"/>
       <c r="M35" s="85"/>
     </row>
-    <row r="36" spans="1:14" s="3" customFormat="1" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="36" spans="1:14" s="3" customFormat="1" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="8"/>
       <c r="B36" s="9"/>
     </row>
-    <row r="37" spans="1:14" ht="26" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="37" spans="1:14" ht="26.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="11"/>
       <c r="B37" s="11"/>
-      <c r="C37" s="353" t="s">
+      <c r="C37" s="357" t="s">
         <v>164</v>
       </c>
-      <c r="D37" s="354"/>
-      <c r="E37" s="354"/>
-      <c r="F37" s="355"/>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="359"/>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.5">
       <c r="C38" s="120"/>
       <c r="D38" s="120"/>
       <c r="E38" s="120"/>
       <c r="F38" s="120"/>
     </row>
-    <row r="39" spans="1:14" ht="35.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="362"/>
-      <c r="B39" s="362"/>
-      <c r="C39" s="362"/>
-      <c r="D39" s="362"/>
-      <c r="E39" s="362"/>
-      <c r="F39" s="362"/>
-    </row>
-    <row r="40" spans="1:14" ht="39" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="362"/>
-      <c r="B40" s="362"/>
-      <c r="C40" s="362"/>
-      <c r="D40" s="362"/>
-      <c r="E40" s="362"/>
-      <c r="F40" s="362"/>
-    </row>
-    <row r="41" spans="1:14" ht="44.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="360" t="str">
+    <row r="39" spans="1:14" ht="35.25" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A39" s="350"/>
+      <c r="B39" s="350"/>
+      <c r="C39" s="350"/>
+      <c r="D39" s="350"/>
+      <c r="E39" s="350"/>
+      <c r="F39" s="350"/>
+    </row>
+    <row r="40" spans="1:14" ht="39" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A40" s="350"/>
+      <c r="B40" s="350"/>
+      <c r="C40" s="350"/>
+      <c r="D40" s="350"/>
+      <c r="E40" s="350"/>
+      <c r="F40" s="350"/>
+    </row>
+    <row r="41" spans="1:14" ht="44.25" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A41" s="356" t="str">
         <f>A3</f>
         <v>STEP 2 : BACK GROUND CALCULATION . NOT TO BE VISIBLE TO CUSTOMER</v>
       </c>
-      <c r="B41" s="360"/>
-      <c r="C41" s="360"/>
-      <c r="D41" s="360"/>
-      <c r="E41" s="360"/>
-      <c r="F41" s="360"/>
-    </row>
-    <row r="42" spans="1:14" ht="44.25" customHeight="1" x14ac:dyDescent="0.85">
+      <c r="B41" s="356"/>
+      <c r="C41" s="356"/>
+      <c r="D41" s="356"/>
+      <c r="E41" s="356"/>
+      <c r="F41" s="356"/>
+    </row>
+    <row r="42" spans="1:14" ht="44.25" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -7627,22 +7680,22 @@
       <c r="F42" s="1"/>
       <c r="N42" s="107"/>
     </row>
-    <row r="43" spans="1:14" ht="48.75" customHeight="1" x14ac:dyDescent="1">
-      <c r="A43" s="356" t="s">
+    <row r="43" spans="1:14" ht="48.75" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="A43" s="361" t="s">
         <v>218</v>
       </c>
-      <c r="B43" s="356"/>
-      <c r="C43" s="356"/>
-      <c r="D43" s="356"/>
-      <c r="E43" s="356"/>
-      <c r="F43" s="356"/>
+      <c r="B43" s="361"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
       <c r="H43" s="126"/>
     </row>
-    <row r="44" spans="1:14" ht="30.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="358" t="s">
+    <row r="44" spans="1:14" ht="30.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A44" s="354" t="s">
         <v>23</v>
       </c>
-      <c r="B44" s="358" t="s">
+      <c r="B44" s="354" t="s">
         <v>36</v>
       </c>
       <c r="C44" s="89" t="str">
@@ -7662,9 +7715,9 @@
         <v>Projected</v>
       </c>
     </row>
-    <row r="45" spans="1:14" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A45" s="359"/>
-      <c r="B45" s="359"/>
+    <row r="45" spans="1:14" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" s="355"/>
+      <c r="B45" s="355"/>
       <c r="C45" s="138">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -7683,17 +7736,17 @@
       </c>
       <c r="H45"/>
     </row>
-    <row r="46" spans="1:14" ht="33.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:14" ht="33.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.5">
       <c r="A46" s="43" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:14" ht="31" x14ac:dyDescent="0.7">
+    <row r="47" spans="1:14" ht="30.6" x14ac:dyDescent="0.55000000000000004">
       <c r="D47" s="141"/>
       <c r="E47" s="141"/>
       <c r="F47" s="141"/>
     </row>
-    <row r="48" spans="1:14" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:14" ht="42.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A48" s="2" t="s">
         <v>78</v>
       </c>
@@ -7716,20 +7769,20 @@
       <c r="G48" s="6"/>
       <c r="H48" s="6"/>
     </row>
-    <row r="49" spans="1:10" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:10" ht="42.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A49" s="56" t="s">
         <v>79</v>
       </c>
       <c r="B49" s="54"/>
       <c r="J49"/>
     </row>
-    <row r="50" spans="1:10" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:10" ht="42.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A50" s="3" t="s">
         <v>77</v>
       </c>
       <c r="B50" s="54"/>
     </row>
-    <row r="51" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A51" s="2" t="s">
         <v>137</v>
       </c>
@@ -7750,21 +7803,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:10" ht="42.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B52" s="54"/>
       <c r="C52" s="48"/>
       <c r="D52" s="48"/>
       <c r="E52" s="48"/>
       <c r="F52" s="48"/>
     </row>
-    <row r="53" spans="1:10" ht="36.75" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="54" spans="1:10" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:10" ht="36.75" customHeight="1" x14ac:dyDescent="0.5"/>
+    <row r="54" spans="1:10" ht="42.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A54" s="3" t="s">
         <v>84</v>
       </c>
       <c r="B54" s="1"/>
     </row>
-    <row r="55" spans="1:10" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:10" ht="42.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A55" s="2" t="s">
         <v>144</v>
       </c>
@@ -7787,7 +7840,7 @@
       </c>
       <c r="G55" s="48"/>
     </row>
-    <row r="56" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A56" s="2" t="s">
         <v>139</v>
       </c>
@@ -7805,19 +7858,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B57" s="54"/>
       <c r="C57" s="6"/>
       <c r="D57" s="6"/>
       <c r="E57" s="6"/>
       <c r="F57" s="6"/>
     </row>
-    <row r="58" spans="1:10" ht="48.75" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="58" spans="1:10" ht="48.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="3"/>
       <c r="B58" s="54"/>
       <c r="I58" s="132"/>
     </row>
-    <row r="59" spans="1:10" ht="47.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="59" spans="1:10" ht="47.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C59" s="12">
         <f>SUM(C48:C57)</f>
         <v>0</v>
@@ -7835,29 +7888,29 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="47.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="60" spans="1:10" ht="47.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C60" s="7"/>
       <c r="D60" s="7"/>
       <c r="E60" s="7"/>
       <c r="F60" s="7"/>
     </row>
-    <row r="61" spans="1:10" ht="26" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="C61" s="353" t="s">
+    <row r="61" spans="1:10" ht="26.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="C61" s="357" t="s">
         <v>164</v>
       </c>
-      <c r="D61" s="354"/>
-      <c r="E61" s="354"/>
-      <c r="F61" s="355"/>
-    </row>
-    <row r="62" spans="1:10" ht="36.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D61" s="358"/>
+      <c r="E61" s="358"/>
+      <c r="F61" s="359"/>
+    </row>
+    <row r="62" spans="1:10" ht="36.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A62" s="43" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="36.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:10" ht="36.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A63" s="5"/>
     </row>
-    <row r="64" spans="1:10" ht="36.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:10" ht="36.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A64" s="3" t="s">
         <v>80</v>
       </c>
@@ -7879,13 +7932,13 @@
       </c>
       <c r="G64" s="6"/>
     </row>
-    <row r="65" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="C65" s="6"/>
       <c r="D65" s="6"/>
       <c r="E65" s="6"/>
       <c r="F65" s="6"/>
     </row>
-    <row r="66" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A66" s="3" t="s">
         <v>140</v>
       </c>
@@ -7906,19 +7959,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="C67" s="6"/>
       <c r="D67" s="6"/>
       <c r="E67" s="6"/>
       <c r="F67" s="6"/>
     </row>
-    <row r="68" spans="1:14" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:14" ht="42.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A68" s="3" t="s">
         <v>81</v>
       </c>
       <c r="B68" s="54"/>
     </row>
-    <row r="69" spans="1:14" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:14" ht="42.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A69" s="2" t="s">
         <v>141</v>
       </c>
@@ -7936,7 +7989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:14" ht="42.75" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="70" spans="1:14" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="2" t="str">
         <f>A18</f>
         <v>Closing Stock</v>
@@ -7960,7 +8013,7 @@
       </c>
       <c r="I70" s="132"/>
     </row>
-    <row r="71" spans="1:14" ht="44.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:14" ht="44.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A71" s="2" t="s">
         <v>4</v>
       </c>
@@ -7982,7 +8035,7 @@
       </c>
       <c r="G71" s="6"/>
     </row>
-    <row r="72" spans="1:14" ht="39" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:14" ht="39" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A72" s="2" t="s">
         <v>65</v>
       </c>
@@ -8003,8 +8056,8 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="73" spans="1:14" ht="39" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="74" spans="1:14" ht="53.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="73" spans="1:14" ht="39" customHeight="1" x14ac:dyDescent="0.5"/>
+    <row r="74" spans="1:14" ht="53.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C74" s="12">
         <f>SUM(C64:C72)</f>
         <v>0</v>
@@ -8022,7 +8075,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="75" spans="1:14" ht="30.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:14" ht="30.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.5">
       <c r="C75" s="7">
         <f>C59-C74</f>
         <v>0</v>
@@ -8040,19 +8093,19 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="76" spans="1:14" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="76" spans="1:14" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C76" s="7"/>
       <c r="D76" s="7"/>
       <c r="E76" s="7"/>
       <c r="F76" s="7"/>
     </row>
-    <row r="77" spans="1:14" ht="53.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="C77" s="353" t="s">
+    <row r="77" spans="1:14" ht="53.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="C77" s="357" t="s">
         <v>164</v>
       </c>
-      <c r="D77" s="354"/>
-      <c r="E77" s="354"/>
-      <c r="F77" s="355"/>
+      <c r="D77" s="358"/>
+      <c r="E77" s="358"/>
+      <c r="F77" s="359"/>
       <c r="I77" s="132"/>
       <c r="J77" s="132"/>
       <c r="K77" s="132"/>
@@ -8060,16 +8113,16 @@
       <c r="M77" s="132"/>
       <c r="N77" s="133"/>
     </row>
-    <row r="78" spans="1:14" ht="51.75" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A78" s="360" t="str">
+    <row r="78" spans="1:14" ht="51.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A78" s="356" t="str">
         <f>A41</f>
         <v>STEP 2 : BACK GROUND CALCULATION . NOT TO BE VISIBLE TO CUSTOMER</v>
       </c>
-      <c r="B78" s="360"/>
-      <c r="C78" s="360"/>
-      <c r="D78" s="360"/>
-      <c r="E78" s="360"/>
-      <c r="F78" s="360"/>
+      <c r="B78" s="356"/>
+      <c r="C78" s="356"/>
+      <c r="D78" s="356"/>
+      <c r="E78" s="356"/>
+      <c r="F78" s="356"/>
       <c r="I78" s="132"/>
       <c r="J78" s="132"/>
       <c r="K78" s="132"/>
@@ -8077,15 +8130,15 @@
       <c r="M78" s="132"/>
       <c r="N78" s="133"/>
     </row>
-    <row r="79" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A79" s="357" t="s">
+    <row r="79" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A79" s="362" t="s">
         <v>219</v>
       </c>
-      <c r="B79" s="357"/>
-      <c r="C79" s="357"/>
-      <c r="D79" s="357"/>
-      <c r="E79" s="357"/>
-      <c r="F79" s="357"/>
+      <c r="B79" s="362"/>
+      <c r="C79" s="362"/>
+      <c r="D79" s="362"/>
+      <c r="E79" s="362"/>
+      <c r="F79" s="362"/>
       <c r="H79" s="132"/>
       <c r="I79" s="132"/>
       <c r="J79" s="132"/>
@@ -8094,7 +8147,7 @@
       <c r="M79" s="132"/>
       <c r="N79" s="133"/>
     </row>
-    <row r="80" spans="1:14" ht="95.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="80" spans="1:14" ht="95.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" s="57"/>
       <c r="B80" s="57"/>
       <c r="C80" s="58">
@@ -8114,11 +8167,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:12" ht="26" thickTop="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:12" ht="26.4" thickTop="1" x14ac:dyDescent="0.5"/>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.5">
       <c r="G82" s="6"/>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A83" s="2" t="s">
         <v>163</v>
       </c>
@@ -8140,7 +8193,7 @@
       </c>
       <c r="G83" s="6"/>
     </row>
-    <row r="84" spans="1:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A84" s="2" t="s">
         <v>70</v>
       </c>
@@ -8165,7 +8218,7 @@
       <c r="K84" s="6"/>
       <c r="L84" s="6"/>
     </row>
-    <row r="85" spans="1:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A85" s="2" t="s">
         <v>69</v>
       </c>
@@ -8190,7 +8243,7 @@
       <c r="K85" s="6"/>
       <c r="L85" s="6"/>
     </row>
-    <row r="86" spans="1:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A86" s="2" t="s">
         <v>76</v>
       </c>
@@ -8215,7 +8268,7 @@
       <c r="K86" s="6"/>
       <c r="L86" s="6"/>
     </row>
-    <row r="87" spans="1:12" ht="41.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:12" ht="41.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A87" s="2" t="s">
         <v>162</v>
       </c>
@@ -8239,16 +8292,16 @@
       <c r="J87" s="87"/>
       <c r="K87" s="87"/>
     </row>
-    <row r="88" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="D88" s="6"/>
       <c r="E88" s="6"/>
       <c r="F88" s="6"/>
     </row>
-    <row r="89" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="E89" s="6"/>
       <c r="F89" s="6"/>
     </row>
-    <row r="91" spans="1:12" ht="50.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:12" ht="50.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="C91" s="51">
         <f>SUM(C82:C89)</f>
         <v>0</v>
@@ -8266,44 +8319,44 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="92" spans="1:12" ht="50.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="92" spans="1:12" ht="50.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C92" s="3"/>
       <c r="D92" s="7"/>
       <c r="E92" s="7"/>
       <c r="F92" s="7"/>
     </row>
-    <row r="93" spans="1:12" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="C93" s="353" t="s">
+    <row r="93" spans="1:12" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="C93" s="357" t="s">
         <v>164</v>
       </c>
-      <c r="D93" s="354"/>
-      <c r="E93" s="354"/>
-      <c r="F93" s="355"/>
+      <c r="D93" s="358"/>
+      <c r="E93" s="358"/>
+      <c r="F93" s="359"/>
       <c r="I93" s="6"/>
     </row>
-    <row r="94" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A94" s="360" t="str">
+    <row r="94" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A94" s="356" t="str">
         <f>A78</f>
         <v>STEP 2 : BACK GROUND CALCULATION . NOT TO BE VISIBLE TO CUSTOMER</v>
       </c>
-      <c r="B94" s="360"/>
-      <c r="C94" s="360"/>
-      <c r="D94" s="360"/>
-      <c r="E94" s="360"/>
-      <c r="F94" s="360"/>
+      <c r="B94" s="356"/>
+      <c r="C94" s="356"/>
+      <c r="D94" s="356"/>
+      <c r="E94" s="356"/>
+      <c r="F94" s="356"/>
       <c r="I94" s="6"/>
     </row>
-    <row r="95" spans="1:12" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A95" s="357" t="s">
+    <row r="95" spans="1:12" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A95" s="362" t="s">
         <v>220</v>
       </c>
-      <c r="B95" s="357"/>
-      <c r="C95" s="357"/>
-      <c r="D95" s="357"/>
-      <c r="E95" s="357"/>
-      <c r="F95" s="357"/>
-    </row>
-    <row r="96" spans="1:12" ht="98.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B95" s="362"/>
+      <c r="C95" s="362"/>
+      <c r="D95" s="362"/>
+      <c r="E95" s="362"/>
+      <c r="F95" s="362"/>
+    </row>
+    <row r="96" spans="1:12" ht="98.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" s="57"/>
       <c r="B96" s="57"/>
       <c r="C96" s="58">
@@ -8323,13 +8376,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:6" ht="32.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:6" ht="32.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.5">
       <c r="C97" s="4"/>
       <c r="D97" s="4"/>
       <c r="E97" s="4"/>
       <c r="F97" s="4"/>
     </row>
-    <row r="98" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A98" s="2" t="s">
         <v>136</v>
       </c>
@@ -8350,7 +8403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A99" s="2" t="s">
         <v>75</v>
       </c>
@@ -8371,19 +8424,19 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="100" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.5">
       <c r="C100" s="48"/>
       <c r="D100" s="6"/>
       <c r="E100" s="6"/>
       <c r="F100" s="6"/>
     </row>
-    <row r="101" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="C101" s="48"/>
       <c r="D101" s="52"/>
       <c r="E101" s="52"/>
       <c r="F101" s="52"/>
     </row>
-    <row r="102" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="C102" s="51">
         <f>SUM(C98:C101)</f>
         <v>0</v>
@@ -8401,28 +8454,28 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="103" spans="1:6" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="103" spans="1:6" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C103" s="3"/>
       <c r="D103" s="3"/>
       <c r="E103" s="3"/>
     </row>
-    <row r="104" spans="1:6" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="C104" s="353" t="s">
+    <row r="104" spans="1:6" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="C104" s="357" t="s">
         <v>164</v>
       </c>
-      <c r="D104" s="354"/>
-      <c r="E104" s="354"/>
-      <c r="F104" s="355"/>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="D104" s="358"/>
+      <c r="E104" s="358"/>
+      <c r="F104" s="359"/>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A107" s="188" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A108" s="188"/>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A109" s="2" t="s">
         <v>269</v>
       </c>
@@ -8443,11 +8496,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A111" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="B111" s="257">
+      <c r="B111" s="254">
         <v>0.75</v>
       </c>
       <c r="C111" s="6">
@@ -8467,11 +8520,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A112" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B112" s="257">
+      <c r="B112" s="254">
         <v>0.5</v>
       </c>
       <c r="C112" s="6">
@@ -8491,13 +8544,13 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.5">
       <c r="C113" s="6"/>
       <c r="D113" s="6"/>
       <c r="E113" s="6"/>
       <c r="F113" s="6"/>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A114" s="2" t="s">
         <v>271</v>
       </c>
@@ -8520,18 +8573,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="A41:F41"/>
-    <mergeCell ref="C77:F77"/>
-    <mergeCell ref="M3:O3"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A39:F39"/>
-    <mergeCell ref="A40:F40"/>
-    <mergeCell ref="C37:F37"/>
     <mergeCell ref="C93:F93"/>
     <mergeCell ref="C104:F104"/>
     <mergeCell ref="A43:F43"/>
@@ -8542,6 +8583,18 @@
     <mergeCell ref="A78:F78"/>
     <mergeCell ref="A94:F94"/>
     <mergeCell ref="C61:F61"/>
+    <mergeCell ref="A41:F41"/>
+    <mergeCell ref="C77:F77"/>
+    <mergeCell ref="M3:O3"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.19685039370078741" top="0.39370078740157483" bottom="0.3" header="0.23622047244094491" footer="0.16"/>
@@ -8558,726 +8611,726 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:S46"/>
-  <sheetFormatPr defaultColWidth="21.81640625" defaultRowHeight="25.5" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="21.77734375" defaultRowHeight="25.8" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="79.26953125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.26953125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="27.26953125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="30.1796875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="31" style="2" customWidth="1"/>
-    <col min="6" max="16384" width="21.81640625" style="2"/>
+    <col min="1" max="1" width="79.21875" style="388" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.21875" style="388" customWidth="1"/>
+    <col min="3" max="3" width="27.21875" style="388" customWidth="1"/>
+    <col min="4" max="4" width="30.21875" style="388" customWidth="1"/>
+    <col min="5" max="5" width="31" style="388" customWidth="1"/>
+    <col min="6" max="16384" width="21.77734375" style="388"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="362"/>
-      <c r="B1" s="362"/>
-      <c r="C1" s="362"/>
-      <c r="D1" s="362"/>
-      <c r="E1" s="362"/>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="362"/>
-      <c r="B2" s="362"/>
-      <c r="C2" s="362"/>
-      <c r="D2" s="362"/>
-      <c r="E2" s="362"/>
-    </row>
-    <row r="3" spans="1:19" ht="29.25" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="A3" s="360" t="s">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="A1" s="387"/>
+      <c r="B1" s="387"/>
+      <c r="C1" s="387"/>
+      <c r="D1" s="387"/>
+      <c r="E1" s="387"/>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="A2" s="387"/>
+      <c r="B2" s="387"/>
+      <c r="C2" s="387"/>
+      <c r="D2" s="387"/>
+      <c r="E2" s="387"/>
+    </row>
+    <row r="3" spans="1:19" ht="29.25" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A3" s="389" t="s">
         <v>215</v>
       </c>
-      <c r="B3" s="360"/>
-      <c r="C3" s="360"/>
-      <c r="D3" s="360"/>
-      <c r="E3" s="360"/>
-      <c r="L3" s="107"/>
-      <c r="M3" s="107"/>
-      <c r="N3" s="107"/>
-    </row>
-    <row r="4" spans="1:19" ht="57" customHeight="1" x14ac:dyDescent="1">
-      <c r="A4" s="371" t="s">
+      <c r="B3" s="389"/>
+      <c r="C3" s="389"/>
+      <c r="D3" s="389"/>
+      <c r="E3" s="389"/>
+      <c r="L3" s="390"/>
+      <c r="M3" s="390"/>
+      <c r="N3" s="390"/>
+    </row>
+    <row r="4" spans="1:19" ht="57" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="A4" s="391" t="s">
         <v>214</v>
       </c>
-      <c r="B4" s="371"/>
-      <c r="C4" s="371"/>
-      <c r="D4" s="371"/>
-      <c r="E4" s="371"/>
-      <c r="G4" s="126"/>
-    </row>
-    <row r="5" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="364" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="89" t="str">
+      <c r="B4" s="391"/>
+      <c r="C4" s="391"/>
+      <c r="D4" s="391"/>
+      <c r="E4" s="391"/>
+      <c r="G4" s="392"/>
+    </row>
+    <row r="5" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="393" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="394" t="str">
         <f>wp!C44</f>
         <v xml:space="preserve">Audited </v>
       </c>
-      <c r="C5" s="89" t="str">
+      <c r="C5" s="394" t="str">
         <f>wp!D44</f>
         <v>Estimated</v>
       </c>
-      <c r="D5" s="89" t="str">
+      <c r="D5" s="394" t="str">
         <f>wp!E44</f>
         <v>Projected</v>
       </c>
-      <c r="E5" s="89" t="str">
+      <c r="E5" s="394" t="str">
         <f>wp!F44</f>
         <v>Projected</v>
       </c>
-      <c r="G5"/>
-    </row>
-    <row r="6" spans="1:19" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A6" s="365"/>
-      <c r="B6" s="138">
+      <c r="G5" s="395"/>
+    </row>
+    <row r="6" spans="1:19" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="396"/>
+      <c r="B6" s="397">
         <f>wp!C45</f>
         <v>0</v>
       </c>
-      <c r="C6" s="138">
+      <c r="C6" s="397">
         <f>wp!D45</f>
         <v>0</v>
       </c>
-      <c r="D6" s="138">
+      <c r="D6" s="397">
         <f>wp!E45</f>
         <v>0</v>
       </c>
-      <c r="E6" s="138">
+      <c r="E6" s="397">
         <f>wp!F45</f>
         <v>0</v>
       </c>
-      <c r="F6" s="3"/>
-    </row>
-    <row r="7" spans="1:19" ht="37.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="9"/>
-      <c r="B7" s="192" t="s">
+      <c r="F6" s="398"/>
+    </row>
+    <row r="7" spans="1:19" ht="37.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.5">
+      <c r="A7" s="399"/>
+      <c r="B7" s="400" t="s">
         <v>231</v>
       </c>
-      <c r="C7" s="192" t="s">
+      <c r="C7" s="400" t="s">
         <v>232</v>
       </c>
-      <c r="D7" s="192" t="s">
+      <c r="D7" s="400" t="s">
         <v>232</v>
       </c>
-      <c r="E7" s="192" t="s">
+      <c r="E7" s="400" t="s">
         <v>232</v>
       </c>
-      <c r="F7" s="3"/>
-    </row>
-    <row r="8" spans="1:19" s="3" customFormat="1" ht="53.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="188" t="s">
+      <c r="F7" s="398"/>
+    </row>
+    <row r="8" spans="1:19" s="398" customFormat="1" ht="53.25" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A8" s="401" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="9" spans="1:19" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:19" s="398" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="388" t="s">
         <v>302</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="413">
         <f>wp!C10</f>
         <v>0</v>
       </c>
-      <c r="C9" s="6" t="e">
+      <c r="C9" s="413" t="e">
         <f>wp!D10</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D9" s="6" t="e">
+      <c r="D9" s="413" t="e">
         <f>wp!E10</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E9" s="6" t="e">
+      <c r="E9" s="413" t="e">
         <f>wp!F10</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="37.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="2" t="s">
+    <row r="10" spans="1:19" ht="37.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A10" s="388" t="s">
         <v>96</v>
       </c>
-      <c r="B10" s="50">
+      <c r="B10" s="414">
         <f>wp!C17</f>
         <v>0</v>
       </c>
-      <c r="C10" s="48" t="e">
+      <c r="C10" s="415" t="e">
         <f>wp!D17</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D10" s="48" t="e">
+      <c r="D10" s="415" t="e">
         <f>wp!E17</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E10" s="48" t="e">
+      <c r="E10" s="415" t="e">
         <f>wp!F17</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K10"/>
-      <c r="S10" s="6"/>
-    </row>
-    <row r="11" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="2" t="s">
+      <c r="K10" s="395"/>
+      <c r="S10" s="402"/>
+    </row>
+    <row r="11" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A11" s="388" t="s">
         <v>298</v>
       </c>
-      <c r="B11" s="50">
+      <c r="B11" s="414">
         <f>wp!C18</f>
         <v>0</v>
       </c>
-      <c r="C11" s="50">
+      <c r="C11" s="414">
         <f>wp!D18</f>
         <v>0</v>
       </c>
-      <c r="D11" s="50">
+      <c r="D11" s="414">
         <f>wp!E18</f>
         <v>0</v>
       </c>
-      <c r="E11" s="48">
+      <c r="E11" s="415">
         <f>wp!F18</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:19" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="2" t="s">
+    <row r="12" spans="1:19" s="398" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A12" s="388" t="s">
         <v>188</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="413">
         <f>wp!C23</f>
         <v>0</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="413">
         <f>wp!D23</f>
         <v>0</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="413">
         <f>wp!E23</f>
         <v>0</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="413">
         <f>wp!F23</f>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:19" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="2" t="s">
+    <row r="13" spans="1:19" s="398" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A13" s="388" t="s">
         <v>163</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="416">
         <f>wp!C83</f>
         <v>0</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="413">
         <f>wp!D83</f>
         <v>0</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="413">
         <f>wp!E83</f>
         <v>0</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="413">
         <f>wp!F83</f>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:19" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="2" t="s">
+    <row r="14" spans="1:19" s="398" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A14" s="388" t="s">
         <v>70</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="416">
         <f>wp!C84</f>
         <v>0</v>
       </c>
-      <c r="C14" s="6" t="e">
+      <c r="C14" s="413" t="e">
         <f>wp!D84</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D14" s="6" t="e">
+      <c r="D14" s="413" t="e">
         <f>wp!E84</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E14" s="6" t="e">
+      <c r="E14" s="413" t="e">
         <f>wp!F84</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="15" spans="1:19" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="2" t="s">
+    <row r="15" spans="1:19" s="398" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A15" s="388" t="s">
         <v>69</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="416">
         <f>wp!C85</f>
         <v>0</v>
       </c>
-      <c r="C15" s="6" t="e">
+      <c r="C15" s="413" t="e">
         <f>wp!D85</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D15" s="6" t="e">
+      <c r="D15" s="413" t="e">
         <f>wp!E85</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E15" s="6" t="e">
+      <c r="E15" s="413" t="e">
         <f>wp!F85</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="16" spans="1:19" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="2" t="s">
+    <row r="16" spans="1:19" s="398" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A16" s="388" t="s">
         <v>162</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="416">
         <f>wp!C87</f>
         <v>0</v>
       </c>
-      <c r="C16" s="6" t="e">
+      <c r="C16" s="413" t="e">
         <f>wp!D87</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D16" s="6" t="e">
+      <c r="D16" s="413" t="e">
         <f>wp!E87</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E16" s="6" t="e">
+      <c r="E16" s="413" t="e">
         <f>wp!F87</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="17" spans="1:7" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="2" t="s">
+    <row r="17" spans="1:7" s="398" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A17" s="388" t="s">
         <v>136</v>
       </c>
-      <c r="B17" s="48">
+      <c r="B17" s="415">
         <f>wp!C98</f>
         <v>0</v>
       </c>
-      <c r="C17" s="48" t="e">
+      <c r="C17" s="415" t="e">
         <f>B17*C22/B22</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D17" s="48">
+      <c r="D17" s="415">
         <f>IF(C22=0,0,C17*D22/C22)</f>
         <v>0</v>
       </c>
-      <c r="E17" s="48">
+      <c r="E17" s="415">
         <f>IF(D22=0,0,D17*E22/D22)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="2" t="s">
+    <row r="18" spans="1:7" s="398" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A18" s="388" t="s">
         <v>75</v>
       </c>
-      <c r="B18" s="48">
+      <c r="B18" s="415">
         <f>wp!C99</f>
         <v>0</v>
       </c>
-      <c r="C18" s="48" t="e">
+      <c r="C18" s="415" t="e">
         <f>wp!D99</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D18" s="48" t="e">
+      <c r="D18" s="415" t="e">
         <f>wp!E99</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E18" s="48" t="e">
+      <c r="E18" s="415" t="e">
         <f>wp!F99</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="19" spans="1:7" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="2" t="s">
+    <row r="19" spans="1:7" s="398" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A19" s="388" t="s">
         <v>297</v>
       </c>
-      <c r="B19" s="48">
+      <c r="B19" s="403">
         <f>PLBS!C35</f>
         <v>0</v>
       </c>
-      <c r="C19" s="48" t="e">
+      <c r="C19" s="403" t="e">
         <f>PLBS!D35</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D19" s="48" t="e">
+      <c r="D19" s="403" t="e">
         <f>PLBS!E35</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E19" s="48" t="e">
+      <c r="E19" s="403" t="e">
         <f>PLBS!F35</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="20" spans="1:7" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="2"/>
-      <c r="B20" s="48"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-    </row>
-    <row r="21" spans="1:7" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="188" t="s">
+    <row r="20" spans="1:7" s="398" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A20" s="388"/>
+      <c r="B20" s="403"/>
+      <c r="C20" s="402"/>
+      <c r="D20" s="402"/>
+      <c r="E20" s="402"/>
+    </row>
+    <row r="21" spans="1:7" s="398" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A21" s="401" t="s">
         <v>229</v>
       </c>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-    </row>
-    <row r="22" spans="1:7" ht="39" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="2" t="s">
+      <c r="B21" s="402"/>
+      <c r="C21" s="402"/>
+      <c r="D21" s="402"/>
+      <c r="E21" s="402"/>
+    </row>
+    <row r="22" spans="1:7" ht="39" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A22" s="388" t="s">
         <v>230</v>
       </c>
-      <c r="B22" s="50">
+      <c r="B22" s="414">
         <f>wp!C51</f>
         <v>0</v>
       </c>
-      <c r="C22" s="48">
+      <c r="C22" s="415">
         <f>wp!D51</f>
         <v>0</v>
       </c>
-      <c r="D22" s="48">
+      <c r="D22" s="415">
         <f>wp!E51</f>
         <v>0</v>
       </c>
-      <c r="E22" s="48">
+      <c r="E22" s="415">
         <f>wp!F51</f>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="2" t="s">
+    <row r="23" spans="1:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A23" s="388" t="s">
         <v>144</v>
       </c>
-      <c r="B23" s="48">
+      <c r="B23" s="415">
         <f>wp!C55</f>
         <v>0</v>
       </c>
-      <c r="C23" s="48" t="e">
+      <c r="C23" s="415" t="e">
         <f>wp!D55</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D23" s="48" t="e">
+      <c r="D23" s="415" t="e">
         <f>wp!E55</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E23" s="48" t="e">
+      <c r="E23" s="415" t="e">
         <f>wp!F55</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F23" s="48"/>
-    </row>
-    <row r="24" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="2" t="s">
+      <c r="F23" s="403"/>
+    </row>
+    <row r="24" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A24" s="388" t="s">
         <v>139</v>
       </c>
-      <c r="B24" s="2">
+      <c r="B24" s="416">
         <f>wp!C56</f>
         <v>0</v>
       </c>
-      <c r="C24" s="2">
+      <c r="C24" s="416">
         <f>wp!D56</f>
         <v>0</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D24" s="416">
         <f>wp!E56</f>
         <v>0</v>
       </c>
-      <c r="E24" s="2">
+      <c r="E24" s="416">
         <f>wp!F56</f>
         <v>0</v>
       </c>
-      <c r="G24" s="191"/>
-    </row>
-    <row r="25" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="2" t="s">
+      <c r="G24" s="404"/>
+    </row>
+    <row r="25" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A25" s="388" t="s">
         <v>204</v>
       </c>
-      <c r="B25" s="2">
+      <c r="B25" s="416">
         <f>wp!C66</f>
         <v>0</v>
       </c>
-      <c r="C25" s="2">
+      <c r="C25" s="416">
         <f>wp!D66</f>
         <v>0</v>
       </c>
-      <c r="D25" s="2">
+      <c r="D25" s="416">
         <f>wp!E66</f>
         <v>0</v>
       </c>
-      <c r="E25" s="2">
+      <c r="E25" s="416">
         <f>wp!F66</f>
         <v>0</v>
       </c>
-      <c r="G25" s="191"/>
-    </row>
-    <row r="26" spans="1:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="2" t="s">
+      <c r="G25" s="404"/>
+    </row>
+    <row r="26" spans="1:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A26" s="388" t="s">
         <v>141</v>
       </c>
-      <c r="B26" s="2">
+      <c r="B26" s="416">
         <f>wp!C69</f>
         <v>0</v>
       </c>
-      <c r="C26" s="2">
+      <c r="C26" s="416">
         <f>wp!D69</f>
         <v>0</v>
       </c>
-      <c r="D26" s="2">
+      <c r="D26" s="416">
         <f>wp!E69</f>
         <v>0</v>
       </c>
-      <c r="E26" s="2">
+      <c r="E26" s="416">
         <f>wp!F69</f>
         <v>0</v>
       </c>
-      <c r="G26" s="191"/>
-    </row>
-    <row r="27" spans="1:7" ht="44.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="2" t="s">
+      <c r="G26" s="404"/>
+    </row>
+    <row r="27" spans="1:7" ht="44.25" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A27" s="388" t="s">
         <v>4</v>
       </c>
-      <c r="B27" s="2">
+      <c r="B27" s="416">
         <f>wp!C71</f>
         <v>0</v>
       </c>
-      <c r="C27" s="6" t="e">
+      <c r="C27" s="413" t="e">
         <f>wp!D71</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D27" s="6" t="e">
+      <c r="D27" s="413" t="e">
         <f>wp!E71</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E27" s="6" t="e">
+      <c r="E27" s="413" t="e">
         <f>wp!F71</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="39" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="2" t="s">
+    <row r="28" spans="1:7" ht="39" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A28" s="388" t="s">
         <v>65</v>
       </c>
-      <c r="B28" s="2">
+      <c r="B28" s="416">
         <f>wp!C72</f>
         <v>0</v>
       </c>
-      <c r="C28" s="2" t="e">
+      <c r="C28" s="416" t="e">
         <f>wp!D72</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D28" s="2" t="e">
+      <c r="D28" s="416" t="e">
         <f>wp!E72</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E28" s="2" t="e">
+      <c r="E28" s="416" t="e">
         <f>wp!F72</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B29" s="48"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
-    </row>
-    <row r="30" spans="1:7" ht="44.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="188" t="s">
+    <row r="29" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B29" s="403"/>
+      <c r="C29" s="402"/>
+      <c r="D29" s="402"/>
+      <c r="E29" s="402"/>
+    </row>
+    <row r="30" spans="1:7" ht="44.25" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A30" s="401" t="s">
         <v>233</v>
       </c>
-      <c r="B30" s="48"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
-    </row>
-    <row r="31" spans="1:7" ht="41.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="2" t="s">
+      <c r="B30" s="403"/>
+      <c r="C30" s="402"/>
+      <c r="D30" s="402"/>
+      <c r="E30" s="402"/>
+    </row>
+    <row r="31" spans="1:7" ht="41.25" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A31" s="388" t="s">
         <v>222</v>
       </c>
-      <c r="B31" s="189" t="e">
+      <c r="B31" s="405" t="e">
         <f>RATIO!C22</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="C31" s="189" t="e">
+      <c r="C31" s="405" t="e">
         <f>RATIO!D22</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D31" s="189" t="e">
+      <c r="D31" s="405" t="e">
         <f>RATIO!E22</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E31" s="189" t="e">
+      <c r="E31" s="405" t="e">
         <f>RATIO!F22</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="2" t="s">
+    <row r="32" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A32" s="388" t="s">
         <v>223</v>
       </c>
-      <c r="B32" s="87" t="e">
+      <c r="B32" s="406" t="e">
         <f>RATIO!C30</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="C32" s="87" t="e">
+      <c r="C32" s="406" t="e">
         <f>RATIO!D30</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D32" s="87" t="e">
+      <c r="D32" s="406" t="e">
         <f>RATIO!E30</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E32" s="87" t="e">
+      <c r="E32" s="406" t="e">
         <f>RATIO!F30</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="2" t="s">
+    <row r="33" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A33" s="388" t="s">
         <v>224</v>
       </c>
-      <c r="B33" s="87" t="e">
+      <c r="B33" s="406" t="e">
         <f>RATIO!C46</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="C33" s="87" t="e">
+      <c r="C33" s="406" t="e">
         <f>RATIO!D46</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D33" s="87" t="e">
+      <c r="D33" s="406" t="e">
         <f>RATIO!E46</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E33" s="87" t="e">
+      <c r="E33" s="406" t="e">
         <f>RATIO!F46</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="39.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="2" t="s">
+    <row r="34" spans="1:5" ht="39.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A34" s="388" t="s">
         <v>212</v>
       </c>
-      <c r="B34" s="87" t="e">
+      <c r="B34" s="406" t="e">
         <f>RATIO!C11</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="C34" s="87" t="e">
+      <c r="C34" s="406" t="e">
         <f>RATIO!D11</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D34" s="87" t="e">
+      <c r="D34" s="406" t="e">
         <f>RATIO!E11</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E34" s="87" t="e">
+      <c r="E34" s="406" t="e">
         <f>RATIO!F11</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="2" t="s">
+    <row r="35" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A35" s="388" t="s">
         <v>213</v>
       </c>
-      <c r="B35" s="87" t="e">
+      <c r="B35" s="406" t="e">
         <f>RATIO!C56</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="C35" s="87" t="e">
+      <c r="C35" s="406" t="e">
         <f>RATIO!D56</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D35" s="87" t="e">
+      <c r="D35" s="406" t="e">
         <f>RATIO!E56</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E35" s="87" t="e">
+      <c r="E35" s="406" t="e">
         <f>RATIO!F56</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B36" s="87"/>
-      <c r="C36" s="87"/>
-      <c r="D36" s="87"/>
-      <c r="E36" s="87"/>
-    </row>
-    <row r="37" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="188" t="s">
+    <row r="36" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B36" s="406"/>
+      <c r="C36" s="406"/>
+      <c r="D36" s="406"/>
+      <c r="E36" s="406"/>
+    </row>
+    <row r="37" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A37" s="401" t="s">
         <v>293</v>
       </c>
-      <c r="B37" s="87"/>
-      <c r="C37" s="87"/>
-      <c r="D37" s="87"/>
-      <c r="E37" s="87"/>
-    </row>
-    <row r="38" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="2" t="s">
+      <c r="B37" s="406"/>
+      <c r="C37" s="406"/>
+      <c r="D37" s="406"/>
+      <c r="E37" s="406"/>
+    </row>
+    <row r="38" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A38" s="388" t="s">
         <v>294</v>
       </c>
-      <c r="B38" s="87"/>
-      <c r="C38" s="6" t="e">
+      <c r="B38" s="417"/>
+      <c r="C38" s="413" t="e">
         <f>'MPBF '!B28</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D38" s="6" t="e">
+      <c r="D38" s="413" t="e">
         <f>'MPBF '!C28</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E38" s="6" t="e">
+      <c r="E38" s="413" t="e">
         <f>'MPBF '!D28</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="2" t="s">
+    <row r="39" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A39" s="388" t="s">
         <v>295</v>
       </c>
-      <c r="B39" s="87"/>
-      <c r="C39" s="6" t="e">
+      <c r="B39" s="417"/>
+      <c r="C39" s="413" t="e">
         <f>'MPBF '!B55</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D39" s="6" t="e">
+      <c r="D39" s="413" t="e">
         <f>'MPBF '!C55</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E39" s="6" t="e">
+      <c r="E39" s="413" t="e">
         <f>'MPBF '!D55</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="2" t="s">
+    <row r="40" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A40" s="388" t="s">
         <v>296</v>
       </c>
-      <c r="B40" s="87"/>
-      <c r="C40" s="6" t="e">
+      <c r="B40" s="417"/>
+      <c r="C40" s="413" t="e">
         <f>nayak!C23</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D40" s="6" t="e">
+      <c r="D40" s="413" t="e">
         <f>nayak!D23</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E40" s="6" t="e">
+      <c r="E40" s="413" t="e">
         <f>nayak!E23</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="26" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A41" s="11"/>
-      <c r="B41" s="11"/>
-      <c r="C41" s="11"/>
-      <c r="D41" s="11"/>
-      <c r="E41" s="11"/>
-    </row>
-    <row r="42" spans="1:5" ht="26" thickBot="1" x14ac:dyDescent="0.6"/>
-    <row r="43" spans="1:5" ht="30.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B43" s="367"/>
-      <c r="C43" s="368"/>
-    </row>
-    <row r="44" spans="1:5" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B44" s="369"/>
-      <c r="C44" s="370"/>
-    </row>
-    <row r="46" spans="1:5" ht="31" x14ac:dyDescent="0.7">
-      <c r="A46" s="366"/>
-      <c r="B46" s="366"/>
-      <c r="C46" s="366"/>
-      <c r="D46" s="366"/>
-      <c r="E46" s="366"/>
+    <row r="41" spans="1:5" ht="26.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="407"/>
+      <c r="B41" s="407"/>
+      <c r="C41" s="407"/>
+      <c r="D41" s="407"/>
+      <c r="E41" s="407"/>
+    </row>
+    <row r="42" spans="1:5" ht="26.4" thickBot="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="43" spans="1:5" ht="30.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B43" s="408"/>
+      <c r="C43" s="409"/>
+    </row>
+    <row r="44" spans="1:5" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B44" s="410"/>
+      <c r="C44" s="411"/>
+    </row>
+    <row r="46" spans="1:5" ht="30.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" s="412"/>
+      <c r="B46" s="412"/>
+      <c r="C46" s="412"/>
+      <c r="D46" s="412"/>
+      <c r="E46" s="412"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -9297,27 +9350,27 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B1:V38"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="23" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="23.4" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="2" width="5.453125" style="68" customWidth="1"/>
+    <col min="1" max="2" width="5.44140625" style="68" customWidth="1"/>
     <col min="3" max="3" width="8" style="68" customWidth="1"/>
     <col min="4" max="4" width="11" style="68" customWidth="1"/>
-    <col min="5" max="5" width="10.54296875" style="68" customWidth="1"/>
-    <col min="6" max="6" width="11.7265625" style="68" customWidth="1"/>
-    <col min="7" max="7" width="12.54296875" style="68" customWidth="1"/>
-    <col min="8" max="8" width="12.453125" style="68" customWidth="1"/>
-    <col min="9" max="9" width="9.1796875" style="68"/>
-    <col min="10" max="11" width="9.1796875" style="68" customWidth="1"/>
+    <col min="5" max="5" width="10.5546875" style="68" customWidth="1"/>
+    <col min="6" max="6" width="11.77734375" style="68" customWidth="1"/>
+    <col min="7" max="7" width="12.5546875" style="68" customWidth="1"/>
+    <col min="8" max="8" width="12.44140625" style="68" customWidth="1"/>
+    <col min="9" max="9" width="9.21875" style="68"/>
+    <col min="10" max="11" width="9.21875" style="68" customWidth="1"/>
     <col min="12" max="12" width="6" style="68" customWidth="1"/>
-    <col min="13" max="13" width="5.54296875" style="68" customWidth="1"/>
-    <col min="14" max="19" width="9.1796875" style="68"/>
-    <col min="20" max="20" width="73.1796875" style="68" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="32.453125" style="68" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.1796875" style="68"/>
+    <col min="13" max="13" width="5.5546875" style="68" customWidth="1"/>
+    <col min="14" max="19" width="9.21875" style="68"/>
+    <col min="20" max="20" width="73.21875" style="68" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="32.44140625" style="68" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.21875" style="68"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:22" ht="23.5" thickBot="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="2" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="1" spans="2:22" ht="24" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="2" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B2" s="71"/>
       <c r="C2" s="72"/>
       <c r="D2" s="72"/>
@@ -9330,7 +9383,7 @@
       <c r="K2" s="72"/>
       <c r="L2" s="73"/>
     </row>
-    <row r="3" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="3" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B3" s="74"/>
       <c r="C3" s="75"/>
       <c r="D3" s="75"/>
@@ -9343,7 +9396,7 @@
       <c r="K3" s="75"/>
       <c r="L3" s="76"/>
     </row>
-    <row r="4" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="4" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B4" s="74"/>
       <c r="C4" s="75"/>
       <c r="D4" s="75"/>
@@ -9356,51 +9409,51 @@
       <c r="K4" s="75"/>
       <c r="L4" s="76"/>
     </row>
-    <row r="5" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="5" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B5" s="74"/>
       <c r="C5" s="75"/>
       <c r="K5" s="75"/>
       <c r="L5" s="76"/>
     </row>
-    <row r="6" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="6" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B6" s="74"/>
       <c r="C6" s="75"/>
-      <c r="D6" s="372" t="s">
+      <c r="D6" s="364" t="s">
         <v>272</v>
       </c>
-      <c r="E6" s="372"/>
-      <c r="F6" s="372"/>
-      <c r="G6" s="372"/>
-      <c r="H6" s="372"/>
-      <c r="I6" s="372"/>
-      <c r="J6" s="372"/>
-      <c r="K6" s="252"/>
+      <c r="E6" s="364"/>
+      <c r="F6" s="364"/>
+      <c r="G6" s="364"/>
+      <c r="H6" s="364"/>
+      <c r="I6" s="364"/>
+      <c r="J6" s="364"/>
+      <c r="K6" s="249"/>
       <c r="L6" s="76"/>
     </row>
-    <row r="7" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="7" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B7" s="74"/>
       <c r="C7" s="75"/>
       <c r="K7" s="75"/>
       <c r="L7" s="76"/>
     </row>
-    <row r="8" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="8" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B8" s="74"/>
       <c r="C8" s="75"/>
-      <c r="E8" s="372" t="s">
+      <c r="E8" s="364" t="s">
         <v>93</v>
       </c>
-      <c r="F8" s="372"/>
-      <c r="G8" s="372"/>
-      <c r="H8" s="372"/>
-      <c r="I8" s="372"/>
+      <c r="F8" s="364"/>
+      <c r="G8" s="364"/>
+      <c r="H8" s="364"/>
+      <c r="I8" s="364"/>
       <c r="J8" s="66"/>
-      <c r="K8" s="252"/>
+      <c r="K8" s="249"/>
       <c r="L8" s="76"/>
       <c r="T8" s="67" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="9" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="9" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B9" s="74"/>
       <c r="C9" s="75"/>
       <c r="E9" s="66"/>
@@ -9409,27 +9462,27 @@
       <c r="H9" s="66"/>
       <c r="I9" s="66"/>
       <c r="J9" s="66"/>
-      <c r="K9" s="252"/>
+      <c r="K9" s="249"/>
       <c r="L9" s="76"/>
       <c r="T9" s="67"/>
     </row>
-    <row r="10" spans="2:22" ht="32.25" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="10" spans="2:22" ht="32.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B10" s="74"/>
       <c r="C10" s="75"/>
-      <c r="D10" s="372">
+      <c r="D10" s="364">
         <f>Assumptions.1!I3</f>
         <v>0</v>
       </c>
-      <c r="E10" s="372"/>
-      <c r="F10" s="372"/>
-      <c r="G10" s="372"/>
-      <c r="H10" s="372"/>
-      <c r="I10" s="372"/>
-      <c r="J10" s="372"/>
-      <c r="K10" s="252"/>
+      <c r="E10" s="364"/>
+      <c r="F10" s="364"/>
+      <c r="G10" s="364"/>
+      <c r="H10" s="364"/>
+      <c r="I10" s="364"/>
+      <c r="J10" s="364"/>
+      <c r="K10" s="249"/>
       <c r="L10" s="76"/>
     </row>
-    <row r="11" spans="2:22" ht="32.25" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="11" spans="2:22" ht="32.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B11" s="74"/>
       <c r="C11" s="75"/>
       <c r="D11" s="66"/>
@@ -9439,51 +9492,51 @@
       <c r="H11" s="66"/>
       <c r="I11" s="66"/>
       <c r="J11" s="66"/>
-      <c r="K11" s="252"/>
+      <c r="K11" s="249"/>
       <c r="L11" s="76"/>
-      <c r="T11" s="249" t="s">
+      <c r="T11" s="246" t="s">
         <v>252</v>
       </c>
-      <c r="U11" s="249" t="s">
+      <c r="U11" s="246" t="s">
         <v>253</v>
       </c>
       <c r="V11" s="67"/>
     </row>
-    <row r="12" spans="2:22" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="12" spans="2:22" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B12" s="74"/>
       <c r="C12" s="75"/>
       <c r="K12" s="75"/>
       <c r="L12" s="76"/>
-      <c r="T12" s="250" t="s">
+      <c r="T12" s="247" t="s">
         <v>254</v>
       </c>
-      <c r="U12" s="250" t="s">
+      <c r="U12" s="247" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="13" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="13" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B13" s="74"/>
       <c r="C13" s="75"/>
-      <c r="D13" s="372">
+      <c r="D13" s="364">
         <f>Assumptions.1!I5</f>
         <v>0</v>
       </c>
-      <c r="E13" s="372"/>
-      <c r="F13" s="372"/>
-      <c r="G13" s="372"/>
-      <c r="H13" s="372"/>
-      <c r="I13" s="372"/>
-      <c r="J13" s="372"/>
-      <c r="K13" s="252"/>
+      <c r="E13" s="364"/>
+      <c r="F13" s="364"/>
+      <c r="G13" s="364"/>
+      <c r="H13" s="364"/>
+      <c r="I13" s="364"/>
+      <c r="J13" s="364"/>
+      <c r="K13" s="249"/>
       <c r="L13" s="76"/>
-      <c r="T13" s="250" t="s">
+      <c r="T13" s="247" t="s">
         <v>250</v>
       </c>
-      <c r="U13" s="250" t="s">
+      <c r="U13" s="247" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="14" spans="2:22" ht="23.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="2:22" ht="24" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B14" s="74"/>
       <c r="C14" s="75"/>
       <c r="E14" s="69"/>
@@ -9493,172 +9546,172 @@
       <c r="I14" s="69"/>
       <c r="K14" s="75"/>
       <c r="L14" s="76"/>
-      <c r="T14" s="250" t="s">
+      <c r="T14" s="247" t="s">
         <v>256</v>
       </c>
-      <c r="U14" s="250" t="s">
+      <c r="U14" s="247" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="15" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="15" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B15" s="74"/>
       <c r="C15" s="75"/>
       <c r="K15" s="75"/>
       <c r="L15" s="76"/>
-      <c r="T15" s="250" t="s">
+      <c r="T15" s="247" t="s">
         <v>258</v>
       </c>
-      <c r="U15" s="250" t="s">
+      <c r="U15" s="247" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="16" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="16" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B16" s="74"/>
       <c r="C16" s="75"/>
-      <c r="D16" s="373"/>
-      <c r="E16" s="373"/>
-      <c r="F16" s="373"/>
-      <c r="G16" s="373"/>
-      <c r="H16" s="373"/>
-      <c r="I16" s="373"/>
-      <c r="J16" s="373"/>
-      <c r="K16" s="253"/>
+      <c r="D16" s="365"/>
+      <c r="E16" s="365"/>
+      <c r="F16" s="365"/>
+      <c r="G16" s="365"/>
+      <c r="H16" s="365"/>
+      <c r="I16" s="365"/>
+      <c r="J16" s="365"/>
+      <c r="K16" s="250"/>
       <c r="L16" s="76"/>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.5">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B17" s="74"/>
       <c r="C17" s="75"/>
       <c r="K17" s="75"/>
       <c r="L17" s="76"/>
     </row>
-    <row r="18" spans="2:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="18" spans="2:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B18" s="74"/>
       <c r="C18" s="75"/>
-      <c r="D18" s="374">
+      <c r="D18" s="366">
         <f>Assumptions.1!I8</f>
         <v>0</v>
       </c>
-      <c r="E18" s="374"/>
-      <c r="F18" s="374"/>
-      <c r="G18" s="374"/>
-      <c r="H18" s="374"/>
-      <c r="I18" s="374"/>
-      <c r="J18" s="374"/>
-      <c r="K18" s="251"/>
+      <c r="E18" s="366"/>
+      <c r="F18" s="366"/>
+      <c r="G18" s="366"/>
+      <c r="H18" s="366"/>
+      <c r="I18" s="366"/>
+      <c r="J18" s="366"/>
+      <c r="K18" s="248"/>
       <c r="L18" s="78"/>
     </row>
-    <row r="19" spans="2:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="19" spans="2:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B19" s="74"/>
       <c r="C19" s="75"/>
-      <c r="D19" s="374"/>
-      <c r="E19" s="374"/>
-      <c r="F19" s="374"/>
-      <c r="G19" s="374"/>
-      <c r="H19" s="374"/>
-      <c r="I19" s="374"/>
-      <c r="J19" s="374"/>
-      <c r="K19" s="251"/>
+      <c r="D19" s="366"/>
+      <c r="E19" s="366"/>
+      <c r="F19" s="366"/>
+      <c r="G19" s="366"/>
+      <c r="H19" s="366"/>
+      <c r="I19" s="366"/>
+      <c r="J19" s="366"/>
+      <c r="K19" s="248"/>
       <c r="L19" s="78"/>
     </row>
-    <row r="20" spans="2:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="20" spans="2:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B20" s="74"/>
       <c r="C20" s="75"/>
-      <c r="D20" s="374"/>
-      <c r="E20" s="374"/>
-      <c r="F20" s="374"/>
-      <c r="G20" s="374"/>
-      <c r="H20" s="374"/>
-      <c r="I20" s="374"/>
-      <c r="J20" s="374"/>
-      <c r="K20" s="251"/>
+      <c r="D20" s="366"/>
+      <c r="E20" s="366"/>
+      <c r="F20" s="366"/>
+      <c r="G20" s="366"/>
+      <c r="H20" s="366"/>
+      <c r="I20" s="366"/>
+      <c r="J20" s="366"/>
+      <c r="K20" s="248"/>
       <c r="L20" s="78"/>
     </row>
-    <row r="21" spans="2:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="21" spans="2:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B21" s="74"/>
       <c r="C21" s="75"/>
-      <c r="D21" s="374"/>
-      <c r="E21" s="374"/>
-      <c r="F21" s="374"/>
-      <c r="G21" s="374"/>
-      <c r="H21" s="374"/>
-      <c r="I21" s="374"/>
-      <c r="J21" s="374"/>
-      <c r="K21" s="251"/>
+      <c r="D21" s="366"/>
+      <c r="E21" s="366"/>
+      <c r="F21" s="366"/>
+      <c r="G21" s="366"/>
+      <c r="H21" s="366"/>
+      <c r="I21" s="366"/>
+      <c r="J21" s="366"/>
+      <c r="K21" s="248"/>
       <c r="L21" s="78"/>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.5">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B22" s="74"/>
       <c r="C22" s="75"/>
-      <c r="D22" s="375">
+      <c r="D22" s="367">
         <f>Assumptions.1!I6</f>
         <v>0</v>
       </c>
-      <c r="E22" s="375"/>
-      <c r="F22" s="375"/>
-      <c r="G22" s="375"/>
-      <c r="H22" s="375"/>
-      <c r="I22" s="375"/>
-      <c r="J22" s="375"/>
-      <c r="K22" s="254"/>
+      <c r="E22" s="367"/>
+      <c r="F22" s="367"/>
+      <c r="G22" s="367"/>
+      <c r="H22" s="367"/>
+      <c r="I22" s="367"/>
+      <c r="J22" s="367"/>
+      <c r="K22" s="251"/>
       <c r="L22" s="76"/>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.5">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B23" s="74"/>
       <c r="C23" s="75"/>
-      <c r="D23" s="375"/>
-      <c r="E23" s="375"/>
-      <c r="F23" s="375"/>
-      <c r="G23" s="375"/>
-      <c r="H23" s="375"/>
-      <c r="I23" s="375"/>
-      <c r="J23" s="375"/>
-      <c r="K23" s="254"/>
+      <c r="D23" s="367"/>
+      <c r="E23" s="367"/>
+      <c r="F23" s="367"/>
+      <c r="G23" s="367"/>
+      <c r="H23" s="367"/>
+      <c r="I23" s="367"/>
+      <c r="J23" s="367"/>
+      <c r="K23" s="251"/>
       <c r="L23" s="76"/>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.5">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B24" s="74"/>
       <c r="C24" s="75"/>
-      <c r="D24" s="375"/>
-      <c r="E24" s="375"/>
-      <c r="F24" s="375"/>
-      <c r="G24" s="375"/>
-      <c r="H24" s="375"/>
-      <c r="I24" s="375"/>
-      <c r="J24" s="375"/>
-      <c r="K24" s="254"/>
+      <c r="D24" s="367"/>
+      <c r="E24" s="367"/>
+      <c r="F24" s="367"/>
+      <c r="G24" s="367"/>
+      <c r="H24" s="367"/>
+      <c r="I24" s="367"/>
+      <c r="J24" s="367"/>
+      <c r="K24" s="251"/>
       <c r="L24" s="76"/>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.5">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B25" s="74"/>
       <c r="C25" s="75"/>
-      <c r="E25" s="376"/>
-      <c r="F25" s="376"/>
+      <c r="E25" s="368"/>
+      <c r="F25" s="368"/>
       <c r="G25" s="67"/>
       <c r="H25" s="67"/>
       <c r="I25" s="67"/>
       <c r="J25" s="66"/>
-      <c r="K25" s="252"/>
+      <c r="K25" s="249"/>
       <c r="L25" s="76"/>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.5">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B26" s="74"/>
       <c r="C26" s="75"/>
-      <c r="D26" s="372" t="s">
+      <c r="D26" s="364" t="s">
         <v>292</v>
       </c>
-      <c r="E26" s="372"/>
-      <c r="F26" s="372"/>
-      <c r="G26" s="372"/>
-      <c r="H26" s="372">
+      <c r="E26" s="364"/>
+      <c r="F26" s="364"/>
+      <c r="G26" s="364"/>
+      <c r="H26" s="364">
         <f>Assumptions.1!I12</f>
         <v>0</v>
       </c>
-      <c r="I26" s="372"/>
-      <c r="J26" s="372"/>
-      <c r="K26" s="252"/>
+      <c r="I26" s="364"/>
+      <c r="J26" s="364"/>
+      <c r="K26" s="249"/>
       <c r="L26" s="76"/>
     </row>
-    <row r="27" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="27" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B27" s="74"/>
       <c r="C27" s="75"/>
       <c r="E27" s="67"/>
@@ -9668,7 +9721,7 @@
       <c r="K27" s="75"/>
       <c r="L27" s="78"/>
     </row>
-    <row r="28" spans="2:12" ht="23.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B28" s="74"/>
       <c r="C28" s="75"/>
       <c r="E28" s="69"/>
@@ -9679,27 +9732,27 @@
       <c r="K28" s="75"/>
       <c r="L28" s="76"/>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.5">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B29" s="74"/>
       <c r="C29" s="75"/>
       <c r="K29" s="75"/>
       <c r="L29" s="76"/>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.5">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B30" s="74"/>
       <c r="C30" s="75"/>
-      <c r="E30" s="377" t="s">
+      <c r="E30" s="369" t="s">
         <v>94</v>
       </c>
-      <c r="F30" s="377"/>
-      <c r="G30" s="377"/>
-      <c r="H30" s="377"/>
-      <c r="I30" s="377"/>
+      <c r="F30" s="369"/>
+      <c r="G30" s="369"/>
+      <c r="H30" s="369"/>
+      <c r="I30" s="369"/>
       <c r="J30" s="70"/>
-      <c r="K30" s="255"/>
+      <c r="K30" s="252"/>
       <c r="L30" s="76"/>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.5">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B31" s="74"/>
       <c r="C31" s="75"/>
       <c r="E31" s="67"/>
@@ -9708,55 +9761,55 @@
       <c r="H31" s="67"/>
       <c r="I31" s="67"/>
       <c r="J31" s="67"/>
-      <c r="K31" s="256"/>
+      <c r="K31" s="253"/>
       <c r="L31" s="76"/>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.5">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B32" s="74"/>
       <c r="C32" s="75"/>
-      <c r="D32" s="372" t="s">
+      <c r="D32" s="364" t="s">
         <v>235</v>
       </c>
-      <c r="E32" s="372"/>
-      <c r="F32" s="372"/>
-      <c r="G32" s="372"/>
-      <c r="H32" s="372"/>
-      <c r="I32" s="372"/>
-      <c r="J32" s="372"/>
-      <c r="K32" s="252"/>
+      <c r="E32" s="364"/>
+      <c r="F32" s="364"/>
+      <c r="G32" s="364"/>
+      <c r="H32" s="364"/>
+      <c r="I32" s="364"/>
+      <c r="J32" s="364"/>
+      <c r="K32" s="249"/>
       <c r="L32" s="76"/>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.5">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B33" s="74"/>
       <c r="C33" s="75"/>
-      <c r="D33" s="372" t="s">
+      <c r="D33" s="364" t="s">
         <v>234</v>
       </c>
-      <c r="E33" s="372"/>
-      <c r="F33" s="372"/>
-      <c r="G33" s="372"/>
-      <c r="H33" s="372"/>
-      <c r="I33" s="372"/>
-      <c r="J33" s="372"/>
-      <c r="K33" s="252"/>
+      <c r="E33" s="364"/>
+      <c r="F33" s="364"/>
+      <c r="G33" s="364"/>
+      <c r="H33" s="364"/>
+      <c r="I33" s="364"/>
+      <c r="J33" s="364"/>
+      <c r="K33" s="249"/>
       <c r="L33" s="76"/>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.5">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B34" s="74"/>
       <c r="C34" s="75"/>
-      <c r="D34" s="372" t="s">
+      <c r="D34" s="364" t="s">
         <v>236</v>
       </c>
-      <c r="E34" s="372"/>
-      <c r="F34" s="372"/>
-      <c r="G34" s="372"/>
-      <c r="H34" s="372"/>
-      <c r="I34" s="372"/>
-      <c r="J34" s="372"/>
-      <c r="K34" s="252"/>
+      <c r="E34" s="364"/>
+      <c r="F34" s="364"/>
+      <c r="G34" s="364"/>
+      <c r="H34" s="364"/>
+      <c r="I34" s="364"/>
+      <c r="J34" s="364"/>
+      <c r="K34" s="249"/>
       <c r="L34" s="76"/>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.5">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B35" s="74"/>
       <c r="C35" s="75"/>
       <c r="E35" s="67"/>
@@ -9765,10 +9818,10 @@
       <c r="H35" s="67"/>
       <c r="I35" s="67"/>
       <c r="J35" s="67"/>
-      <c r="K35" s="256"/>
+      <c r="K35" s="253"/>
       <c r="L35" s="76"/>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.5">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B36" s="74"/>
       <c r="C36" s="75"/>
       <c r="D36" s="75"/>
@@ -9781,7 +9834,7 @@
       <c r="K36" s="75"/>
       <c r="L36" s="76"/>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.5">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B37" s="74"/>
       <c r="C37" s="75"/>
       <c r="D37" s="75"/>
@@ -9794,7 +9847,7 @@
       <c r="K37" s="75"/>
       <c r="L37" s="76"/>
     </row>
-    <row r="38" spans="2:12" ht="23.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B38" s="77"/>
       <c r="C38" s="80"/>
       <c r="D38" s="80"/>
@@ -9809,6 +9862,11 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="E8:I8"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D33:J33"/>
     <mergeCell ref="D34:J34"/>
     <mergeCell ref="D16:J16"/>
     <mergeCell ref="D18:J21"/>
@@ -9818,11 +9876,6 @@
     <mergeCell ref="D26:G26"/>
     <mergeCell ref="D32:J32"/>
     <mergeCell ref="E30:I30"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="E8:I8"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D33:J33"/>
   </mergeCells>
   <pageMargins left="0.26" right="0.17" top="0.43307086614173229" bottom="0.2" header="0.31496062992125984" footer="0.16"/>
   <pageSetup scale="87" orientation="portrait" r:id="rId1"/>
@@ -9832,67 +9885,67 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:V96"/>
-  <sheetFormatPr defaultColWidth="21.81640625" defaultRowHeight="25.5" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="21.77734375" defaultRowHeight="25.8" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="66.1796875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="66.21875" style="2" customWidth="1"/>
     <col min="2" max="2" width="19" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="21.81640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="21.81640625" style="2"/>
+    <col min="3" max="3" width="20.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="21.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="21.77734375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="362">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.5">
+      <c r="A1" s="350">
         <f>Assumptions.1!I3</f>
         <v>0</v>
       </c>
-      <c r="B1" s="362"/>
-      <c r="C1" s="362"/>
-      <c r="D1" s="362"/>
-      <c r="E1" s="362"/>
-      <c r="F1" s="362"/>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="362">
+      <c r="B1" s="350"/>
+      <c r="C1" s="350"/>
+      <c r="D1" s="350"/>
+      <c r="E1" s="350"/>
+      <c r="F1" s="350"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.5">
+      <c r="A2" s="350">
         <f>Assumptions.1!I5</f>
         <v>0</v>
       </c>
-      <c r="B2" s="362"/>
-      <c r="C2" s="362"/>
-      <c r="D2" s="362"/>
-      <c r="E2" s="362"/>
-      <c r="F2" s="362"/>
-    </row>
-    <row r="3" spans="1:15" ht="29.25" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="A3" s="362">
+      <c r="B2" s="350"/>
+      <c r="C2" s="350"/>
+      <c r="D2" s="350"/>
+      <c r="E2" s="350"/>
+      <c r="F2" s="350"/>
+    </row>
+    <row r="3" spans="1:15" ht="29.25" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A3" s="350">
         <f>Assumptions.1!I6</f>
         <v>0</v>
       </c>
-      <c r="B3" s="362"/>
-      <c r="C3" s="362"/>
-      <c r="D3" s="362"/>
-      <c r="E3" s="362"/>
-      <c r="F3" s="362"/>
+      <c r="B3" s="350"/>
+      <c r="C3" s="350"/>
+      <c r="D3" s="350"/>
+      <c r="E3" s="350"/>
+      <c r="F3" s="350"/>
       <c r="M3" s="107"/>
       <c r="N3" s="107"/>
       <c r="O3" s="107"/>
     </row>
-    <row r="4" spans="1:15" ht="57" customHeight="1" x14ac:dyDescent="1">
-      <c r="A4" s="371" t="s">
+    <row r="4" spans="1:15" ht="57" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="A4" s="363" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="371"/>
-      <c r="C4" s="371"/>
-      <c r="D4" s="371"/>
-      <c r="E4" s="371"/>
-      <c r="F4" s="371"/>
+      <c r="B4" s="363"/>
+      <c r="C4" s="363"/>
+      <c r="D4" s="363"/>
+      <c r="E4" s="363"/>
+      <c r="F4" s="363"/>
       <c r="H4" s="126"/>
     </row>
-    <row r="5" spans="1:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="364" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="358" t="s">
+    <row r="5" spans="1:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="352" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="354" t="s">
         <v>36</v>
       </c>
       <c r="C5" s="89" t="str">
@@ -9913,9 +9966,9 @@
       </c>
       <c r="H5"/>
     </row>
-    <row r="6" spans="1:15" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A6" s="365"/>
-      <c r="B6" s="359"/>
+    <row r="6" spans="1:15" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="353"/>
+      <c r="B6" s="355"/>
       <c r="C6" s="138">
         <f>FinalWorkings!B6</f>
         <v>0</v>
@@ -9934,10 +9987,10 @@
       </c>
       <c r="G6" s="3"/>
     </row>
-    <row r="7" spans="1:15" s="3" customFormat="1" ht="26" thickTop="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:15" s="3" customFormat="1" ht="26.4" thickTop="1" x14ac:dyDescent="0.5">
       <c r="E7" s="4"/>
     </row>
-    <row r="8" spans="1:15" s="3" customFormat="1" ht="31" x14ac:dyDescent="0.7">
+    <row r="8" spans="1:15" s="3" customFormat="1" ht="30.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="5" t="s">
         <v>303</v>
       </c>
@@ -9945,12 +9998,12 @@
       <c r="E8" s="141"/>
       <c r="F8" s="141"/>
     </row>
-    <row r="9" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A9" s="5"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
     </row>
-    <row r="10" spans="1:15" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:15" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A10" s="2" t="s">
         <v>304</v>
       </c>
@@ -9972,7 +10025,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="11" spans="1:15" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:15" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="6"/>
@@ -9980,7 +10033,7 @@
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
     </row>
-    <row r="12" spans="1:15" ht="38.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:15" ht="38.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="C12" s="7">
         <f>SUM(C10:C11)</f>
         <v>0</v>
@@ -9998,15 +10051,15 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.5">
       <c r="A14" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.5">
       <c r="A15" s="5"/>
     </row>
-    <row r="16" spans="1:15" ht="35.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:15" ht="35.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A16" s="2" t="s">
         <v>1</v>
       </c>
@@ -10028,7 +10081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:22" ht="37.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:22" ht="37.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A17" s="2" t="s">
         <v>96</v>
       </c>
@@ -10052,7 +10105,7 @@
       <c r="L17"/>
       <c r="T17" s="6"/>
     </row>
-    <row r="18" spans="1:22" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:22" ht="36" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A18" s="2" t="s">
         <v>298</v>
       </c>
@@ -10074,7 +10127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:22" ht="39.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:22" ht="39.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A19" s="3" t="s">
         <v>66</v>
       </c>
@@ -10095,12 +10148,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="20" spans="1:22" ht="46.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:22" ht="46.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A20" s="5"/>
       <c r="C20" s="3"/>
       <c r="D20" s="6"/>
     </row>
-    <row r="21" spans="1:22" s="3" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:22" s="3" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A21" s="5" t="s">
         <v>187</v>
       </c>
@@ -10126,14 +10179,14 @@
       <c r="K21" s="82"/>
       <c r="L21" s="82"/>
     </row>
-    <row r="22" spans="1:22" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:22" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A22" s="5"/>
       <c r="C22" s="135"/>
       <c r="D22" s="135"/>
       <c r="E22" s="135"/>
       <c r="F22" s="135"/>
     </row>
-    <row r="23" spans="1:22" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:22" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A23" s="2" t="s">
         <v>188</v>
       </c>
@@ -10155,7 +10208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:22" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:22" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A24" s="2"/>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
@@ -10163,7 +10216,7 @@
       <c r="F24" s="7"/>
       <c r="V24"/>
     </row>
-    <row r="25" spans="1:22" ht="43.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:22" ht="43.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A25" s="2" t="s">
         <v>238</v>
       </c>
@@ -10192,7 +10245,7 @@
       <c r="K25" s="86"/>
       <c r="L25" s="86"/>
     </row>
-    <row r="26" spans="1:22" ht="43.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:22" ht="43.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B26" s="10"/>
       <c r="H26" s="83"/>
       <c r="I26" s="83"/>
@@ -10200,7 +10253,7 @@
       <c r="K26" s="83"/>
       <c r="L26" s="83"/>
     </row>
-    <row r="27" spans="1:22" ht="43.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:22" ht="43.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A27" s="5" t="s">
         <v>189</v>
       </c>
@@ -10227,7 +10280,7 @@
       <c r="K27" s="83"/>
       <c r="L27" s="83"/>
     </row>
-    <row r="28" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A28" s="3"/>
       <c r="B28" s="10"/>
       <c r="H28" s="86"/>
@@ -10236,7 +10289,7 @@
       <c r="K28" s="86"/>
       <c r="L28" s="86"/>
     </row>
-    <row r="29" spans="1:22" ht="43.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:22" ht="43.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A29" s="2" t="s">
         <v>190</v>
       </c>
@@ -10263,7 +10316,7 @@
       <c r="K29" s="83"/>
       <c r="L29" s="83"/>
     </row>
-    <row r="30" spans="1:22" ht="43.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:22" ht="43.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B30" s="10"/>
       <c r="C30" s="6"/>
       <c r="D30" s="6"/>
@@ -10275,7 +10328,7 @@
       <c r="K30" s="83"/>
       <c r="L30" s="83"/>
     </row>
-    <row r="31" spans="1:22" s="15" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:22" s="15" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A31" s="5" t="s">
         <v>191</v>
       </c>
@@ -10301,7 +10354,7 @@
       <c r="K31" s="84"/>
       <c r="L31" s="84"/>
     </row>
-    <row r="32" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A32" s="3"/>
       <c r="D32" s="6"/>
       <c r="E32" s="6"/>
@@ -10312,7 +10365,7 @@
       <c r="K32" s="83"/>
       <c r="L32" s="83"/>
     </row>
-    <row r="33" spans="1:14" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:14" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A33" s="2" t="s">
         <v>192</v>
       </c>
@@ -10341,14 +10394,14 @@
       <c r="K33" s="83"/>
       <c r="L33" s="83"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.5">
       <c r="H34" s="83"/>
       <c r="I34" s="83"/>
       <c r="J34" s="83"/>
       <c r="K34" s="83"/>
       <c r="L34" s="83"/>
     </row>
-    <row r="35" spans="1:14" s="3" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:14" s="3" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A35" s="8" t="s">
         <v>193</v>
       </c>
@@ -10375,7 +10428,7 @@
       <c r="K35" s="85"/>
       <c r="L35" s="85"/>
     </row>
-    <row r="36" spans="1:14" ht="26" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="36" spans="1:14" ht="26.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="11"/>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -10383,46 +10436,46 @@
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.5">
       <c r="C37" s="120"/>
       <c r="D37" s="120"/>
       <c r="E37" s="120"/>
       <c r="F37" s="120"/>
     </row>
-    <row r="38" spans="1:14" ht="35.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="362">
+    <row r="38" spans="1:14" ht="35.25" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A38" s="350">
         <f>A1</f>
         <v>0</v>
       </c>
-      <c r="B38" s="362"/>
-      <c r="C38" s="362"/>
-      <c r="D38" s="362"/>
-      <c r="E38" s="362"/>
-      <c r="F38" s="362"/>
-    </row>
-    <row r="39" spans="1:14" ht="39" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="362">
+      <c r="B38" s="350"/>
+      <c r="C38" s="350"/>
+      <c r="D38" s="350"/>
+      <c r="E38" s="350"/>
+      <c r="F38" s="350"/>
+    </row>
+    <row r="39" spans="1:14" ht="39" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A39" s="350">
         <f>A2</f>
         <v>0</v>
       </c>
-      <c r="B39" s="362"/>
-      <c r="C39" s="362"/>
-      <c r="D39" s="362"/>
-      <c r="E39" s="362"/>
-      <c r="F39" s="362"/>
-    </row>
-    <row r="40" spans="1:14" ht="44.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="362">
+      <c r="B39" s="350"/>
+      <c r="C39" s="350"/>
+      <c r="D39" s="350"/>
+      <c r="E39" s="350"/>
+      <c r="F39" s="350"/>
+    </row>
+    <row r="40" spans="1:14" ht="44.25" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A40" s="350">
         <f>A3</f>
         <v>0</v>
       </c>
-      <c r="B40" s="362"/>
-      <c r="C40" s="362"/>
-      <c r="D40" s="362"/>
-      <c r="E40" s="362"/>
-      <c r="F40" s="362"/>
-    </row>
-    <row r="41" spans="1:14" ht="44.25" customHeight="1" x14ac:dyDescent="0.85">
+      <c r="B40" s="350"/>
+      <c r="C40" s="350"/>
+      <c r="D40" s="350"/>
+      <c r="E40" s="350"/>
+      <c r="F40" s="350"/>
+    </row>
+    <row r="41" spans="1:14" ht="44.25" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -10431,22 +10484,22 @@
       <c r="F41" s="1"/>
       <c r="N41" s="107"/>
     </row>
-    <row r="42" spans="1:14" ht="48.75" customHeight="1" x14ac:dyDescent="1">
-      <c r="A42" s="371" t="s">
+    <row r="42" spans="1:14" ht="48.75" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="A42" s="363" t="s">
         <v>10</v>
       </c>
-      <c r="B42" s="371"/>
-      <c r="C42" s="371"/>
-      <c r="D42" s="371"/>
-      <c r="E42" s="371"/>
-      <c r="F42" s="371"/>
+      <c r="B42" s="363"/>
+      <c r="C42" s="363"/>
+      <c r="D42" s="363"/>
+      <c r="E42" s="363"/>
+      <c r="F42" s="363"/>
       <c r="H42" s="126"/>
     </row>
-    <row r="43" spans="1:14" ht="30.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="358" t="s">
+    <row r="43" spans="1:14" ht="30.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A43" s="354" t="s">
         <v>23</v>
       </c>
-      <c r="B43" s="358" t="s">
+      <c r="B43" s="354" t="s">
         <v>36</v>
       </c>
       <c r="C43" s="89" t="str">
@@ -10466,9 +10519,9 @@
         <v>Projected</v>
       </c>
     </row>
-    <row r="44" spans="1:14" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A44" s="359"/>
-      <c r="B44" s="359"/>
+    <row r="44" spans="1:14" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="355"/>
+      <c r="B44" s="355"/>
       <c r="C44" s="138">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -10487,17 +10540,17 @@
       </c>
       <c r="H44"/>
     </row>
-    <row r="45" spans="1:14" ht="33.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:14" ht="33.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.5">
       <c r="A45" s="43" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:14" ht="31" x14ac:dyDescent="0.7">
+    <row r="46" spans="1:14" ht="30.6" x14ac:dyDescent="0.55000000000000004">
       <c r="D46" s="141"/>
       <c r="E46" s="141"/>
       <c r="F46" s="141"/>
     </row>
-    <row r="47" spans="1:14" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:14" ht="42.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A47" s="2" t="s">
         <v>305</v>
       </c>
@@ -10520,20 +10573,20 @@
       <c r="G47" s="6"/>
       <c r="H47" s="6"/>
     </row>
-    <row r="48" spans="1:14" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:14" ht="42.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A48" s="56" t="s">
         <v>79</v>
       </c>
       <c r="B48" s="54"/>
       <c r="J48"/>
     </row>
-    <row r="49" spans="1:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A49" s="3" t="s">
         <v>77</v>
       </c>
       <c r="B49" s="54"/>
     </row>
-    <row r="50" spans="1:7" ht="39" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:7" ht="39" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A50" s="2" t="s">
         <v>137</v>
       </c>
@@ -10554,20 +10607,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B51" s="54"/>
       <c r="C51" s="48"/>
       <c r="D51" s="48"/>
       <c r="E51" s="48"/>
       <c r="F51" s="48"/>
     </row>
-    <row r="52" spans="1:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A52" s="3" t="s">
         <v>84</v>
       </c>
       <c r="B52" s="1"/>
     </row>
-    <row r="53" spans="1:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A53" s="2" t="s">
         <v>144</v>
       </c>
@@ -10590,7 +10643,7 @@
       </c>
       <c r="G53" s="48"/>
     </row>
-    <row r="54" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A54" s="2" t="s">
         <v>139</v>
       </c>
@@ -10611,14 +10664,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B55" s="54"/>
       <c r="C55" s="6"/>
       <c r="D55" s="6"/>
       <c r="E55" s="6"/>
       <c r="F55" s="6"/>
     </row>
-    <row r="56" spans="1:7" ht="47.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="56" spans="1:7" ht="47.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C56" s="12">
         <f>SUM(C47:C55)</f>
         <v>0</v>
@@ -10636,21 +10689,21 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="47.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:7" ht="47.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.5">
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
       <c r="E57" s="7"/>
       <c r="F57" s="7"/>
     </row>
-    <row r="58" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A58" s="43" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A59" s="5"/>
     </row>
-    <row r="60" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A60" s="3" t="s">
         <v>80</v>
       </c>
@@ -10672,13 +10725,13 @@
       </c>
       <c r="G60" s="6"/>
     </row>
-    <row r="61" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="C61" s="6"/>
       <c r="D61" s="6"/>
       <c r="E61" s="6"/>
       <c r="F61" s="6"/>
     </row>
-    <row r="62" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A62" s="3" t="s">
         <v>140</v>
       </c>
@@ -10699,19 +10752,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="C63" s="6"/>
       <c r="D63" s="6"/>
       <c r="E63" s="6"/>
       <c r="F63" s="6"/>
     </row>
-    <row r="64" spans="1:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A64" s="3" t="s">
         <v>81</v>
       </c>
       <c r="B64" s="54"/>
     </row>
-    <row r="65" spans="1:14" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:14" ht="42.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A65" s="2" t="s">
         <v>141</v>
       </c>
@@ -10732,7 +10785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:14" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:14" ht="42.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A66" s="2" t="str">
         <f>A18</f>
         <v>Closing Stock / WIP</v>
@@ -10755,7 +10808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:14" ht="44.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:14" ht="44.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A67" s="2" t="s">
         <v>4</v>
       </c>
@@ -10777,7 +10830,7 @@
       </c>
       <c r="G67" s="6"/>
     </row>
-    <row r="68" spans="1:14" ht="39" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:14" ht="39" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A68" s="2" t="s">
         <v>65</v>
       </c>
@@ -10798,8 +10851,8 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="69" spans="1:14" ht="39" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="70" spans="1:14" ht="53.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="69" spans="1:14" ht="39" customHeight="1" x14ac:dyDescent="0.5"/>
+    <row r="70" spans="1:14" ht="53.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C70" s="12">
         <f>SUM(C60:C69)</f>
         <v>0</v>
@@ -10817,7 +10870,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="71" spans="1:14" ht="30.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="71" spans="1:14" ht="30.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="11"/>
       <c r="B71" s="11"/>
       <c r="C71" s="142">
@@ -10837,7 +10890,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="72" spans="1:14" ht="51.75" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="72" spans="1:14" ht="51.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C72" s="7"/>
       <c r="D72" s="7"/>
       <c r="E72" s="7"/>
@@ -10850,15 +10903,15 @@
       <c r="M72" s="139"/>
       <c r="N72" s="140"/>
     </row>
-    <row r="73" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A73" s="371" t="s">
+    <row r="73" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A73" s="363" t="s">
         <v>37</v>
       </c>
-      <c r="B73" s="371"/>
-      <c r="C73" s="371"/>
-      <c r="D73" s="371"/>
-      <c r="E73" s="371"/>
-      <c r="F73" s="371"/>
+      <c r="B73" s="363"/>
+      <c r="C73" s="363"/>
+      <c r="D73" s="363"/>
+      <c r="E73" s="363"/>
+      <c r="F73" s="363"/>
       <c r="H73" s="139"/>
       <c r="I73" s="139"/>
       <c r="J73" s="139"/>
@@ -10867,7 +10920,7 @@
       <c r="M73" s="139"/>
       <c r="N73" s="140"/>
     </row>
-    <row r="74" spans="1:14" ht="95.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="74" spans="1:14" ht="95.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="57"/>
       <c r="B74" s="57"/>
       <c r="C74" s="58">
@@ -10887,11 +10940,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:14" ht="26" thickTop="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:14" ht="26.4" thickTop="1" x14ac:dyDescent="0.5"/>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.5">
       <c r="G76" s="6"/>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.5">
       <c r="A77" s="2" t="s">
         <v>163</v>
       </c>
@@ -10913,7 +10966,7 @@
       </c>
       <c r="G77" s="6"/>
     </row>
-    <row r="78" spans="1:14" ht="35.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:14" ht="35.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A78" s="2" t="s">
         <v>70</v>
       </c>
@@ -10938,7 +10991,7 @@
       <c r="K78" s="6"/>
       <c r="L78" s="6"/>
     </row>
-    <row r="79" spans="1:14" ht="35.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:14" ht="35.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A79" s="2" t="s">
         <v>69</v>
       </c>
@@ -10963,7 +11016,7 @@
       <c r="K79" s="6"/>
       <c r="L79" s="6"/>
     </row>
-    <row r="80" spans="1:14" ht="35.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:14" ht="35.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A80" s="2" t="s">
         <v>76</v>
       </c>
@@ -10988,7 +11041,7 @@
       <c r="K80" s="6"/>
       <c r="L80" s="6"/>
     </row>
-    <row r="81" spans="1:11" ht="41.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:11" ht="41.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A81" s="2" t="s">
         <v>300</v>
       </c>
@@ -11012,16 +11065,16 @@
       <c r="J81" s="87"/>
       <c r="K81" s="87"/>
     </row>
-    <row r="82" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="D82" s="6"/>
       <c r="E82" s="6"/>
       <c r="F82" s="6"/>
     </row>
-    <row r="83" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="E83" s="6"/>
       <c r="F83" s="6"/>
     </row>
-    <row r="85" spans="1:11" ht="50.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:11" ht="50.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="C85" s="51">
         <f>SUM(C75:C84)</f>
         <v>0</v>
@@ -11039,24 +11092,24 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="86" spans="1:11" ht="34.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:11" ht="34.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="C86" s="68"/>
       <c r="D86" s="68"/>
       <c r="E86" s="68"/>
       <c r="F86" s="68"/>
       <c r="I86" s="6"/>
     </row>
-    <row r="87" spans="1:11" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A87" s="371" t="s">
+    <row r="87" spans="1:11" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A87" s="363" t="s">
         <v>38</v>
       </c>
-      <c r="B87" s="371"/>
-      <c r="C87" s="371"/>
-      <c r="D87" s="371"/>
-      <c r="E87" s="371"/>
-      <c r="F87" s="371"/>
-    </row>
-    <row r="88" spans="1:11" ht="98.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B87" s="363"/>
+      <c r="C87" s="363"/>
+      <c r="D87" s="363"/>
+      <c r="E87" s="363"/>
+      <c r="F87" s="363"/>
+    </row>
+    <row r="88" spans="1:11" ht="98.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="57"/>
       <c r="B88" s="57"/>
       <c r="C88" s="58">
@@ -11076,13 +11129,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:11" ht="32.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:11" ht="32.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.5">
       <c r="C89" s="4"/>
       <c r="D89" s="4"/>
       <c r="E89" s="4"/>
       <c r="F89" s="4"/>
     </row>
-    <row r="90" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A90" s="2" t="s">
         <v>136</v>
       </c>
@@ -11103,7 +11156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A91" s="2" t="s">
         <v>306</v>
       </c>
@@ -11124,19 +11177,19 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="92" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.5">
       <c r="C92" s="48"/>
       <c r="D92" s="6"/>
       <c r="E92" s="6"/>
       <c r="F92" s="6"/>
     </row>
-    <row r="93" spans="1:11" ht="34.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:11" ht="34.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="C93" s="48"/>
       <c r="D93" s="52"/>
       <c r="E93" s="52"/>
       <c r="F93" s="52"/>
     </row>
-    <row r="94" spans="1:11" ht="46.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:11" ht="46.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="C94" s="51">
         <f>SUM(C89:C93)</f>
         <v>0</v>
@@ -11154,12 +11207,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="95" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
     </row>
-    <row r="96" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="C96" s="68"/>
       <c r="D96" s="68"/>
       <c r="E96" s="68"/>
@@ -11167,12 +11220,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
     <mergeCell ref="A73:F73"/>
     <mergeCell ref="A87:F87"/>
     <mergeCell ref="A38:F38"/>
@@ -11181,6 +11228,12 @@
     <mergeCell ref="A42:F42"/>
     <mergeCell ref="A43:A44"/>
     <mergeCell ref="B43:B44"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
   </mergeCells>
   <pageMargins left="0.56000000000000005" right="0.15748031496062992" top="0.39370078740157483" bottom="0.44" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="53" orientation="portrait" r:id="rId1"/>
@@ -11193,61 +11246,61 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:I112"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="27.54296875" style="17" customWidth="1"/>
-    <col min="2" max="2" width="11.453125" style="17" customWidth="1"/>
-    <col min="3" max="5" width="12.453125" style="17" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.54296875" style="17" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.26953125" style="17" customWidth="1"/>
-    <col min="8" max="16384" width="9.1796875" style="17"/>
+    <col min="1" max="1" width="27.5546875" style="17" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" style="17" customWidth="1"/>
+    <col min="3" max="5" width="12.44140625" style="17" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5546875" style="17" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="17" customWidth="1"/>
+    <col min="8" max="16384" width="9.21875" style="17"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="378">
+    <row r="1" spans="1:7" ht="15" x14ac:dyDescent="0.35">
+      <c r="A1" s="370">
         <f>Assumptions.1!I3</f>
         <v>0</v>
       </c>
-      <c r="B1" s="378"/>
-      <c r="C1" s="378"/>
-      <c r="D1" s="378"/>
-      <c r="E1" s="378"/>
-      <c r="F1" s="378"/>
+      <c r="B1" s="370"/>
+      <c r="C1" s="370"/>
+      <c r="D1" s="370"/>
+      <c r="E1" s="370"/>
+      <c r="F1" s="370"/>
       <c r="G1" s="40"/>
     </row>
-    <row r="2" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="378">
+    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.35">
+      <c r="A2" s="370">
         <f>Assumptions.1!I5</f>
         <v>0</v>
       </c>
-      <c r="B2" s="378"/>
-      <c r="C2" s="378"/>
-      <c r="D2" s="378"/>
-      <c r="E2" s="378"/>
-      <c r="F2" s="378"/>
+      <c r="B2" s="370"/>
+      <c r="C2" s="370"/>
+      <c r="D2" s="370"/>
+      <c r="E2" s="370"/>
+      <c r="F2" s="370"/>
       <c r="G2" s="40"/>
     </row>
-    <row r="3" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="378">
+    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.35">
+      <c r="A3" s="370">
         <f>Assumptions.1!I6</f>
         <v>0</v>
       </c>
-      <c r="B3" s="378"/>
-      <c r="C3" s="378"/>
-      <c r="D3" s="378"/>
-      <c r="E3" s="378"/>
-      <c r="F3" s="378"/>
+      <c r="B3" s="370"/>
+      <c r="C3" s="370"/>
+      <c r="D3" s="370"/>
+      <c r="E3" s="370"/>
+      <c r="F3" s="370"/>
       <c r="G3" s="40"/>
     </row>
-    <row r="5" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="379" t="s">
+    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.35">
+      <c r="A5" s="371" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="379"/>
-      <c r="C5" s="379"/>
-      <c r="D5" s="379"/>
-      <c r="E5" s="379"/>
-      <c r="F5" s="379"/>
+      <c r="B5" s="371"/>
+      <c r="C5" s="371"/>
+      <c r="D5" s="371"/>
+      <c r="E5" s="371"/>
+      <c r="F5" s="371"/>
       <c r="G5" s="16"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
@@ -11260,7 +11313,7 @@
       <c r="G6" s="16"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" s="258" t="s">
+      <c r="A7" s="255" t="s">
         <v>260</v>
       </c>
       <c r="B7" s="16"/>
@@ -11271,11 +11324,11 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="36"/>
-      <c r="D8" s="385" t="s">
+      <c r="D8" s="377" t="s">
         <v>276</v>
       </c>
-      <c r="E8" s="385"/>
-      <c r="F8" s="385"/>
+      <c r="E8" s="377"/>
+      <c r="F8" s="377"/>
       <c r="G8" s="16"/>
     </row>
     <row r="9" spans="1:7" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -11301,7 +11354,7 @@
       </c>
       <c r="G9" s="16"/>
     </row>
-    <row r="10" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="16.2" x14ac:dyDescent="0.35">
       <c r="E10" s="34"/>
       <c r="G10" s="16"/>
     </row>
@@ -11383,7 +11436,7 @@
       <c r="E15" s="32"/>
       <c r="G15" s="16"/>
     </row>
-    <row r="16" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="21" t="s">
         <v>59</v>
       </c>
@@ -11404,7 +11457,7 @@
       <c r="G17" s="16"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A18" s="258" t="s">
+      <c r="A18" s="255" t="s">
         <v>82</v>
       </c>
       <c r="G18" s="16"/>
@@ -11467,7 +11520,7 @@
       <c r="E23" s="26"/>
       <c r="G23" s="16"/>
     </row>
-    <row r="24" spans="1:7" ht="14" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="33" t="s">
         <v>57</v>
       </c>
@@ -11478,18 +11531,18 @@
       <c r="F24" s="21"/>
       <c r="G24" s="16"/>
     </row>
-    <row r="25" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" ht="16.2" x14ac:dyDescent="0.35">
       <c r="E25" s="34"/>
       <c r="G25" s="16"/>
     </row>
-    <row r="26" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A26" s="258" t="s">
+    <row r="26" spans="1:7" ht="16.2" x14ac:dyDescent="0.35">
+      <c r="A26" s="255" t="s">
         <v>83</v>
       </c>
       <c r="E26" s="34"/>
       <c r="G26" s="16"/>
     </row>
-    <row r="27" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" ht="16.2" x14ac:dyDescent="0.35">
       <c r="A27" s="36"/>
       <c r="E27" s="34"/>
       <c r="G27" s="16"/>
@@ -11517,7 +11570,7 @@
       </c>
       <c r="G28" s="16"/>
     </row>
-    <row r="29" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" ht="16.2" x14ac:dyDescent="0.35">
       <c r="E29" s="34"/>
       <c r="G29" s="16"/>
     </row>
@@ -11549,7 +11602,7 @@
       <c r="E31" s="26"/>
       <c r="G31" s="16"/>
     </row>
-    <row r="32" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="33" t="s">
         <v>58</v>
       </c>
@@ -11597,7 +11650,7 @@
       <c r="G36" s="16"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A37" s="259" t="s">
+      <c r="A37" s="256" t="s">
         <v>261</v>
       </c>
     </row>
@@ -11624,7 +11677,7 @@
       </c>
       <c r="G38" s="25"/>
     </row>
-    <row r="39" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" ht="15" x14ac:dyDescent="0.35">
       <c r="A39" s="24"/>
       <c r="B39" s="27"/>
       <c r="C39" s="25"/>
@@ -11654,23 +11707,23 @@
       <c r="G40" s="26"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A41" s="388" t="s">
+      <c r="A41" s="380" t="s">
         <v>19</v>
       </c>
-      <c r="B41" s="388"/>
+      <c r="B41" s="380"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A43" s="386" t="s">
+      <c r="A43" s="378" t="s">
         <v>63</v>
       </c>
-      <c r="B43" s="387"/>
-      <c r="C43" s="387"/>
-      <c r="D43" s="387"/>
-      <c r="E43" s="387"/>
-      <c r="F43" s="387"/>
-      <c r="G43" s="387"/>
-      <c r="H43" s="387"/>
-      <c r="I43" s="387"/>
+      <c r="B43" s="379"/>
+      <c r="C43" s="379"/>
+      <c r="D43" s="379"/>
+      <c r="E43" s="379"/>
+      <c r="F43" s="379"/>
+      <c r="G43" s="379"/>
+      <c r="H43" s="379"/>
+      <c r="I43" s="379"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" s="17" t="s">
@@ -11701,12 +11754,12 @@
       <c r="G46" s="28"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A47" s="386" t="s">
+      <c r="A47" s="378" t="s">
         <v>15</v>
       </c>
-      <c r="B47" s="387"/>
-    </row>
-    <row r="49" spans="1:7" ht="14" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B47" s="379"/>
+    </row>
+    <row r="49" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A49" s="29" t="s">
         <v>14</v>
       </c>
@@ -11736,13 +11789,13 @@
       <c r="F51" s="16"/>
       <c r="G51" s="16"/>
     </row>
-    <row r="52" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A52" s="258" t="s">
+    <row r="52" spans="1:7" ht="16.2" x14ac:dyDescent="0.35">
+      <c r="A52" s="255" t="s">
         <v>262</v>
       </c>
       <c r="E52" s="34"/>
     </row>
-    <row r="53" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:7" ht="16.2" x14ac:dyDescent="0.35">
       <c r="A53" s="36"/>
       <c r="E53" s="34"/>
       <c r="G53" s="44"/>
@@ -11770,7 +11823,7 @@
       </c>
       <c r="G54" s="25"/>
     </row>
-    <row r="55" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:7" ht="16.2" x14ac:dyDescent="0.35">
       <c r="E55" s="34"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
@@ -11801,7 +11854,7 @@
       <c r="E57" s="26"/>
       <c r="G57" s="26"/>
     </row>
-    <row r="58" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A58" s="21" t="s">
         <v>60</v>
       </c>
@@ -11816,15 +11869,15 @@
       <c r="G59" s="32"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A61" s="258" t="s">
+      <c r="A61" s="255" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="E62" s="383" t="s">
+      <c r="E62" s="375" t="s">
         <v>29</v>
       </c>
-      <c r="F62" s="383"/>
+      <c r="F62" s="375"/>
       <c r="G62" s="25"/>
     </row>
     <row r="63" spans="1:7" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -11941,11 +11994,11 @@
       <c r="G72" s="26"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A74" s="384" t="s">
+      <c r="A74" s="376" t="s">
         <v>264</v>
       </c>
-      <c r="B74" s="384"/>
-      <c r="C74" s="384"/>
+      <c r="B74" s="376"/>
+      <c r="C74" s="376"/>
       <c r="D74" s="16"/>
       <c r="E74" s="16"/>
       <c r="G74" s="16"/>
@@ -12050,12 +12103,12 @@
       <c r="E81" s="16"/>
       <c r="G81" s="16"/>
     </row>
-    <row r="82" spans="1:7" ht="14" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A82" s="382" t="s">
+    <row r="82" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A82" s="374" t="s">
         <v>55</v>
       </c>
-      <c r="B82" s="382"/>
-      <c r="C82" s="382"/>
+      <c r="B82" s="374"/>
+      <c r="C82" s="374"/>
       <c r="D82" s="20"/>
       <c r="E82" s="20"/>
       <c r="F82" s="21"/>
@@ -12070,7 +12123,7 @@
       <c r="G83" s="16"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A84" s="259" t="s">
+      <c r="A84" s="256" t="s">
         <v>265</v>
       </c>
       <c r="B84" s="16"/>
@@ -12107,7 +12160,7 @@
       </c>
       <c r="G86" s="16"/>
     </row>
-    <row r="87" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:7" ht="15" x14ac:dyDescent="0.35">
       <c r="A87" s="24"/>
       <c r="C87" s="25"/>
       <c r="D87" s="25"/>
@@ -12187,14 +12240,14 @@
         <v>16</v>
       </c>
     </row>
-    <row r="94" spans="1:7" ht="14" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A94" s="380" t="s">
+    <row r="94" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A94" s="372" t="s">
         <v>13</v>
       </c>
-      <c r="B94" s="380"/>
-      <c r="C94" s="380"/>
-      <c r="D94" s="380"/>
-      <c r="E94" s="380"/>
+      <c r="B94" s="372"/>
+      <c r="C94" s="372"/>
+      <c r="D94" s="372"/>
+      <c r="E94" s="372"/>
       <c r="F94" s="21"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.35">
@@ -12205,10 +12258,10 @@
       <c r="E95" s="23"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A96" s="389" t="s">
+      <c r="A96" s="381" t="s">
         <v>266</v>
       </c>
-      <c r="B96" s="389"/>
+      <c r="B96" s="381"/>
       <c r="C96" s="16"/>
       <c r="D96" s="16"/>
       <c r="E96" s="16"/>
@@ -12250,7 +12303,7 @@
       <c r="E99" s="16"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A100" s="381" t="s">
+      <c r="A100" s="373" t="s">
         <v>30</v>
       </c>
       <c r="B100" s="16"/>
@@ -12272,7 +12325,7 @@
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A101" s="381"/>
+      <c r="A101" s="373"/>
       <c r="B101" s="16"/>
       <c r="C101" s="16"/>
       <c r="D101" s="16"/>
@@ -12285,12 +12338,12 @@
       <c r="D102" s="16"/>
       <c r="E102" s="16"/>
     </row>
-    <row r="103" spans="1:6" ht="14" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A103" s="380" t="s">
+    <row r="103" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A103" s="372" t="s">
         <v>54</v>
       </c>
-      <c r="B103" s="380"/>
-      <c r="C103" s="380"/>
+      <c r="B103" s="372"/>
+      <c r="C103" s="372"/>
       <c r="D103" s="20"/>
       <c r="E103" s="20"/>
       <c r="F103" s="21"/>
@@ -12300,7 +12353,7 @@
       <c r="E104" s="16"/>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A105" s="258" t="s">
+      <c r="A105" s="255" t="s">
         <v>267</v>
       </c>
     </row>
@@ -12347,7 +12400,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="111" spans="1:6" ht="14" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A111" s="21" t="s">
         <v>61</v>
       </c>
@@ -12357,7 +12410,7 @@
       <c r="E111" s="21"/>
       <c r="F111" s="21"/>
     </row>
-    <row r="112" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
       <c r="E112" s="34"/>
     </row>
   </sheetData>
@@ -12392,56 +12445,55 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:E57"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="44.453125" style="37" customWidth="1"/>
-    <col min="2" max="2" width="14.81640625" style="37" customWidth="1"/>
-    <col min="3" max="3" width="14.26953125" style="37" customWidth="1"/>
-    <col min="4" max="4" width="14.1796875" style="37" customWidth="1"/>
-    <col min="5" max="16384" width="9.1796875" style="37"/>
+    <col min="1" max="1" width="44.44140625" style="37" customWidth="1"/>
+    <col min="2" max="2" width="14.77734375" style="37" customWidth="1"/>
+    <col min="3" max="4" width="14.21875" style="37" customWidth="1"/>
+    <col min="5" max="16384" width="9.21875" style="37"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="378">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="370">
         <f>Assumptions.1!I3</f>
         <v>0</v>
       </c>
-      <c r="B1" s="378"/>
-      <c r="C1" s="378"/>
-      <c r="D1" s="378"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="378">
+      <c r="B1" s="370"/>
+      <c r="C1" s="370"/>
+      <c r="D1" s="370"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="370">
         <f>Assumptions.1!I5</f>
         <v>0</v>
       </c>
-      <c r="B2" s="378"/>
-      <c r="C2" s="378"/>
-      <c r="D2" s="378"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="378">
+      <c r="B2" s="370"/>
+      <c r="C2" s="370"/>
+      <c r="D2" s="370"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="370">
         <f>Assumptions.1!I6</f>
         <v>0</v>
       </c>
-      <c r="B3" s="378"/>
-      <c r="C3" s="378"/>
-      <c r="D3" s="378"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="379" t="s">
+      <c r="B3" s="370"/>
+      <c r="C3" s="370"/>
+      <c r="D3" s="370"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="371" t="s">
         <v>50</v>
       </c>
-      <c r="B5" s="379"/>
-      <c r="C5" s="379"/>
-      <c r="D5" s="379"/>
-    </row>
-    <row r="7" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B5" s="371"/>
+      <c r="C5" s="371"/>
+      <c r="D5" s="371"/>
+    </row>
+    <row r="7" spans="1:4" ht="16.2" x14ac:dyDescent="0.35">
       <c r="A7" s="134" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="121" t="s">
         <v>23</v>
       </c>
@@ -12458,7 +12510,7 @@
         <v>Projected</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="123"/>
       <c r="B9" s="124">
         <f>wp!D6</f>
@@ -12473,12 +12525,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="22.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" ht="22.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B10" s="41"/>
       <c r="C10" s="41"/>
       <c r="D10" s="41"/>
     </row>
-    <row r="11" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="37" t="s">
         <v>41</v>
       </c>
@@ -12495,12 +12547,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="42"/>
       <c r="C12" s="42"/>
       <c r="D12" s="42"/>
     </row>
-    <row r="13" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="37" t="s">
         <v>42</v>
       </c>
@@ -12517,13 +12569,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="37" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="16" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="37" t="s">
         <v>44</v>
       </c>
@@ -12540,17 +12592,17 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="42"/>
       <c r="C17" s="42"/>
       <c r="D17" s="42"/>
     </row>
-    <row r="18" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="37" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="37" t="s">
         <v>52</v>
       </c>
@@ -12567,12 +12619,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="37" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="37" t="s">
         <v>45</v>
       </c>
@@ -12589,12 +12641,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B23" s="42"/>
       <c r="C23" s="42"/>
       <c r="D23" s="42"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="37" t="s">
         <v>46</v>
       </c>
@@ -12611,12 +12663,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B25" s="42"/>
       <c r="C25" s="42"/>
       <c r="D25" s="42"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="37" t="s">
         <v>47</v>
       </c>
@@ -12633,12 +12685,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B27" s="42"/>
       <c r="C27" s="42"/>
       <c r="D27" s="42"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="39" t="s">
         <v>48</v>
       </c>
@@ -12655,7 +12707,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="39" t="s">
         <v>49</v>
       </c>
@@ -12663,27 +12715,27 @@
       <c r="C29" s="39"/>
       <c r="D29" s="39"/>
     </row>
-    <row r="30" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="55"/>
       <c r="B30" s="55"/>
       <c r="C30" s="55"/>
       <c r="D30" s="55"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A33" s="379" t="str">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="371" t="str">
         <f>A5</f>
         <v>CALCULATION OF MAXIMUM PERMISSIBLE BANK FINANCE</v>
       </c>
-      <c r="B33" s="379"/>
-      <c r="C33" s="379"/>
-      <c r="D33" s="379"/>
-    </row>
-    <row r="35" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B33" s="371"/>
+      <c r="C33" s="371"/>
+      <c r="D33" s="371"/>
+    </row>
+    <row r="35" spans="1:5" ht="16.2" x14ac:dyDescent="0.35">
       <c r="A35" s="134" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="121" t="s">
         <v>23</v>
       </c>
@@ -12700,7 +12752,7 @@
         <v>Projected</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:5" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="123"/>
       <c r="B37" s="124">
         <f t="shared" si="0"/>
@@ -12715,12 +12767,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B38" s="41"/>
       <c r="C38" s="41"/>
       <c r="D38" s="41"/>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="37" t="s">
         <v>41</v>
       </c>
@@ -12737,12 +12789,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B40" s="42"/>
       <c r="C40" s="42"/>
       <c r="D40" s="42"/>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="37" t="s">
         <v>42</v>
       </c>
@@ -12759,12 +12811,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="37" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="37" t="s">
         <v>44</v>
       </c>
@@ -12781,17 +12833,17 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B45" s="42"/>
       <c r="C45" s="42"/>
       <c r="D45" s="42"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="37" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="37" t="s">
         <v>72</v>
       </c>
@@ -12809,7 +12861,7 @@
       </c>
       <c r="E47" s="42"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="37" t="s">
         <v>45</v>
       </c>
@@ -12826,12 +12878,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B50" s="42"/>
       <c r="C50" s="42"/>
       <c r="D50" s="42"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="37" t="s">
         <v>46</v>
       </c>
@@ -12848,12 +12900,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B52" s="42"/>
       <c r="C52" s="42"/>
       <c r="D52" s="42"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="37" t="s">
         <v>47</v>
       </c>
@@ -12870,12 +12922,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B54" s="42"/>
       <c r="C54" s="42"/>
       <c r="D54" s="42"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="39" t="s">
         <v>48</v>
       </c>
@@ -12892,7 +12944,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="39" t="s">
         <v>49</v>
       </c>
@@ -12900,7 +12952,7 @@
       <c r="C56" s="39"/>
       <c r="D56" s="39"/>
     </row>
-    <row r="57" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="55"/>
       <c r="B57" s="55"/>
       <c r="C57" s="55"/>
@@ -12925,68 +12977,68 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:E29"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.26953125" style="37" customWidth="1"/>
-    <col min="2" max="2" width="10.453125" style="37" customWidth="1"/>
-    <col min="3" max="3" width="12.54296875" style="37" customWidth="1"/>
-    <col min="4" max="4" width="15.1796875" style="37" customWidth="1"/>
-    <col min="5" max="5" width="14.7265625" style="37" customWidth="1"/>
-    <col min="6" max="16384" width="9.1796875" style="37"/>
+    <col min="1" max="1" width="22.21875" style="37" customWidth="1"/>
+    <col min="2" max="2" width="10.44140625" style="37" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" style="37" customWidth="1"/>
+    <col min="4" max="4" width="15.21875" style="37" customWidth="1"/>
+    <col min="5" max="5" width="14.77734375" style="37" customWidth="1"/>
+    <col min="6" max="16384" width="9.21875" style="37"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="378" t="s">
+    <row r="1" spans="1:5" ht="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="370" t="s">
         <v>68</v>
       </c>
-      <c r="B2" s="378"/>
-      <c r="C2" s="378"/>
-      <c r="D2" s="378"/>
-      <c r="E2" s="378"/>
-    </row>
-    <row r="3" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="378">
+      <c r="B2" s="370"/>
+      <c r="C2" s="370"/>
+      <c r="D2" s="370"/>
+      <c r="E2" s="370"/>
+    </row>
+    <row r="3" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="370">
         <f>Assumptions.1!I5</f>
         <v>0</v>
       </c>
-      <c r="B3" s="378"/>
-      <c r="C3" s="378"/>
-      <c r="D3" s="378"/>
-      <c r="E3" s="378"/>
-    </row>
-    <row r="4" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="378" t="s">
+      <c r="B3" s="370"/>
+      <c r="C3" s="370"/>
+      <c r="D3" s="370"/>
+      <c r="E3" s="370"/>
+    </row>
+    <row r="4" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="370" t="s">
         <v>71</v>
       </c>
-      <c r="B4" s="378"/>
-      <c r="C4" s="378"/>
-      <c r="D4" s="378"/>
-      <c r="E4" s="378"/>
-    </row>
-    <row r="6" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="379" t="s">
+      <c r="B4" s="370"/>
+      <c r="C4" s="370"/>
+      <c r="D4" s="370"/>
+      <c r="E4" s="370"/>
+    </row>
+    <row r="6" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="371" t="s">
         <v>85</v>
       </c>
-      <c r="B6" s="379"/>
-      <c r="C6" s="379"/>
-      <c r="D6" s="379"/>
-      <c r="E6" s="379"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B6" s="371"/>
+      <c r="C6" s="371"/>
+      <c r="D6" s="371"/>
+      <c r="E6" s="371"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="39"/>
       <c r="B7" s="39"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="378" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="370" t="s">
         <v>86</v>
       </c>
-      <c r="B8" s="378"/>
-      <c r="C8" s="378"/>
-      <c r="D8" s="378"/>
-      <c r="E8" s="378"/>
-    </row>
-    <row r="10" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="370"/>
+      <c r="C8" s="370"/>
+      <c r="D8" s="370"/>
+      <c r="E8" s="370"/>
+    </row>
+    <row r="10" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="121" t="s">
         <v>0</v>
       </c>
@@ -13004,7 +13056,7 @@
         <v>Projected</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:5" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="123"/>
       <c r="B11" s="124"/>
       <c r="C11" s="124">
@@ -13020,8 +13072,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="37" t="s">
         <v>40</v>
       </c>
@@ -13039,10 +13091,10 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B14" s="42"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="37" t="s">
         <v>273</v>
       </c>
@@ -13060,16 +13112,16 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="37" t="s">
         <v>87</v>
       </c>
       <c r="B16" s="42"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B17" s="42"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="37" t="s">
         <v>274</v>
       </c>
@@ -13087,16 +13139,16 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="37" t="s">
         <v>275</v>
       </c>
       <c r="B19" s="42"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B20" s="42"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="37" t="s">
         <v>88</v>
       </c>
@@ -13114,10 +13166,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B22" s="42"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="37" t="s">
         <v>89</v>
       </c>
@@ -13135,24 +13187,24 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="55"/>
       <c r="B24" s="55"/>
       <c r="C24" s="55"/>
       <c r="D24" s="55"/>
       <c r="E24" s="55"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="39" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="37" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="37" t="s">
         <v>92</v>
       </c>
@@ -13173,93 +13225,93 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:M94"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.7265625" style="17" customWidth="1"/>
-    <col min="2" max="2" width="15.26953125" style="17" customWidth="1"/>
+    <col min="1" max="1" width="26.77734375" style="17" customWidth="1"/>
+    <col min="2" max="2" width="15.21875" style="17" customWidth="1"/>
     <col min="3" max="3" width="11" style="17" customWidth="1"/>
-    <col min="4" max="4" width="10.7265625" style="17" customWidth="1"/>
-    <col min="5" max="5" width="10.453125" style="17" customWidth="1"/>
-    <col min="6" max="6" width="10.81640625" style="17" customWidth="1"/>
-    <col min="7" max="7" width="12.81640625" style="17" customWidth="1"/>
-    <col min="8" max="9" width="11.54296875" style="17" customWidth="1"/>
-    <col min="10" max="10" width="12.54296875" style="17" customWidth="1"/>
-    <col min="11" max="11" width="11.54296875" style="17" customWidth="1"/>
-    <col min="12" max="12" width="13.1796875" style="17" customWidth="1"/>
-    <col min="13" max="13" width="11.453125" style="17" customWidth="1"/>
-    <col min="14" max="16384" width="9.1796875" style="17"/>
+    <col min="4" max="4" width="10.77734375" style="17" customWidth="1"/>
+    <col min="5" max="5" width="10.44140625" style="17" customWidth="1"/>
+    <col min="6" max="6" width="10.77734375" style="17" customWidth="1"/>
+    <col min="7" max="7" width="12.77734375" style="17" customWidth="1"/>
+    <col min="8" max="9" width="11.5546875" style="17" customWidth="1"/>
+    <col min="10" max="10" width="12.5546875" style="17" customWidth="1"/>
+    <col min="11" max="11" width="11.5546875" style="17" customWidth="1"/>
+    <col min="12" max="12" width="13.21875" style="17" customWidth="1"/>
+    <col min="13" max="13" width="11.44140625" style="17" customWidth="1"/>
+    <col min="14" max="16384" width="9.21875" style="17"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A1" s="390">
+      <c r="A1" s="382">
         <f>Assumptions.1!I3</f>
         <v>0</v>
       </c>
-      <c r="B1" s="390"/>
-      <c r="C1" s="390"/>
-      <c r="D1" s="390"/>
-      <c r="E1" s="390"/>
-      <c r="F1" s="390"/>
-      <c r="G1" s="390"/>
-      <c r="H1" s="390"/>
-      <c r="I1" s="390"/>
-      <c r="J1" s="390"/>
-      <c r="K1" s="390"/>
-      <c r="L1" s="390"/>
-      <c r="M1" s="390"/>
+      <c r="B1" s="382"/>
+      <c r="C1" s="382"/>
+      <c r="D1" s="382"/>
+      <c r="E1" s="382"/>
+      <c r="F1" s="382"/>
+      <c r="G1" s="382"/>
+      <c r="H1" s="382"/>
+      <c r="I1" s="382"/>
+      <c r="J1" s="382"/>
+      <c r="K1" s="382"/>
+      <c r="L1" s="382"/>
+      <c r="M1" s="382"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" s="390">
+      <c r="A2" s="382">
         <f>Assumptions.1!I5</f>
         <v>0</v>
       </c>
-      <c r="B2" s="390"/>
-      <c r="C2" s="390"/>
-      <c r="D2" s="390"/>
-      <c r="E2" s="390"/>
-      <c r="F2" s="390"/>
-      <c r="G2" s="390"/>
-      <c r="H2" s="390"/>
-      <c r="I2" s="390"/>
-      <c r="J2" s="390"/>
-      <c r="K2" s="390"/>
-      <c r="L2" s="390"/>
-      <c r="M2" s="390"/>
+      <c r="B2" s="382"/>
+      <c r="C2" s="382"/>
+      <c r="D2" s="382"/>
+      <c r="E2" s="382"/>
+      <c r="F2" s="382"/>
+      <c r="G2" s="382"/>
+      <c r="H2" s="382"/>
+      <c r="I2" s="382"/>
+      <c r="J2" s="382"/>
+      <c r="K2" s="382"/>
+      <c r="L2" s="382"/>
+      <c r="M2" s="382"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" s="390">
+      <c r="A3" s="382">
         <f>Assumptions.1!I6</f>
         <v>0</v>
       </c>
-      <c r="B3" s="390"/>
-      <c r="C3" s="390"/>
-      <c r="D3" s="390"/>
-      <c r="E3" s="390"/>
-      <c r="F3" s="390"/>
-      <c r="G3" s="390"/>
-      <c r="H3" s="390"/>
-      <c r="I3" s="390"/>
-      <c r="J3" s="390"/>
-      <c r="K3" s="390"/>
-      <c r="L3" s="390"/>
-      <c r="M3" s="390"/>
+      <c r="B3" s="382"/>
+      <c r="C3" s="382"/>
+      <c r="D3" s="382"/>
+      <c r="E3" s="382"/>
+      <c r="F3" s="382"/>
+      <c r="G3" s="382"/>
+      <c r="H3" s="382"/>
+      <c r="I3" s="382"/>
+      <c r="J3" s="382"/>
+      <c r="K3" s="382"/>
+      <c r="L3" s="382"/>
+      <c r="M3" s="382"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" s="390" t="s">
+      <c r="A5" s="382" t="s">
         <v>115</v>
       </c>
-      <c r="B5" s="390"/>
-      <c r="C5" s="390"/>
-      <c r="D5" s="390"/>
-      <c r="E5" s="390"/>
-      <c r="F5" s="390"/>
-      <c r="G5" s="390"/>
-      <c r="H5" s="390"/>
-      <c r="I5" s="390"/>
-      <c r="J5" s="390"/>
-      <c r="K5" s="390"/>
-      <c r="L5" s="390"/>
-      <c r="M5" s="390"/>
+      <c r="B5" s="382"/>
+      <c r="C5" s="382"/>
+      <c r="D5" s="382"/>
+      <c r="E5" s="382"/>
+      <c r="F5" s="382"/>
+      <c r="G5" s="382"/>
+      <c r="H5" s="382"/>
+      <c r="I5" s="382"/>
+      <c r="J5" s="382"/>
+      <c r="K5" s="382"/>
+      <c r="L5" s="382"/>
+      <c r="M5" s="382"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="40"/>
@@ -13300,47 +13352,47 @@
     </row>
     <row r="9" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="93"/>
-      <c r="B9" s="392" t="str">
+      <c r="B9" s="384" t="str">
         <f>Assumptions.1!B99</f>
         <v>Plant and Machinery</v>
       </c>
-      <c r="C9" s="391" t="str">
+      <c r="C9" s="383" t="str">
         <f>Assumptions.1!B109</f>
         <v>Service Equipment</v>
       </c>
-      <c r="D9" s="392" t="str">
+      <c r="D9" s="384" t="str">
         <f>Assumptions.1!B119</f>
         <v>Shed and Civil works</v>
       </c>
-      <c r="E9" s="393" t="str">
+      <c r="E9" s="385" t="str">
         <f>Assumptions.1!B129</f>
         <v>Land</v>
       </c>
-      <c r="F9" s="392" t="str">
+      <c r="F9" s="384" t="str">
         <f>Assumptions.1!B132</f>
         <v>Electrical Items</v>
       </c>
-      <c r="G9" s="392" t="str">
+      <c r="G9" s="384" t="str">
         <f>Assumptions.1!B141</f>
         <v>Electronic items</v>
       </c>
-      <c r="H9" s="392" t="str">
+      <c r="H9" s="384" t="str">
         <f>Assumptions.1!B151</f>
         <v xml:space="preserve">Furniture and Fittings </v>
       </c>
-      <c r="I9" s="394" t="str">
+      <c r="I9" s="386" t="str">
         <f>Assumptions.1!B161</f>
         <v>Vehicles</v>
       </c>
-      <c r="J9" s="393" t="str">
+      <c r="J9" s="385" t="str">
         <f>Assumptions.1!B171</f>
         <v>Live stock</v>
       </c>
-      <c r="K9" s="393" t="str">
+      <c r="K9" s="385" t="str">
         <f>Assumptions.1!B180</f>
         <v>Other Assets</v>
       </c>
-      <c r="L9" s="392" t="str">
+      <c r="L9" s="384" t="str">
         <f>Assumptions.1!B190</f>
         <v>Other Assets (Nil Depreciation)</v>
       </c>
@@ -13348,37 +13400,37 @@
     </row>
     <row r="10" spans="1:13" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="93"/>
-      <c r="B10" s="392"/>
-      <c r="C10" s="391"/>
-      <c r="D10" s="392"/>
-      <c r="E10" s="393"/>
-      <c r="F10" s="392"/>
-      <c r="G10" s="392"/>
-      <c r="H10" s="392"/>
-      <c r="I10" s="394"/>
-      <c r="J10" s="393"/>
-      <c r="K10" s="393"/>
-      <c r="L10" s="392"/>
+      <c r="B10" s="384"/>
+      <c r="C10" s="383"/>
+      <c r="D10" s="384"/>
+      <c r="E10" s="385"/>
+      <c r="F10" s="384"/>
+      <c r="G10" s="384"/>
+      <c r="H10" s="384"/>
+      <c r="I10" s="386"/>
+      <c r="J10" s="385"/>
+      <c r="K10" s="385"/>
+      <c r="L10" s="384"/>
       <c r="M10" s="94"/>
     </row>
     <row r="11" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="93"/>
       <c r="B11" s="94"/>
-      <c r="C11" s="391"/>
+      <c r="C11" s="383"/>
       <c r="D11" s="95"/>
       <c r="E11" s="95"/>
       <c r="F11" s="95"/>
       <c r="G11" s="95"/>
       <c r="H11" s="95"/>
-      <c r="I11" s="394"/>
+      <c r="I11" s="386"/>
       <c r="J11" s="95"/>
       <c r="K11" s="95"/>
-      <c r="L11" s="392"/>
+      <c r="L11" s="384"/>
       <c r="M11" s="94" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="14" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="96"/>
       <c r="B12" s="97">
         <f>Assumptions.1!I69</f>
@@ -13426,7 +13478,7 @@
       </c>
       <c r="M12" s="98"/>
     </row>
-    <row r="13" spans="1:13" ht="14" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="B13" s="99"/>
       <c r="C13" s="99"/>
       <c r="D13" s="99"/>
@@ -14311,20 +14363,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="14" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35" s="21"/>
-      <c r="B35" s="300"/>
-      <c r="C35" s="300"/>
-      <c r="D35" s="300"/>
-      <c r="E35" s="300"/>
-      <c r="F35" s="300"/>
-      <c r="G35" s="300"/>
-      <c r="H35" s="300"/>
-      <c r="I35" s="300"/>
-      <c r="J35" s="300"/>
-      <c r="K35" s="300"/>
-      <c r="L35" s="300"/>
-      <c r="M35" s="300"/>
+      <c r="B35" s="297"/>
+      <c r="C35" s="297"/>
+      <c r="D35" s="297"/>
+      <c r="E35" s="297"/>
+      <c r="F35" s="297"/>
+      <c r="G35" s="297"/>
+      <c r="H35" s="297"/>
+      <c r="I35" s="297"/>
+      <c r="J35" s="297"/>
+      <c r="K35" s="297"/>
+      <c r="L35" s="297"/>
+      <c r="M35" s="297"/>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A36" s="31"/>
